--- a/docs/工作/00-指南与规范/我的工作进度表-曹.xlsx
+++ b/docs/工作/00-指南与规范/我的工作进度表-曹.xlsx
@@ -17,11 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="m/d"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="mm-dd"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -197,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -346,6 +347,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -835,7 +846,7 @@
           <t>在「我的任务」填完自动更新；今天：</t>
         </is>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="58">
         <f>TODAY()</f>
         <v/>
       </c>
@@ -2352,10 +2363,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E3" s="51" t="n">
+      <c r="E3" s="59" t="n">
         <v>46239</v>
       </c>
-      <c r="F3" s="51" t="n">
+      <c r="F3" s="59" t="n">
         <v>46241</v>
       </c>
       <c r="G3" s="27">
@@ -2390,10 +2401,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E4" s="51" t="n">
+      <c r="E4" s="59" t="n">
         <v>46240</v>
       </c>
-      <c r="F4" s="51" t="n"/>
+      <c r="F4" s="59" t="n"/>
       <c r="G4" s="27">
         <f>IF(AND(D4&lt;&gt;"已完成",D4&lt;&gt;"",E4&lt;&gt;"",E4&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2426,10 +2437,10 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="E5" s="51" t="n">
+      <c r="E5" s="59" t="n">
         <v>46240</v>
       </c>
-      <c r="F5" s="51" t="n"/>
+      <c r="F5" s="59" t="n"/>
       <c r="G5" s="27">
         <f>IF(AND(D5&lt;&gt;"已完成",D5&lt;&gt;"",E5&lt;&gt;"",E5&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2458,10 +2469,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="59" t="n">
         <v>46240</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="59" t="n">
         <v>46240</v>
       </c>
       <c r="G6" s="27">
@@ -2496,8 +2507,8 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="E7" s="51" t="n"/>
-      <c r="F7" s="51" t="n"/>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="59" t="n"/>
       <c r="G7" s="27">
         <f>IF(AND(D7&lt;&gt;"已完成",D7&lt;&gt;"",E7&lt;&gt;"",E7&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2530,10 +2541,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E8" s="51" t="n">
+      <c r="E8" s="59" t="n">
         <v>46240</v>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="59" t="n">
         <v>46240</v>
       </c>
       <c r="G8" s="27">
@@ -2568,10 +2579,10 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="E9" s="51" t="n">
+      <c r="E9" s="59" t="n">
         <v>46241</v>
       </c>
-      <c r="F9" s="51" t="n"/>
+      <c r="F9" s="59" t="n"/>
       <c r="G9" s="27">
         <f>IF(AND(D9&lt;&gt;"已完成",D9&lt;&gt;"",E9&lt;&gt;"",E9&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2604,10 +2615,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E10" s="51" t="n">
+      <c r="E10" s="59" t="n">
         <v>46241</v>
       </c>
-      <c r="F10" s="51" t="n"/>
+      <c r="F10" s="59" t="n"/>
       <c r="G10" s="27">
         <f>IF(AND(D10&lt;&gt;"已完成",D10&lt;&gt;"",E10&lt;&gt;"",E10&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2640,10 +2651,10 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="E11" s="51" t="n">
+      <c r="E11" s="59" t="n">
         <v>46246</v>
       </c>
-      <c r="F11" s="51" t="n"/>
+      <c r="F11" s="59" t="n"/>
       <c r="G11" s="27">
         <f>IF(AND(D11&lt;&gt;"已完成",D11&lt;&gt;"",E11&lt;&gt;"",E11&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2672,10 +2683,10 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="E12" s="51" t="n">
+      <c r="E12" s="59" t="n">
         <v>46248</v>
       </c>
-      <c r="F12" s="51" t="n"/>
+      <c r="F12" s="59" t="n"/>
       <c r="G12" s="27">
         <f>IF(AND(D12&lt;&gt;"已完成",D12&lt;&gt;"",E12&lt;&gt;"",E12&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2704,10 +2715,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E13" s="51" t="n">
+      <c r="E13" s="59" t="n">
         <v>46241</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="59" t="n">
         <v>46245</v>
       </c>
       <c r="G13" s="27">
@@ -2742,10 +2753,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="59" t="n">
         <v>46244</v>
       </c>
-      <c r="F14" s="51" t="n"/>
+      <c r="F14" s="59" t="n"/>
       <c r="G14" s="27">
         <f>IF(AND(D14&lt;&gt;"已完成",D14&lt;&gt;"",E14&lt;&gt;"",E14&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2778,10 +2789,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E15" s="51" t="n">
+      <c r="E15" s="59" t="n">
         <v>46254</v>
       </c>
-      <c r="F15" s="51" t="n"/>
+      <c r="F15" s="59" t="n"/>
       <c r="G15" s="27">
         <f>IF(AND(D15&lt;&gt;"已完成",D15&lt;&gt;"",E15&lt;&gt;"",E15&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2810,10 +2821,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E16" s="51" t="n">
+      <c r="E16" s="59" t="n">
         <v>46241</v>
       </c>
-      <c r="F16" s="51" t="n"/>
+      <c r="F16" s="59" t="n"/>
       <c r="G16" s="27">
         <f>IF(AND(D16&lt;&gt;"已完成",D16&lt;&gt;"",E16&lt;&gt;"",E16&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2842,10 +2853,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E17" s="51" t="n">
+      <c r="E17" s="59" t="n">
         <v>46241</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="59" t="n">
         <v>46241</v>
       </c>
       <c r="G17" s="27">
@@ -2880,8 +2891,8 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="E18" s="51" t="n"/>
-      <c r="F18" s="51" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="59" t="n"/>
       <c r="G18" s="27">
         <f>IF(AND(D18&lt;&gt;"已完成",D18&lt;&gt;"",E18&lt;&gt;"",E18&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -2910,10 +2921,10 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="60" t="n">
         <v>46247</v>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F19" s="60" t="n">
         <v>46250</v>
       </c>
       <c r="G19" s="31">
@@ -2924,2600 +2935,2600 @@
       <c r="I19" s="33" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="50">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>Sakuranomori</t>
         </is>
       </c>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>9-12月份库存</t>
         </is>
       </c>
-      <c r="C20" s="39" t="inlineStr">
+      <c r="C20" s="54" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="E20" s="53" t="n">
+      <c r="E20" s="61" t="n">
         <v>46244</v>
       </c>
-      <c r="F20" s="53" t="n">
+      <c r="F20" s="61" t="n">
         <v>46244</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="57">
         <f>IF(AND(D20&lt;&gt;"已完成",D20&lt;&gt;"",E20&lt;&gt;"",E20&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H20" s="39" t="inlineStr">
+      <c r="H20" s="54" t="inlineStr">
         <is>
           <t>天猫</t>
         </is>
       </c>
-      <c r="I20" s="38" t="n"/>
+      <c r="I20" s="55" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="50">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="54" t="inlineStr">
         <is>
           <t>Sakuranomori</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>koc笔记审核</t>
         </is>
       </c>
-      <c r="C21" s="39" t="inlineStr">
+      <c r="C21" s="54" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="D21" s="39" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="E21" s="53" t="n"/>
-      <c r="F21" s="53" t="n"/>
-      <c r="G21" s="37">
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="61" t="n"/>
+      <c r="G21" s="57">
         <f>IF(AND(D21&lt;&gt;"已完成",D21&lt;&gt;"",E21&lt;&gt;"",E21&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H21" s="39" t="n"/>
-      <c r="I21" s="38" t="n"/>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="55" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="50">
-      <c r="A22" s="39" t="n"/>
-      <c r="B22" s="38" t="n"/>
-      <c r="C22" s="39" t="n"/>
-      <c r="D22" s="39" t="n"/>
-      <c r="E22" s="53" t="n"/>
-      <c r="F22" s="53" t="n"/>
-      <c r="G22" s="37">
+      <c r="A22" s="54" t="n"/>
+      <c r="B22" s="55" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="61" t="n"/>
+      <c r="G22" s="57">
         <f>IF(AND(D22&lt;&gt;"已完成",D22&lt;&gt;"",E22&lt;&gt;"",E22&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H22" s="39" t="n"/>
-      <c r="I22" s="38" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="55" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="50">
-      <c r="A23" s="39" t="n"/>
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="39" t="n"/>
-      <c r="D23" s="39" t="n"/>
-      <c r="E23" s="53" t="n"/>
-      <c r="F23" s="53" t="n"/>
-      <c r="G23" s="37">
+      <c r="A23" s="54" t="n"/>
+      <c r="B23" s="55" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="61" t="n"/>
+      <c r="G23" s="57">
         <f>IF(AND(D23&lt;&gt;"已完成",D23&lt;&gt;"",E23&lt;&gt;"",E23&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H23" s="39" t="n"/>
-      <c r="I23" s="38" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="55" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="50">
-      <c r="A24" s="39" t="n"/>
-      <c r="B24" s="38" t="n"/>
-      <c r="C24" s="39" t="n"/>
-      <c r="D24" s="39" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
-      <c r="G24" s="37">
+      <c r="A24" s="54" t="n"/>
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="61" t="n"/>
+      <c r="G24" s="57">
         <f>IF(AND(D24&lt;&gt;"已完成",D24&lt;&gt;"",E24&lt;&gt;"",E24&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H24" s="39" t="n"/>
-      <c r="I24" s="38" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="55" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="50">
-      <c r="A25" s="39" t="n"/>
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="39" t="n"/>
-      <c r="D25" s="39" t="n"/>
-      <c r="E25" s="53" t="n"/>
-      <c r="F25" s="53" t="n"/>
-      <c r="G25" s="37">
+      <c r="A25" s="54" t="n"/>
+      <c r="B25" s="55" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="61" t="n"/>
+      <c r="F25" s="61" t="n"/>
+      <c r="G25" s="57">
         <f>IF(AND(D25&lt;&gt;"已完成",D25&lt;&gt;"",E25&lt;&gt;"",E25&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H25" s="39" t="n"/>
-      <c r="I25" s="38" t="n"/>
+      <c r="H25" s="54" t="n"/>
+      <c r="I25" s="55" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="50">
-      <c r="A26" s="39" t="n"/>
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="39" t="n"/>
-      <c r="D26" s="39" t="n"/>
-      <c r="E26" s="53" t="n"/>
-      <c r="F26" s="53" t="n"/>
-      <c r="G26" s="37">
+      <c r="A26" s="54" t="n"/>
+      <c r="B26" s="55" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="61" t="n"/>
+      <c r="F26" s="61" t="n"/>
+      <c r="G26" s="57">
         <f>IF(AND(D26&lt;&gt;"已完成",D26&lt;&gt;"",E26&lt;&gt;"",E26&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H26" s="39" t="n"/>
-      <c r="I26" s="38" t="n"/>
+      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="55" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="50">
-      <c r="A27" s="39" t="n"/>
-      <c r="B27" s="38" t="n"/>
-      <c r="C27" s="39" t="n"/>
-      <c r="D27" s="39" t="n"/>
-      <c r="E27" s="53" t="n"/>
-      <c r="F27" s="53" t="n"/>
-      <c r="G27" s="37">
+      <c r="A27" s="54" t="n"/>
+      <c r="B27" s="55" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="61" t="n"/>
+      <c r="F27" s="61" t="n"/>
+      <c r="G27" s="57">
         <f>IF(AND(D27&lt;&gt;"已完成",D27&lt;&gt;"",E27&lt;&gt;"",E27&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H27" s="39" t="n"/>
-      <c r="I27" s="38" t="n"/>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="55" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="50">
-      <c r="A28" s="39" t="n"/>
-      <c r="B28" s="38" t="n"/>
-      <c r="C28" s="39" t="n"/>
-      <c r="D28" s="39" t="n"/>
-      <c r="E28" s="53" t="n"/>
-      <c r="F28" s="53" t="n"/>
-      <c r="G28" s="37">
+      <c r="A28" s="54" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="61" t="n"/>
+      <c r="F28" s="61" t="n"/>
+      <c r="G28" s="57">
         <f>IF(AND(D28&lt;&gt;"已完成",D28&lt;&gt;"",E28&lt;&gt;"",E28&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H28" s="39" t="n"/>
-      <c r="I28" s="38" t="n"/>
+      <c r="H28" s="54" t="n"/>
+      <c r="I28" s="55" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="50">
-      <c r="A29" s="39" t="n"/>
-      <c r="B29" s="38" t="n"/>
-      <c r="C29" s="39" t="n"/>
-      <c r="D29" s="39" t="n"/>
-      <c r="E29" s="53" t="n"/>
-      <c r="F29" s="53" t="n"/>
-      <c r="G29" s="37">
+      <c r="A29" s="54" t="n"/>
+      <c r="B29" s="55" t="n"/>
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="61" t="n"/>
+      <c r="F29" s="61" t="n"/>
+      <c r="G29" s="57">
         <f>IF(AND(D29&lt;&gt;"已完成",D29&lt;&gt;"",E29&lt;&gt;"",E29&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H29" s="39" t="n"/>
-      <c r="I29" s="38" t="n"/>
+      <c r="H29" s="54" t="n"/>
+      <c r="I29" s="55" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="50">
-      <c r="A30" s="39" t="n"/>
-      <c r="B30" s="38" t="n"/>
-      <c r="C30" s="39" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="53" t="n"/>
-      <c r="F30" s="53" t="n"/>
-      <c r="G30" s="37">
+      <c r="A30" s="54" t="n"/>
+      <c r="B30" s="55" t="n"/>
+      <c r="C30" s="54" t="n"/>
+      <c r="D30" s="54" t="n"/>
+      <c r="E30" s="61" t="n"/>
+      <c r="F30" s="61" t="n"/>
+      <c r="G30" s="57">
         <f>IF(AND(D30&lt;&gt;"已完成",D30&lt;&gt;"",E30&lt;&gt;"",E30&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H30" s="39" t="n"/>
-      <c r="I30" s="38" t="n"/>
+      <c r="H30" s="54" t="n"/>
+      <c r="I30" s="55" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="50">
-      <c r="A31" s="39" t="n"/>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="39" t="n"/>
-      <c r="D31" s="39" t="n"/>
-      <c r="E31" s="53" t="n"/>
-      <c r="F31" s="53" t="n"/>
-      <c r="G31" s="37">
+      <c r="A31" s="54" t="n"/>
+      <c r="B31" s="55" t="n"/>
+      <c r="C31" s="54" t="n"/>
+      <c r="D31" s="54" t="n"/>
+      <c r="E31" s="61" t="n"/>
+      <c r="F31" s="61" t="n"/>
+      <c r="G31" s="57">
         <f>IF(AND(D31&lt;&gt;"已完成",D31&lt;&gt;"",E31&lt;&gt;"",E31&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H31" s="39" t="n"/>
-      <c r="I31" s="38" t="n"/>
+      <c r="H31" s="54" t="n"/>
+      <c r="I31" s="55" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="50">
-      <c r="A32" s="39" t="n"/>
-      <c r="B32" s="38" t="n"/>
-      <c r="C32" s="39" t="n"/>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="53" t="n"/>
-      <c r="F32" s="53" t="n"/>
-      <c r="G32" s="37">
+      <c r="A32" s="54" t="n"/>
+      <c r="B32" s="55" t="n"/>
+      <c r="C32" s="54" t="n"/>
+      <c r="D32" s="54" t="n"/>
+      <c r="E32" s="61" t="n"/>
+      <c r="F32" s="61" t="n"/>
+      <c r="G32" s="57">
         <f>IF(AND(D32&lt;&gt;"已完成",D32&lt;&gt;"",E32&lt;&gt;"",E32&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H32" s="39" t="n"/>
-      <c r="I32" s="38" t="n"/>
+      <c r="H32" s="54" t="n"/>
+      <c r="I32" s="55" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="50">
-      <c r="A33" s="39" t="n"/>
-      <c r="B33" s="38" t="n"/>
-      <c r="C33" s="39" t="n"/>
-      <c r="D33" s="39" t="n"/>
-      <c r="E33" s="53" t="n"/>
-      <c r="F33" s="53" t="n"/>
-      <c r="G33" s="37">
+      <c r="A33" s="54" t="n"/>
+      <c r="B33" s="55" t="n"/>
+      <c r="C33" s="54" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="61" t="n"/>
+      <c r="F33" s="61" t="n"/>
+      <c r="G33" s="57">
         <f>IF(AND(D33&lt;&gt;"已完成",D33&lt;&gt;"",E33&lt;&gt;"",E33&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H33" s="39" t="n"/>
-      <c r="I33" s="38" t="n"/>
+      <c r="H33" s="54" t="n"/>
+      <c r="I33" s="55" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="50">
-      <c r="A34" s="39" t="n"/>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="39" t="n"/>
-      <c r="D34" s="39" t="n"/>
-      <c r="E34" s="53" t="n"/>
-      <c r="F34" s="53" t="n"/>
-      <c r="G34" s="37">
+      <c r="A34" s="54" t="n"/>
+      <c r="B34" s="55" t="n"/>
+      <c r="C34" s="54" t="n"/>
+      <c r="D34" s="54" t="n"/>
+      <c r="E34" s="61" t="n"/>
+      <c r="F34" s="61" t="n"/>
+      <c r="G34" s="57">
         <f>IF(AND(D34&lt;&gt;"已完成",D34&lt;&gt;"",E34&lt;&gt;"",E34&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H34" s="39" t="n"/>
-      <c r="I34" s="38" t="n"/>
+      <c r="H34" s="54" t="n"/>
+      <c r="I34" s="55" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="50">
-      <c r="A35" s="39" t="n"/>
-      <c r="B35" s="38" t="n"/>
-      <c r="C35" s="39" t="n"/>
-      <c r="D35" s="39" t="n"/>
-      <c r="E35" s="53" t="n"/>
-      <c r="F35" s="53" t="n"/>
-      <c r="G35" s="37">
+      <c r="A35" s="54" t="n"/>
+      <c r="B35" s="55" t="n"/>
+      <c r="C35" s="54" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="61" t="n"/>
+      <c r="F35" s="61" t="n"/>
+      <c r="G35" s="57">
         <f>IF(AND(D35&lt;&gt;"已完成",D35&lt;&gt;"",E35&lt;&gt;"",E35&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H35" s="39" t="n"/>
-      <c r="I35" s="38" t="n"/>
+      <c r="H35" s="54" t="n"/>
+      <c r="I35" s="55" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="50">
-      <c r="A36" s="39" t="n"/>
-      <c r="B36" s="38" t="n"/>
-      <c r="C36" s="39" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
-      <c r="G36" s="37">
+      <c r="A36" s="54" t="n"/>
+      <c r="B36" s="55" t="n"/>
+      <c r="C36" s="54" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="61" t="n"/>
+      <c r="F36" s="61" t="n"/>
+      <c r="G36" s="57">
         <f>IF(AND(D36&lt;&gt;"已完成",D36&lt;&gt;"",E36&lt;&gt;"",E36&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H36" s="39" t="n"/>
-      <c r="I36" s="38" t="n"/>
+      <c r="H36" s="54" t="n"/>
+      <c r="I36" s="55" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="50">
-      <c r="A37" s="39" t="n"/>
-      <c r="B37" s="38" t="n"/>
-      <c r="C37" s="39" t="n"/>
-      <c r="D37" s="39" t="n"/>
-      <c r="E37" s="53" t="n"/>
-      <c r="F37" s="53" t="n"/>
-      <c r="G37" s="37">
+      <c r="A37" s="54" t="n"/>
+      <c r="B37" s="55" t="n"/>
+      <c r="C37" s="54" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="61" t="n"/>
+      <c r="F37" s="61" t="n"/>
+      <c r="G37" s="57">
         <f>IF(AND(D37&lt;&gt;"已完成",D37&lt;&gt;"",E37&lt;&gt;"",E37&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H37" s="39" t="n"/>
-      <c r="I37" s="38" t="n"/>
+      <c r="H37" s="54" t="n"/>
+      <c r="I37" s="55" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="50">
-      <c r="A38" s="39" t="n"/>
-      <c r="B38" s="38" t="n"/>
-      <c r="C38" s="39" t="n"/>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="53" t="n"/>
-      <c r="F38" s="53" t="n"/>
-      <c r="G38" s="37">
+      <c r="A38" s="54" t="n"/>
+      <c r="B38" s="55" t="n"/>
+      <c r="C38" s="54" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="61" t="n"/>
+      <c r="F38" s="61" t="n"/>
+      <c r="G38" s="57">
         <f>IF(AND(D38&lt;&gt;"已完成",D38&lt;&gt;"",E38&lt;&gt;"",E38&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H38" s="39" t="n"/>
-      <c r="I38" s="38" t="n"/>
+      <c r="H38" s="54" t="n"/>
+      <c r="I38" s="55" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="50">
-      <c r="A39" s="39" t="n"/>
-      <c r="B39" s="38" t="n"/>
-      <c r="C39" s="39" t="n"/>
-      <c r="D39" s="39" t="n"/>
-      <c r="E39" s="53" t="n"/>
-      <c r="F39" s="53" t="n"/>
-      <c r="G39" s="37">
+      <c r="A39" s="54" t="n"/>
+      <c r="B39" s="55" t="n"/>
+      <c r="C39" s="54" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="61" t="n"/>
+      <c r="F39" s="61" t="n"/>
+      <c r="G39" s="57">
         <f>IF(AND(D39&lt;&gt;"已完成",D39&lt;&gt;"",E39&lt;&gt;"",E39&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H39" s="39" t="n"/>
-      <c r="I39" s="38" t="n"/>
+      <c r="H39" s="54" t="n"/>
+      <c r="I39" s="55" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="50">
-      <c r="A40" s="39" t="n"/>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="39" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="53" t="n"/>
-      <c r="F40" s="53" t="n"/>
-      <c r="G40" s="37">
+      <c r="A40" s="54" t="n"/>
+      <c r="B40" s="55" t="n"/>
+      <c r="C40" s="54" t="n"/>
+      <c r="D40" s="54" t="n"/>
+      <c r="E40" s="61" t="n"/>
+      <c r="F40" s="61" t="n"/>
+      <c r="G40" s="57">
         <f>IF(AND(D40&lt;&gt;"已完成",D40&lt;&gt;"",E40&lt;&gt;"",E40&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H40" s="39" t="n"/>
-      <c r="I40" s="38" t="n"/>
+      <c r="H40" s="54" t="n"/>
+      <c r="I40" s="55" t="n"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="50">
-      <c r="A41" s="39" t="n"/>
-      <c r="B41" s="38" t="n"/>
-      <c r="C41" s="39" t="n"/>
-      <c r="D41" s="39" t="n"/>
-      <c r="E41" s="53" t="n"/>
-      <c r="F41" s="53" t="n"/>
-      <c r="G41" s="37">
+      <c r="A41" s="54" t="n"/>
+      <c r="B41" s="55" t="n"/>
+      <c r="C41" s="54" t="n"/>
+      <c r="D41" s="54" t="n"/>
+      <c r="E41" s="61" t="n"/>
+      <c r="F41" s="61" t="n"/>
+      <c r="G41" s="57">
         <f>IF(AND(D41&lt;&gt;"已完成",D41&lt;&gt;"",E41&lt;&gt;"",E41&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H41" s="39" t="n"/>
-      <c r="I41" s="38" t="n"/>
+      <c r="H41" s="54" t="n"/>
+      <c r="I41" s="55" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="50">
-      <c r="A42" s="39" t="n"/>
-      <c r="B42" s="38" t="n"/>
-      <c r="C42" s="39" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="53" t="n"/>
-      <c r="F42" s="53" t="n"/>
-      <c r="G42" s="37">
+      <c r="A42" s="54" t="n"/>
+      <c r="B42" s="55" t="n"/>
+      <c r="C42" s="54" t="n"/>
+      <c r="D42" s="54" t="n"/>
+      <c r="E42" s="61" t="n"/>
+      <c r="F42" s="61" t="n"/>
+      <c r="G42" s="57">
         <f>IF(AND(D42&lt;&gt;"已完成",D42&lt;&gt;"",E42&lt;&gt;"",E42&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H42" s="39" t="n"/>
-      <c r="I42" s="38" t="n"/>
+      <c r="H42" s="54" t="n"/>
+      <c r="I42" s="55" t="n"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="50">
-      <c r="A43" s="39" t="n"/>
-      <c r="B43" s="38" t="n"/>
-      <c r="C43" s="39" t="n"/>
-      <c r="D43" s="39" t="n"/>
-      <c r="E43" s="53" t="n"/>
-      <c r="F43" s="53" t="n"/>
-      <c r="G43" s="37">
+      <c r="A43" s="54" t="n"/>
+      <c r="B43" s="55" t="n"/>
+      <c r="C43" s="54" t="n"/>
+      <c r="D43" s="54" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="61" t="n"/>
+      <c r="G43" s="57">
         <f>IF(AND(D43&lt;&gt;"已完成",D43&lt;&gt;"",E43&lt;&gt;"",E43&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H43" s="39" t="n"/>
-      <c r="I43" s="38" t="n"/>
+      <c r="H43" s="54" t="n"/>
+      <c r="I43" s="55" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="50">
-      <c r="A44" s="39" t="n"/>
-      <c r="B44" s="38" t="n"/>
-      <c r="C44" s="39" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="53" t="n"/>
-      <c r="F44" s="53" t="n"/>
-      <c r="G44" s="37">
+      <c r="A44" s="54" t="n"/>
+      <c r="B44" s="55" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="61" t="n"/>
+      <c r="F44" s="61" t="n"/>
+      <c r="G44" s="57">
         <f>IF(AND(D44&lt;&gt;"已完成",D44&lt;&gt;"",E44&lt;&gt;"",E44&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H44" s="39" t="n"/>
-      <c r="I44" s="38" t="n"/>
+      <c r="H44" s="54" t="n"/>
+      <c r="I44" s="55" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="50">
-      <c r="A45" s="39" t="n"/>
-      <c r="B45" s="38" t="n"/>
-      <c r="C45" s="39" t="n"/>
-      <c r="D45" s="39" t="n"/>
-      <c r="E45" s="53" t="n"/>
-      <c r="F45" s="53" t="n"/>
-      <c r="G45" s="37">
+      <c r="A45" s="54" t="n"/>
+      <c r="B45" s="55" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="54" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="61" t="n"/>
+      <c r="G45" s="57">
         <f>IF(AND(D45&lt;&gt;"已完成",D45&lt;&gt;"",E45&lt;&gt;"",E45&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H45" s="39" t="n"/>
-      <c r="I45" s="38" t="n"/>
+      <c r="H45" s="54" t="n"/>
+      <c r="I45" s="55" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="50">
-      <c r="A46" s="39" t="n"/>
-      <c r="B46" s="38" t="n"/>
-      <c r="C46" s="39" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="53" t="n"/>
-      <c r="F46" s="53" t="n"/>
-      <c r="G46" s="37">
+      <c r="A46" s="54" t="n"/>
+      <c r="B46" s="55" t="n"/>
+      <c r="C46" s="54" t="n"/>
+      <c r="D46" s="54" t="n"/>
+      <c r="E46" s="61" t="n"/>
+      <c r="F46" s="61" t="n"/>
+      <c r="G46" s="57">
         <f>IF(AND(D46&lt;&gt;"已完成",D46&lt;&gt;"",E46&lt;&gt;"",E46&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H46" s="39" t="n"/>
-      <c r="I46" s="38" t="n"/>
+      <c r="H46" s="54" t="n"/>
+      <c r="I46" s="55" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="50">
-      <c r="A47" s="39" t="n"/>
-      <c r="B47" s="38" t="n"/>
-      <c r="C47" s="39" t="n"/>
-      <c r="D47" s="39" t="n"/>
-      <c r="E47" s="53" t="n"/>
-      <c r="F47" s="53" t="n"/>
-      <c r="G47" s="37">
+      <c r="A47" s="54" t="n"/>
+      <c r="B47" s="55" t="n"/>
+      <c r="C47" s="54" t="n"/>
+      <c r="D47" s="54" t="n"/>
+      <c r="E47" s="61" t="n"/>
+      <c r="F47" s="61" t="n"/>
+      <c r="G47" s="57">
         <f>IF(AND(D47&lt;&gt;"已完成",D47&lt;&gt;"",E47&lt;&gt;"",E47&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H47" s="39" t="n"/>
-      <c r="I47" s="38" t="n"/>
+      <c r="H47" s="54" t="n"/>
+      <c r="I47" s="55" t="n"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="50">
-      <c r="A48" s="39" t="n"/>
-      <c r="B48" s="38" t="n"/>
-      <c r="C48" s="39" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
-      <c r="G48" s="37">
+      <c r="A48" s="54" t="n"/>
+      <c r="B48" s="55" t="n"/>
+      <c r="C48" s="54" t="n"/>
+      <c r="D48" s="54" t="n"/>
+      <c r="E48" s="61" t="n"/>
+      <c r="F48" s="61" t="n"/>
+      <c r="G48" s="57">
         <f>IF(AND(D48&lt;&gt;"已完成",D48&lt;&gt;"",E48&lt;&gt;"",E48&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H48" s="39" t="n"/>
-      <c r="I48" s="38" t="n"/>
+      <c r="H48" s="54" t="n"/>
+      <c r="I48" s="55" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="50">
-      <c r="A49" s="39" t="n"/>
-      <c r="B49" s="38" t="n"/>
-      <c r="C49" s="39" t="n"/>
-      <c r="D49" s="39" t="n"/>
-      <c r="E49" s="53" t="n"/>
-      <c r="F49" s="53" t="n"/>
-      <c r="G49" s="37">
+      <c r="A49" s="54" t="n"/>
+      <c r="B49" s="55" t="n"/>
+      <c r="C49" s="54" t="n"/>
+      <c r="D49" s="54" t="n"/>
+      <c r="E49" s="61" t="n"/>
+      <c r="F49" s="61" t="n"/>
+      <c r="G49" s="57">
         <f>IF(AND(D49&lt;&gt;"已完成",D49&lt;&gt;"",E49&lt;&gt;"",E49&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H49" s="39" t="n"/>
-      <c r="I49" s="38" t="n"/>
+      <c r="H49" s="54" t="n"/>
+      <c r="I49" s="55" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="50">
-      <c r="A50" s="39" t="n"/>
-      <c r="B50" s="38" t="n"/>
-      <c r="C50" s="39" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="53" t="n"/>
-      <c r="F50" s="53" t="n"/>
-      <c r="G50" s="37">
+      <c r="A50" s="54" t="n"/>
+      <c r="B50" s="55" t="n"/>
+      <c r="C50" s="54" t="n"/>
+      <c r="D50" s="54" t="n"/>
+      <c r="E50" s="61" t="n"/>
+      <c r="F50" s="61" t="n"/>
+      <c r="G50" s="57">
         <f>IF(AND(D50&lt;&gt;"已完成",D50&lt;&gt;"",E50&lt;&gt;"",E50&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H50" s="39" t="n"/>
-      <c r="I50" s="38" t="n"/>
+      <c r="H50" s="54" t="n"/>
+      <c r="I50" s="55" t="n"/>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="50">
-      <c r="A51" s="39" t="n"/>
-      <c r="B51" s="38" t="n"/>
-      <c r="C51" s="39" t="n"/>
-      <c r="D51" s="39" t="n"/>
-      <c r="E51" s="53" t="n"/>
-      <c r="F51" s="53" t="n"/>
-      <c r="G51" s="37">
+      <c r="A51" s="54" t="n"/>
+      <c r="B51" s="55" t="n"/>
+      <c r="C51" s="54" t="n"/>
+      <c r="D51" s="54" t="n"/>
+      <c r="E51" s="61" t="n"/>
+      <c r="F51" s="61" t="n"/>
+      <c r="G51" s="57">
         <f>IF(AND(D51&lt;&gt;"已完成",D51&lt;&gt;"",E51&lt;&gt;"",E51&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H51" s="39" t="n"/>
-      <c r="I51" s="38" t="n"/>
+      <c r="H51" s="54" t="n"/>
+      <c r="I51" s="55" t="n"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="50">
-      <c r="A52" s="39" t="n"/>
-      <c r="B52" s="38" t="n"/>
-      <c r="C52" s="39" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="53" t="n"/>
-      <c r="F52" s="53" t="n"/>
-      <c r="G52" s="37">
+      <c r="A52" s="54" t="n"/>
+      <c r="B52" s="55" t="n"/>
+      <c r="C52" s="54" t="n"/>
+      <c r="D52" s="54" t="n"/>
+      <c r="E52" s="61" t="n"/>
+      <c r="F52" s="61" t="n"/>
+      <c r="G52" s="57">
         <f>IF(AND(D52&lt;&gt;"已完成",D52&lt;&gt;"",E52&lt;&gt;"",E52&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H52" s="39" t="n"/>
-      <c r="I52" s="38" t="n"/>
+      <c r="H52" s="54" t="n"/>
+      <c r="I52" s="55" t="n"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="50">
-      <c r="A53" s="39" t="n"/>
-      <c r="B53" s="38" t="n"/>
-      <c r="C53" s="39" t="n"/>
-      <c r="D53" s="39" t="n"/>
-      <c r="E53" s="53" t="n"/>
-      <c r="F53" s="53" t="n"/>
-      <c r="G53" s="37">
+      <c r="A53" s="54" t="n"/>
+      <c r="B53" s="55" t="n"/>
+      <c r="C53" s="54" t="n"/>
+      <c r="D53" s="54" t="n"/>
+      <c r="E53" s="61" t="n"/>
+      <c r="F53" s="61" t="n"/>
+      <c r="G53" s="57">
         <f>IF(AND(D53&lt;&gt;"已完成",D53&lt;&gt;"",E53&lt;&gt;"",E53&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H53" s="39" t="n"/>
-      <c r="I53" s="38" t="n"/>
+      <c r="H53" s="54" t="n"/>
+      <c r="I53" s="55" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="50">
-      <c r="A54" s="39" t="n"/>
-      <c r="B54" s="38" t="n"/>
-      <c r="C54" s="39" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="53" t="n"/>
-      <c r="F54" s="53" t="n"/>
-      <c r="G54" s="37">
+      <c r="A54" s="54" t="n"/>
+      <c r="B54" s="55" t="n"/>
+      <c r="C54" s="54" t="n"/>
+      <c r="D54" s="54" t="n"/>
+      <c r="E54" s="61" t="n"/>
+      <c r="F54" s="61" t="n"/>
+      <c r="G54" s="57">
         <f>IF(AND(D54&lt;&gt;"已完成",D54&lt;&gt;"",E54&lt;&gt;"",E54&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H54" s="39" t="n"/>
-      <c r="I54" s="38" t="n"/>
+      <c r="H54" s="54" t="n"/>
+      <c r="I54" s="55" t="n"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="50">
-      <c r="A55" s="39" t="n"/>
-      <c r="B55" s="38" t="n"/>
-      <c r="C55" s="39" t="n"/>
-      <c r="D55" s="39" t="n"/>
-      <c r="E55" s="53" t="n"/>
-      <c r="F55" s="53" t="n"/>
-      <c r="G55" s="37">
+      <c r="A55" s="54" t="n"/>
+      <c r="B55" s="55" t="n"/>
+      <c r="C55" s="54" t="n"/>
+      <c r="D55" s="54" t="n"/>
+      <c r="E55" s="61" t="n"/>
+      <c r="F55" s="61" t="n"/>
+      <c r="G55" s="57">
         <f>IF(AND(D55&lt;&gt;"已完成",D55&lt;&gt;"",E55&lt;&gt;"",E55&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H55" s="39" t="n"/>
-      <c r="I55" s="38" t="n"/>
+      <c r="H55" s="54" t="n"/>
+      <c r="I55" s="55" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="50">
-      <c r="A56" s="39" t="n"/>
-      <c r="B56" s="38" t="n"/>
-      <c r="C56" s="39" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="53" t="n"/>
-      <c r="F56" s="53" t="n"/>
-      <c r="G56" s="37">
+      <c r="A56" s="54" t="n"/>
+      <c r="B56" s="55" t="n"/>
+      <c r="C56" s="54" t="n"/>
+      <c r="D56" s="54" t="n"/>
+      <c r="E56" s="61" t="n"/>
+      <c r="F56" s="61" t="n"/>
+      <c r="G56" s="57">
         <f>IF(AND(D56&lt;&gt;"已完成",D56&lt;&gt;"",E56&lt;&gt;"",E56&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H56" s="39" t="n"/>
-      <c r="I56" s="38" t="n"/>
+      <c r="H56" s="54" t="n"/>
+      <c r="I56" s="55" t="n"/>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="50">
-      <c r="A57" s="39" t="n"/>
-      <c r="B57" s="38" t="n"/>
-      <c r="C57" s="39" t="n"/>
-      <c r="D57" s="39" t="n"/>
-      <c r="E57" s="53" t="n"/>
-      <c r="F57" s="53" t="n"/>
-      <c r="G57" s="37">
+      <c r="A57" s="54" t="n"/>
+      <c r="B57" s="55" t="n"/>
+      <c r="C57" s="54" t="n"/>
+      <c r="D57" s="54" t="n"/>
+      <c r="E57" s="61" t="n"/>
+      <c r="F57" s="61" t="n"/>
+      <c r="G57" s="57">
         <f>IF(AND(D57&lt;&gt;"已完成",D57&lt;&gt;"",E57&lt;&gt;"",E57&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H57" s="39" t="n"/>
-      <c r="I57" s="38" t="n"/>
+      <c r="H57" s="54" t="n"/>
+      <c r="I57" s="55" t="n"/>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="50">
-      <c r="A58" s="39" t="n"/>
-      <c r="B58" s="38" t="n"/>
-      <c r="C58" s="39" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="53" t="n"/>
-      <c r="F58" s="53" t="n"/>
-      <c r="G58" s="37">
+      <c r="A58" s="54" t="n"/>
+      <c r="B58" s="55" t="n"/>
+      <c r="C58" s="54" t="n"/>
+      <c r="D58" s="54" t="n"/>
+      <c r="E58" s="61" t="n"/>
+      <c r="F58" s="61" t="n"/>
+      <c r="G58" s="57">
         <f>IF(AND(D58&lt;&gt;"已完成",D58&lt;&gt;"",E58&lt;&gt;"",E58&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H58" s="39" t="n"/>
-      <c r="I58" s="38" t="n"/>
+      <c r="H58" s="54" t="n"/>
+      <c r="I58" s="55" t="n"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="50">
-      <c r="A59" s="39" t="n"/>
-      <c r="B59" s="38" t="n"/>
-      <c r="C59" s="39" t="n"/>
-      <c r="D59" s="39" t="n"/>
-      <c r="E59" s="53" t="n"/>
-      <c r="F59" s="53" t="n"/>
-      <c r="G59" s="37">
+      <c r="A59" s="54" t="n"/>
+      <c r="B59" s="55" t="n"/>
+      <c r="C59" s="54" t="n"/>
+      <c r="D59" s="54" t="n"/>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="61" t="n"/>
+      <c r="G59" s="57">
         <f>IF(AND(D59&lt;&gt;"已完成",D59&lt;&gt;"",E59&lt;&gt;"",E59&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H59" s="39" t="n"/>
-      <c r="I59" s="38" t="n"/>
+      <c r="H59" s="54" t="n"/>
+      <c r="I59" s="55" t="n"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="50">
-      <c r="A60" s="39" t="n"/>
-      <c r="B60" s="38" t="n"/>
-      <c r="C60" s="39" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
-      <c r="G60" s="37">
+      <c r="A60" s="54" t="n"/>
+      <c r="B60" s="55" t="n"/>
+      <c r="C60" s="54" t="n"/>
+      <c r="D60" s="54" t="n"/>
+      <c r="E60" s="61" t="n"/>
+      <c r="F60" s="61" t="n"/>
+      <c r="G60" s="57">
         <f>IF(AND(D60&lt;&gt;"已完成",D60&lt;&gt;"",E60&lt;&gt;"",E60&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H60" s="39" t="n"/>
-      <c r="I60" s="38" t="n"/>
+      <c r="H60" s="54" t="n"/>
+      <c r="I60" s="55" t="n"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="50">
-      <c r="A61" s="39" t="n"/>
-      <c r="B61" s="38" t="n"/>
-      <c r="C61" s="39" t="n"/>
-      <c r="D61" s="39" t="n"/>
-      <c r="E61" s="53" t="n"/>
-      <c r="F61" s="53" t="n"/>
-      <c r="G61" s="37">
+      <c r="A61" s="54" t="n"/>
+      <c r="B61" s="55" t="n"/>
+      <c r="C61" s="54" t="n"/>
+      <c r="D61" s="54" t="n"/>
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="61" t="n"/>
+      <c r="G61" s="57">
         <f>IF(AND(D61&lt;&gt;"已完成",D61&lt;&gt;"",E61&lt;&gt;"",E61&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H61" s="39" t="n"/>
-      <c r="I61" s="38" t="n"/>
+      <c r="H61" s="54" t="n"/>
+      <c r="I61" s="55" t="n"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" s="50">
-      <c r="A62" s="39" t="n"/>
-      <c r="B62" s="38" t="n"/>
-      <c r="C62" s="39" t="n"/>
-      <c r="D62" s="39" t="n"/>
-      <c r="E62" s="53" t="n"/>
-      <c r="F62" s="53" t="n"/>
-      <c r="G62" s="37">
+      <c r="A62" s="54" t="n"/>
+      <c r="B62" s="55" t="n"/>
+      <c r="C62" s="54" t="n"/>
+      <c r="D62" s="54" t="n"/>
+      <c r="E62" s="61" t="n"/>
+      <c r="F62" s="61" t="n"/>
+      <c r="G62" s="57">
         <f>IF(AND(D62&lt;&gt;"已完成",D62&lt;&gt;"",E62&lt;&gt;"",E62&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H62" s="39" t="n"/>
-      <c r="I62" s="38" t="n"/>
+      <c r="H62" s="54" t="n"/>
+      <c r="I62" s="55" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="50">
-      <c r="A63" s="39" t="n"/>
-      <c r="B63" s="38" t="n"/>
-      <c r="C63" s="39" t="n"/>
-      <c r="D63" s="39" t="n"/>
-      <c r="E63" s="53" t="n"/>
-      <c r="F63" s="53" t="n"/>
-      <c r="G63" s="37">
+      <c r="A63" s="54" t="n"/>
+      <c r="B63" s="55" t="n"/>
+      <c r="C63" s="54" t="n"/>
+      <c r="D63" s="54" t="n"/>
+      <c r="E63" s="61" t="n"/>
+      <c r="F63" s="61" t="n"/>
+      <c r="G63" s="57">
         <f>IF(AND(D63&lt;&gt;"已完成",D63&lt;&gt;"",E63&lt;&gt;"",E63&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H63" s="39" t="n"/>
-      <c r="I63" s="38" t="n"/>
+      <c r="H63" s="54" t="n"/>
+      <c r="I63" s="55" t="n"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" s="50">
-      <c r="A64" s="39" t="n"/>
-      <c r="B64" s="38" t="n"/>
-      <c r="C64" s="39" t="n"/>
-      <c r="D64" s="39" t="n"/>
-      <c r="E64" s="53" t="n"/>
-      <c r="F64" s="53" t="n"/>
-      <c r="G64" s="37">
+      <c r="A64" s="54" t="n"/>
+      <c r="B64" s="55" t="n"/>
+      <c r="C64" s="54" t="n"/>
+      <c r="D64" s="54" t="n"/>
+      <c r="E64" s="61" t="n"/>
+      <c r="F64" s="61" t="n"/>
+      <c r="G64" s="57">
         <f>IF(AND(D64&lt;&gt;"已完成",D64&lt;&gt;"",E64&lt;&gt;"",E64&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H64" s="39" t="n"/>
-      <c r="I64" s="38" t="n"/>
+      <c r="H64" s="54" t="n"/>
+      <c r="I64" s="55" t="n"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="50">
-      <c r="A65" s="39" t="n"/>
-      <c r="B65" s="38" t="n"/>
-      <c r="C65" s="39" t="n"/>
-      <c r="D65" s="39" t="n"/>
-      <c r="E65" s="53" t="n"/>
-      <c r="F65" s="53" t="n"/>
-      <c r="G65" s="37">
+      <c r="A65" s="54" t="n"/>
+      <c r="B65" s="55" t="n"/>
+      <c r="C65" s="54" t="n"/>
+      <c r="D65" s="54" t="n"/>
+      <c r="E65" s="61" t="n"/>
+      <c r="F65" s="61" t="n"/>
+      <c r="G65" s="57">
         <f>IF(AND(D65&lt;&gt;"已完成",D65&lt;&gt;"",E65&lt;&gt;"",E65&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H65" s="39" t="n"/>
-      <c r="I65" s="38" t="n"/>
+      <c r="H65" s="54" t="n"/>
+      <c r="I65" s="55" t="n"/>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="50">
-      <c r="A66" s="39" t="n"/>
-      <c r="B66" s="38" t="n"/>
-      <c r="C66" s="39" t="n"/>
-      <c r="D66" s="39" t="n"/>
-      <c r="E66" s="53" t="n"/>
-      <c r="F66" s="53" t="n"/>
-      <c r="G66" s="37">
+      <c r="A66" s="54" t="n"/>
+      <c r="B66" s="55" t="n"/>
+      <c r="C66" s="54" t="n"/>
+      <c r="D66" s="54" t="n"/>
+      <c r="E66" s="61" t="n"/>
+      <c r="F66" s="61" t="n"/>
+      <c r="G66" s="57">
         <f>IF(AND(D66&lt;&gt;"已完成",D66&lt;&gt;"",E66&lt;&gt;"",E66&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H66" s="39" t="n"/>
-      <c r="I66" s="38" t="n"/>
+      <c r="H66" s="54" t="n"/>
+      <c r="I66" s="55" t="n"/>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="50">
-      <c r="A67" s="39" t="n"/>
-      <c r="B67" s="38" t="n"/>
-      <c r="C67" s="39" t="n"/>
-      <c r="D67" s="39" t="n"/>
-      <c r="E67" s="53" t="n"/>
-      <c r="F67" s="53" t="n"/>
-      <c r="G67" s="37">
+      <c r="A67" s="54" t="n"/>
+      <c r="B67" s="55" t="n"/>
+      <c r="C67" s="54" t="n"/>
+      <c r="D67" s="54" t="n"/>
+      <c r="E67" s="61" t="n"/>
+      <c r="F67" s="61" t="n"/>
+      <c r="G67" s="57">
         <f>IF(AND(D67&lt;&gt;"已完成",D67&lt;&gt;"",E67&lt;&gt;"",E67&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H67" s="39" t="n"/>
-      <c r="I67" s="38" t="n"/>
+      <c r="H67" s="54" t="n"/>
+      <c r="I67" s="55" t="n"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" s="50">
-      <c r="A68" s="39" t="n"/>
-      <c r="B68" s="38" t="n"/>
-      <c r="C68" s="39" t="n"/>
-      <c r="D68" s="39" t="n"/>
-      <c r="E68" s="53" t="n"/>
-      <c r="F68" s="53" t="n"/>
-      <c r="G68" s="37">
+      <c r="A68" s="54" t="n"/>
+      <c r="B68" s="55" t="n"/>
+      <c r="C68" s="54" t="n"/>
+      <c r="D68" s="54" t="n"/>
+      <c r="E68" s="61" t="n"/>
+      <c r="F68" s="61" t="n"/>
+      <c r="G68" s="57">
         <f>IF(AND(D68&lt;&gt;"已完成",D68&lt;&gt;"",E68&lt;&gt;"",E68&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H68" s="39" t="n"/>
-      <c r="I68" s="38" t="n"/>
+      <c r="H68" s="54" t="n"/>
+      <c r="I68" s="55" t="n"/>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="50">
-      <c r="A69" s="39" t="n"/>
-      <c r="B69" s="38" t="n"/>
-      <c r="C69" s="39" t="n"/>
-      <c r="D69" s="39" t="n"/>
-      <c r="E69" s="53" t="n"/>
-      <c r="F69" s="53" t="n"/>
-      <c r="G69" s="37">
+      <c r="A69" s="54" t="n"/>
+      <c r="B69" s="55" t="n"/>
+      <c r="C69" s="54" t="n"/>
+      <c r="D69" s="54" t="n"/>
+      <c r="E69" s="61" t="n"/>
+      <c r="F69" s="61" t="n"/>
+      <c r="G69" s="57">
         <f>IF(AND(D69&lt;&gt;"已完成",D69&lt;&gt;"",E69&lt;&gt;"",E69&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H69" s="39" t="n"/>
-      <c r="I69" s="38" t="n"/>
+      <c r="H69" s="54" t="n"/>
+      <c r="I69" s="55" t="n"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="50">
-      <c r="A70" s="39" t="n"/>
-      <c r="B70" s="38" t="n"/>
-      <c r="C70" s="39" t="n"/>
-      <c r="D70" s="39" t="n"/>
-      <c r="E70" s="53" t="n"/>
-      <c r="F70" s="53" t="n"/>
-      <c r="G70" s="37">
+      <c r="A70" s="54" t="n"/>
+      <c r="B70" s="55" t="n"/>
+      <c r="C70" s="54" t="n"/>
+      <c r="D70" s="54" t="n"/>
+      <c r="E70" s="61" t="n"/>
+      <c r="F70" s="61" t="n"/>
+      <c r="G70" s="57">
         <f>IF(AND(D70&lt;&gt;"已完成",D70&lt;&gt;"",E70&lt;&gt;"",E70&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H70" s="39" t="n"/>
-      <c r="I70" s="38" t="n"/>
+      <c r="H70" s="54" t="n"/>
+      <c r="I70" s="55" t="n"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="50">
-      <c r="A71" s="39" t="n"/>
-      <c r="B71" s="38" t="n"/>
-      <c r="C71" s="39" t="n"/>
-      <c r="D71" s="39" t="n"/>
-      <c r="E71" s="53" t="n"/>
-      <c r="F71" s="53" t="n"/>
-      <c r="G71" s="37">
+      <c r="A71" s="54" t="n"/>
+      <c r="B71" s="55" t="n"/>
+      <c r="C71" s="54" t="n"/>
+      <c r="D71" s="54" t="n"/>
+      <c r="E71" s="61" t="n"/>
+      <c r="F71" s="61" t="n"/>
+      <c r="G71" s="57">
         <f>IF(AND(D71&lt;&gt;"已完成",D71&lt;&gt;"",E71&lt;&gt;"",E71&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H71" s="39" t="n"/>
-      <c r="I71" s="38" t="n"/>
+      <c r="H71" s="54" t="n"/>
+      <c r="I71" s="55" t="n"/>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="50">
-      <c r="A72" s="39" t="n"/>
-      <c r="B72" s="38" t="n"/>
-      <c r="C72" s="39" t="n"/>
-      <c r="D72" s="39" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
-      <c r="G72" s="37">
+      <c r="A72" s="54" t="n"/>
+      <c r="B72" s="55" t="n"/>
+      <c r="C72" s="54" t="n"/>
+      <c r="D72" s="54" t="n"/>
+      <c r="E72" s="61" t="n"/>
+      <c r="F72" s="61" t="n"/>
+      <c r="G72" s="57">
         <f>IF(AND(D72&lt;&gt;"已完成",D72&lt;&gt;"",E72&lt;&gt;"",E72&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H72" s="39" t="n"/>
-      <c r="I72" s="38" t="n"/>
+      <c r="H72" s="54" t="n"/>
+      <c r="I72" s="55" t="n"/>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="50">
-      <c r="A73" s="39" t="n"/>
-      <c r="B73" s="38" t="n"/>
-      <c r="C73" s="39" t="n"/>
-      <c r="D73" s="39" t="n"/>
-      <c r="E73" s="53" t="n"/>
-      <c r="F73" s="53" t="n"/>
-      <c r="G73" s="37">
+      <c r="A73" s="54" t="n"/>
+      <c r="B73" s="55" t="n"/>
+      <c r="C73" s="54" t="n"/>
+      <c r="D73" s="54" t="n"/>
+      <c r="E73" s="61" t="n"/>
+      <c r="F73" s="61" t="n"/>
+      <c r="G73" s="57">
         <f>IF(AND(D73&lt;&gt;"已完成",D73&lt;&gt;"",E73&lt;&gt;"",E73&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H73" s="39" t="n"/>
-      <c r="I73" s="38" t="n"/>
+      <c r="H73" s="54" t="n"/>
+      <c r="I73" s="55" t="n"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="50">
-      <c r="A74" s="39" t="n"/>
-      <c r="B74" s="38" t="n"/>
-      <c r="C74" s="39" t="n"/>
-      <c r="D74" s="39" t="n"/>
-      <c r="E74" s="53" t="n"/>
-      <c r="F74" s="53" t="n"/>
-      <c r="G74" s="37">
+      <c r="A74" s="54" t="n"/>
+      <c r="B74" s="55" t="n"/>
+      <c r="C74" s="54" t="n"/>
+      <c r="D74" s="54" t="n"/>
+      <c r="E74" s="61" t="n"/>
+      <c r="F74" s="61" t="n"/>
+      <c r="G74" s="57">
         <f>IF(AND(D74&lt;&gt;"已完成",D74&lt;&gt;"",E74&lt;&gt;"",E74&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H74" s="39" t="n"/>
-      <c r="I74" s="38" t="n"/>
+      <c r="H74" s="54" t="n"/>
+      <c r="I74" s="55" t="n"/>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="50">
-      <c r="A75" s="39" t="n"/>
-      <c r="B75" s="38" t="n"/>
-      <c r="C75" s="39" t="n"/>
-      <c r="D75" s="39" t="n"/>
-      <c r="E75" s="53" t="n"/>
-      <c r="F75" s="53" t="n"/>
-      <c r="G75" s="37">
+      <c r="A75" s="54" t="n"/>
+      <c r="B75" s="55" t="n"/>
+      <c r="C75" s="54" t="n"/>
+      <c r="D75" s="54" t="n"/>
+      <c r="E75" s="61" t="n"/>
+      <c r="F75" s="61" t="n"/>
+      <c r="G75" s="57">
         <f>IF(AND(D75&lt;&gt;"已完成",D75&lt;&gt;"",E75&lt;&gt;"",E75&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H75" s="39" t="n"/>
-      <c r="I75" s="38" t="n"/>
+      <c r="H75" s="54" t="n"/>
+      <c r="I75" s="55" t="n"/>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="50">
-      <c r="A76" s="39" t="n"/>
-      <c r="B76" s="38" t="n"/>
-      <c r="C76" s="39" t="n"/>
-      <c r="D76" s="39" t="n"/>
-      <c r="E76" s="53" t="n"/>
-      <c r="F76" s="53" t="n"/>
-      <c r="G76" s="37">
+      <c r="A76" s="54" t="n"/>
+      <c r="B76" s="55" t="n"/>
+      <c r="C76" s="54" t="n"/>
+      <c r="D76" s="54" t="n"/>
+      <c r="E76" s="61" t="n"/>
+      <c r="F76" s="61" t="n"/>
+      <c r="G76" s="57">
         <f>IF(AND(D76&lt;&gt;"已完成",D76&lt;&gt;"",E76&lt;&gt;"",E76&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H76" s="39" t="n"/>
-      <c r="I76" s="38" t="n"/>
+      <c r="H76" s="54" t="n"/>
+      <c r="I76" s="55" t="n"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="50">
-      <c r="A77" s="39" t="n"/>
-      <c r="B77" s="38" t="n"/>
-      <c r="C77" s="39" t="n"/>
-      <c r="D77" s="39" t="n"/>
-      <c r="E77" s="53" t="n"/>
-      <c r="F77" s="53" t="n"/>
-      <c r="G77" s="37">
+      <c r="A77" s="54" t="n"/>
+      <c r="B77" s="55" t="n"/>
+      <c r="C77" s="54" t="n"/>
+      <c r="D77" s="54" t="n"/>
+      <c r="E77" s="61" t="n"/>
+      <c r="F77" s="61" t="n"/>
+      <c r="G77" s="57">
         <f>IF(AND(D77&lt;&gt;"已完成",D77&lt;&gt;"",E77&lt;&gt;"",E77&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H77" s="39" t="n"/>
-      <c r="I77" s="38" t="n"/>
+      <c r="H77" s="54" t="n"/>
+      <c r="I77" s="55" t="n"/>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="50">
-      <c r="A78" s="39" t="n"/>
-      <c r="B78" s="38" t="n"/>
-      <c r="C78" s="39" t="n"/>
-      <c r="D78" s="39" t="n"/>
-      <c r="E78" s="53" t="n"/>
-      <c r="F78" s="53" t="n"/>
-      <c r="G78" s="37">
+      <c r="A78" s="54" t="n"/>
+      <c r="B78" s="55" t="n"/>
+      <c r="C78" s="54" t="n"/>
+      <c r="D78" s="54" t="n"/>
+      <c r="E78" s="61" t="n"/>
+      <c r="F78" s="61" t="n"/>
+      <c r="G78" s="57">
         <f>IF(AND(D78&lt;&gt;"已完成",D78&lt;&gt;"",E78&lt;&gt;"",E78&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H78" s="39" t="n"/>
-      <c r="I78" s="38" t="n"/>
+      <c r="H78" s="54" t="n"/>
+      <c r="I78" s="55" t="n"/>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="50">
-      <c r="A79" s="39" t="n"/>
-      <c r="B79" s="38" t="n"/>
-      <c r="C79" s="39" t="n"/>
-      <c r="D79" s="39" t="n"/>
-      <c r="E79" s="53" t="n"/>
-      <c r="F79" s="53" t="n"/>
-      <c r="G79" s="37">
+      <c r="A79" s="54" t="n"/>
+      <c r="B79" s="55" t="n"/>
+      <c r="C79" s="54" t="n"/>
+      <c r="D79" s="54" t="n"/>
+      <c r="E79" s="61" t="n"/>
+      <c r="F79" s="61" t="n"/>
+      <c r="G79" s="57">
         <f>IF(AND(D79&lt;&gt;"已完成",D79&lt;&gt;"",E79&lt;&gt;"",E79&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H79" s="39" t="n"/>
-      <c r="I79" s="38" t="n"/>
+      <c r="H79" s="54" t="n"/>
+      <c r="I79" s="55" t="n"/>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="50">
-      <c r="A80" s="39" t="n"/>
-      <c r="B80" s="38" t="n"/>
-      <c r="C80" s="39" t="n"/>
-      <c r="D80" s="39" t="n"/>
-      <c r="E80" s="53" t="n"/>
-      <c r="F80" s="53" t="n"/>
-      <c r="G80" s="37">
+      <c r="A80" s="54" t="n"/>
+      <c r="B80" s="55" t="n"/>
+      <c r="C80" s="54" t="n"/>
+      <c r="D80" s="54" t="n"/>
+      <c r="E80" s="61" t="n"/>
+      <c r="F80" s="61" t="n"/>
+      <c r="G80" s="57">
         <f>IF(AND(D80&lt;&gt;"已完成",D80&lt;&gt;"",E80&lt;&gt;"",E80&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H80" s="39" t="n"/>
-      <c r="I80" s="38" t="n"/>
+      <c r="H80" s="54" t="n"/>
+      <c r="I80" s="55" t="n"/>
     </row>
     <row r="81" ht="16.5" customHeight="1" s="50">
-      <c r="A81" s="39" t="n"/>
-      <c r="B81" s="38" t="n"/>
-      <c r="C81" s="39" t="n"/>
-      <c r="D81" s="39" t="n"/>
-      <c r="E81" s="53" t="n"/>
-      <c r="F81" s="53" t="n"/>
-      <c r="G81" s="37">
+      <c r="A81" s="54" t="n"/>
+      <c r="B81" s="55" t="n"/>
+      <c r="C81" s="54" t="n"/>
+      <c r="D81" s="54" t="n"/>
+      <c r="E81" s="61" t="n"/>
+      <c r="F81" s="61" t="n"/>
+      <c r="G81" s="57">
         <f>IF(AND(D81&lt;&gt;"已完成",D81&lt;&gt;"",E81&lt;&gt;"",E81&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H81" s="39" t="n"/>
-      <c r="I81" s="38" t="n"/>
+      <c r="H81" s="54" t="n"/>
+      <c r="I81" s="55" t="n"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="50">
-      <c r="A82" s="39" t="n"/>
-      <c r="B82" s="38" t="n"/>
-      <c r="C82" s="39" t="n"/>
-      <c r="D82" s="39" t="n"/>
-      <c r="E82" s="53" t="n"/>
-      <c r="F82" s="53" t="n"/>
-      <c r="G82" s="37">
+      <c r="A82" s="54" t="n"/>
+      <c r="B82" s="55" t="n"/>
+      <c r="C82" s="54" t="n"/>
+      <c r="D82" s="54" t="n"/>
+      <c r="E82" s="61" t="n"/>
+      <c r="F82" s="61" t="n"/>
+      <c r="G82" s="57">
         <f>IF(AND(D82&lt;&gt;"已完成",D82&lt;&gt;"",E82&lt;&gt;"",E82&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H82" s="39" t="n"/>
-      <c r="I82" s="38" t="n"/>
+      <c r="H82" s="54" t="n"/>
+      <c r="I82" s="55" t="n"/>
     </row>
     <row r="83" ht="16.5" customHeight="1" s="50">
-      <c r="A83" s="39" t="n"/>
-      <c r="B83" s="38" t="n"/>
-      <c r="C83" s="39" t="n"/>
-      <c r="D83" s="39" t="n"/>
-      <c r="E83" s="53" t="n"/>
-      <c r="F83" s="53" t="n"/>
-      <c r="G83" s="37">
+      <c r="A83" s="54" t="n"/>
+      <c r="B83" s="55" t="n"/>
+      <c r="C83" s="54" t="n"/>
+      <c r="D83" s="54" t="n"/>
+      <c r="E83" s="61" t="n"/>
+      <c r="F83" s="61" t="n"/>
+      <c r="G83" s="57">
         <f>IF(AND(D83&lt;&gt;"已完成",D83&lt;&gt;"",E83&lt;&gt;"",E83&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H83" s="39" t="n"/>
-      <c r="I83" s="38" t="n"/>
+      <c r="H83" s="54" t="n"/>
+      <c r="I83" s="55" t="n"/>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="50">
-      <c r="A84" s="39" t="n"/>
-      <c r="B84" s="38" t="n"/>
-      <c r="C84" s="39" t="n"/>
-      <c r="D84" s="39" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
-      <c r="G84" s="37">
+      <c r="A84" s="54" t="n"/>
+      <c r="B84" s="55" t="n"/>
+      <c r="C84" s="54" t="n"/>
+      <c r="D84" s="54" t="n"/>
+      <c r="E84" s="61" t="n"/>
+      <c r="F84" s="61" t="n"/>
+      <c r="G84" s="57">
         <f>IF(AND(D84&lt;&gt;"已完成",D84&lt;&gt;"",E84&lt;&gt;"",E84&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H84" s="39" t="n"/>
-      <c r="I84" s="38" t="n"/>
+      <c r="H84" s="54" t="n"/>
+      <c r="I84" s="55" t="n"/>
     </row>
     <row r="85" ht="16.5" customHeight="1" s="50">
-      <c r="A85" s="39" t="n"/>
-      <c r="B85" s="38" t="n"/>
-      <c r="C85" s="39" t="n"/>
-      <c r="D85" s="39" t="n"/>
-      <c r="E85" s="53" t="n"/>
-      <c r="F85" s="53" t="n"/>
-      <c r="G85" s="37">
+      <c r="A85" s="54" t="n"/>
+      <c r="B85" s="55" t="n"/>
+      <c r="C85" s="54" t="n"/>
+      <c r="D85" s="54" t="n"/>
+      <c r="E85" s="61" t="n"/>
+      <c r="F85" s="61" t="n"/>
+      <c r="G85" s="57">
         <f>IF(AND(D85&lt;&gt;"已完成",D85&lt;&gt;"",E85&lt;&gt;"",E85&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H85" s="39" t="n"/>
-      <c r="I85" s="38" t="n"/>
+      <c r="H85" s="54" t="n"/>
+      <c r="I85" s="55" t="n"/>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="50">
-      <c r="A86" s="39" t="n"/>
-      <c r="B86" s="38" t="n"/>
-      <c r="C86" s="39" t="n"/>
-      <c r="D86" s="39" t="n"/>
-      <c r="E86" s="53" t="n"/>
-      <c r="F86" s="53" t="n"/>
-      <c r="G86" s="37">
+      <c r="A86" s="54" t="n"/>
+      <c r="B86" s="55" t="n"/>
+      <c r="C86" s="54" t="n"/>
+      <c r="D86" s="54" t="n"/>
+      <c r="E86" s="61" t="n"/>
+      <c r="F86" s="61" t="n"/>
+      <c r="G86" s="57">
         <f>IF(AND(D86&lt;&gt;"已完成",D86&lt;&gt;"",E86&lt;&gt;"",E86&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H86" s="39" t="n"/>
-      <c r="I86" s="38" t="n"/>
+      <c r="H86" s="54" t="n"/>
+      <c r="I86" s="55" t="n"/>
     </row>
     <row r="87" ht="16.5" customHeight="1" s="50">
-      <c r="A87" s="39" t="n"/>
-      <c r="B87" s="38" t="n"/>
-      <c r="C87" s="39" t="n"/>
-      <c r="D87" s="39" t="n"/>
-      <c r="E87" s="53" t="n"/>
-      <c r="F87" s="53" t="n"/>
-      <c r="G87" s="37">
+      <c r="A87" s="54" t="n"/>
+      <c r="B87" s="55" t="n"/>
+      <c r="C87" s="54" t="n"/>
+      <c r="D87" s="54" t="n"/>
+      <c r="E87" s="61" t="n"/>
+      <c r="F87" s="61" t="n"/>
+      <c r="G87" s="57">
         <f>IF(AND(D87&lt;&gt;"已完成",D87&lt;&gt;"",E87&lt;&gt;"",E87&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H87" s="39" t="n"/>
-      <c r="I87" s="38" t="n"/>
+      <c r="H87" s="54" t="n"/>
+      <c r="I87" s="55" t="n"/>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="50">
-      <c r="A88" s="39" t="n"/>
-      <c r="B88" s="38" t="n"/>
-      <c r="C88" s="39" t="n"/>
-      <c r="D88" s="39" t="n"/>
-      <c r="E88" s="53" t="n"/>
-      <c r="F88" s="53" t="n"/>
-      <c r="G88" s="37">
+      <c r="A88" s="54" t="n"/>
+      <c r="B88" s="55" t="n"/>
+      <c r="C88" s="54" t="n"/>
+      <c r="D88" s="54" t="n"/>
+      <c r="E88" s="61" t="n"/>
+      <c r="F88" s="61" t="n"/>
+      <c r="G88" s="57">
         <f>IF(AND(D88&lt;&gt;"已完成",D88&lt;&gt;"",E88&lt;&gt;"",E88&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H88" s="39" t="n"/>
-      <c r="I88" s="38" t="n"/>
+      <c r="H88" s="54" t="n"/>
+      <c r="I88" s="55" t="n"/>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="50">
-      <c r="A89" s="39" t="n"/>
-      <c r="B89" s="38" t="n"/>
-      <c r="C89" s="39" t="n"/>
-      <c r="D89" s="39" t="n"/>
-      <c r="E89" s="53" t="n"/>
-      <c r="F89" s="53" t="n"/>
-      <c r="G89" s="37">
+      <c r="A89" s="54" t="n"/>
+      <c r="B89" s="55" t="n"/>
+      <c r="C89" s="54" t="n"/>
+      <c r="D89" s="54" t="n"/>
+      <c r="E89" s="61" t="n"/>
+      <c r="F89" s="61" t="n"/>
+      <c r="G89" s="57">
         <f>IF(AND(D89&lt;&gt;"已完成",D89&lt;&gt;"",E89&lt;&gt;"",E89&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H89" s="39" t="n"/>
-      <c r="I89" s="38" t="n"/>
+      <c r="H89" s="54" t="n"/>
+      <c r="I89" s="55" t="n"/>
     </row>
     <row r="90" ht="16.5" customHeight="1" s="50">
-      <c r="A90" s="39" t="n"/>
-      <c r="B90" s="38" t="n"/>
-      <c r="C90" s="39" t="n"/>
-      <c r="D90" s="39" t="n"/>
-      <c r="E90" s="53" t="n"/>
-      <c r="F90" s="53" t="n"/>
-      <c r="G90" s="37">
+      <c r="A90" s="54" t="n"/>
+      <c r="B90" s="55" t="n"/>
+      <c r="C90" s="54" t="n"/>
+      <c r="D90" s="54" t="n"/>
+      <c r="E90" s="61" t="n"/>
+      <c r="F90" s="61" t="n"/>
+      <c r="G90" s="57">
         <f>IF(AND(D90&lt;&gt;"已完成",D90&lt;&gt;"",E90&lt;&gt;"",E90&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H90" s="39" t="n"/>
-      <c r="I90" s="38" t="n"/>
+      <c r="H90" s="54" t="n"/>
+      <c r="I90" s="55" t="n"/>
     </row>
     <row r="91" ht="16.5" customHeight="1" s="50">
-      <c r="A91" s="39" t="n"/>
-      <c r="B91" s="38" t="n"/>
-      <c r="C91" s="39" t="n"/>
-      <c r="D91" s="39" t="n"/>
-      <c r="E91" s="53" t="n"/>
-      <c r="F91" s="53" t="n"/>
-      <c r="G91" s="37">
+      <c r="A91" s="54" t="n"/>
+      <c r="B91" s="55" t="n"/>
+      <c r="C91" s="54" t="n"/>
+      <c r="D91" s="54" t="n"/>
+      <c r="E91" s="61" t="n"/>
+      <c r="F91" s="61" t="n"/>
+      <c r="G91" s="57">
         <f>IF(AND(D91&lt;&gt;"已完成",D91&lt;&gt;"",E91&lt;&gt;"",E91&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H91" s="39" t="n"/>
-      <c r="I91" s="38" t="n"/>
+      <c r="H91" s="54" t="n"/>
+      <c r="I91" s="55" t="n"/>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="50">
-      <c r="A92" s="39" t="n"/>
-      <c r="B92" s="38" t="n"/>
-      <c r="C92" s="39" t="n"/>
-      <c r="D92" s="39" t="n"/>
-      <c r="E92" s="53" t="n"/>
-      <c r="F92" s="53" t="n"/>
-      <c r="G92" s="37">
+      <c r="A92" s="54" t="n"/>
+      <c r="B92" s="55" t="n"/>
+      <c r="C92" s="54" t="n"/>
+      <c r="D92" s="54" t="n"/>
+      <c r="E92" s="61" t="n"/>
+      <c r="F92" s="61" t="n"/>
+      <c r="G92" s="57">
         <f>IF(AND(D92&lt;&gt;"已完成",D92&lt;&gt;"",E92&lt;&gt;"",E92&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H92" s="39" t="n"/>
-      <c r="I92" s="38" t="n"/>
+      <c r="H92" s="54" t="n"/>
+      <c r="I92" s="55" t="n"/>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="50">
-      <c r="A93" s="39" t="n"/>
-      <c r="B93" s="38" t="n"/>
-      <c r="C93" s="39" t="n"/>
-      <c r="D93" s="39" t="n"/>
-      <c r="E93" s="53" t="n"/>
-      <c r="F93" s="53" t="n"/>
-      <c r="G93" s="37">
+      <c r="A93" s="54" t="n"/>
+      <c r="B93" s="55" t="n"/>
+      <c r="C93" s="54" t="n"/>
+      <c r="D93" s="54" t="n"/>
+      <c r="E93" s="61" t="n"/>
+      <c r="F93" s="61" t="n"/>
+      <c r="G93" s="57">
         <f>IF(AND(D93&lt;&gt;"已完成",D93&lt;&gt;"",E93&lt;&gt;"",E93&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H93" s="39" t="n"/>
-      <c r="I93" s="38" t="n"/>
+      <c r="H93" s="54" t="n"/>
+      <c r="I93" s="55" t="n"/>
     </row>
     <row r="94" ht="16.5" customHeight="1" s="50">
-      <c r="A94" s="39" t="n"/>
-      <c r="B94" s="38" t="n"/>
-      <c r="C94" s="39" t="n"/>
-      <c r="D94" s="39" t="n"/>
-      <c r="E94" s="53" t="n"/>
-      <c r="F94" s="53" t="n"/>
-      <c r="G94" s="37">
+      <c r="A94" s="54" t="n"/>
+      <c r="B94" s="55" t="n"/>
+      <c r="C94" s="54" t="n"/>
+      <c r="D94" s="54" t="n"/>
+      <c r="E94" s="61" t="n"/>
+      <c r="F94" s="61" t="n"/>
+      <c r="G94" s="57">
         <f>IF(AND(D94&lt;&gt;"已完成",D94&lt;&gt;"",E94&lt;&gt;"",E94&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H94" s="39" t="n"/>
-      <c r="I94" s="38" t="n"/>
+      <c r="H94" s="54" t="n"/>
+      <c r="I94" s="55" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" s="50">
-      <c r="A95" s="39" t="n"/>
-      <c r="B95" s="38" t="n"/>
-      <c r="C95" s="39" t="n"/>
-      <c r="D95" s="39" t="n"/>
-      <c r="E95" s="53" t="n"/>
-      <c r="F95" s="53" t="n"/>
-      <c r="G95" s="37">
+      <c r="A95" s="54" t="n"/>
+      <c r="B95" s="55" t="n"/>
+      <c r="C95" s="54" t="n"/>
+      <c r="D95" s="54" t="n"/>
+      <c r="E95" s="61" t="n"/>
+      <c r="F95" s="61" t="n"/>
+      <c r="G95" s="57">
         <f>IF(AND(D95&lt;&gt;"已完成",D95&lt;&gt;"",E95&lt;&gt;"",E95&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H95" s="39" t="n"/>
-      <c r="I95" s="38" t="n"/>
+      <c r="H95" s="54" t="n"/>
+      <c r="I95" s="55" t="n"/>
     </row>
     <row r="96" ht="16.5" customHeight="1" s="50">
-      <c r="A96" s="39" t="n"/>
-      <c r="B96" s="38" t="n"/>
-      <c r="C96" s="39" t="n"/>
-      <c r="D96" s="39" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
-      <c r="G96" s="37">
+      <c r="A96" s="54" t="n"/>
+      <c r="B96" s="55" t="n"/>
+      <c r="C96" s="54" t="n"/>
+      <c r="D96" s="54" t="n"/>
+      <c r="E96" s="61" t="n"/>
+      <c r="F96" s="61" t="n"/>
+      <c r="G96" s="57">
         <f>IF(AND(D96&lt;&gt;"已完成",D96&lt;&gt;"",E96&lt;&gt;"",E96&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H96" s="39" t="n"/>
-      <c r="I96" s="38" t="n"/>
+      <c r="H96" s="54" t="n"/>
+      <c r="I96" s="55" t="n"/>
     </row>
     <row r="97" ht="16.5" customHeight="1" s="50">
-      <c r="A97" s="39" t="n"/>
-      <c r="B97" s="38" t="n"/>
-      <c r="C97" s="39" t="n"/>
-      <c r="D97" s="39" t="n"/>
-      <c r="E97" s="53" t="n"/>
-      <c r="F97" s="53" t="n"/>
-      <c r="G97" s="37">
+      <c r="A97" s="54" t="n"/>
+      <c r="B97" s="55" t="n"/>
+      <c r="C97" s="54" t="n"/>
+      <c r="D97" s="54" t="n"/>
+      <c r="E97" s="61" t="n"/>
+      <c r="F97" s="61" t="n"/>
+      <c r="G97" s="57">
         <f>IF(AND(D97&lt;&gt;"已完成",D97&lt;&gt;"",E97&lt;&gt;"",E97&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H97" s="39" t="n"/>
-      <c r="I97" s="38" t="n"/>
+      <c r="H97" s="54" t="n"/>
+      <c r="I97" s="55" t="n"/>
     </row>
     <row r="98" ht="16.5" customHeight="1" s="50">
-      <c r="A98" s="39" t="n"/>
-      <c r="B98" s="38" t="n"/>
-      <c r="C98" s="39" t="n"/>
-      <c r="D98" s="39" t="n"/>
-      <c r="E98" s="53" t="n"/>
-      <c r="F98" s="53" t="n"/>
-      <c r="G98" s="37">
+      <c r="A98" s="54" t="n"/>
+      <c r="B98" s="55" t="n"/>
+      <c r="C98" s="54" t="n"/>
+      <c r="D98" s="54" t="n"/>
+      <c r="E98" s="61" t="n"/>
+      <c r="F98" s="61" t="n"/>
+      <c r="G98" s="57">
         <f>IF(AND(D98&lt;&gt;"已完成",D98&lt;&gt;"",E98&lt;&gt;"",E98&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H98" s="39" t="n"/>
-      <c r="I98" s="38" t="n"/>
+      <c r="H98" s="54" t="n"/>
+      <c r="I98" s="55" t="n"/>
     </row>
     <row r="99" ht="16.5" customHeight="1" s="50">
-      <c r="A99" s="39" t="n"/>
-      <c r="B99" s="38" t="n"/>
-      <c r="C99" s="39" t="n"/>
-      <c r="D99" s="39" t="n"/>
-      <c r="E99" s="53" t="n"/>
-      <c r="F99" s="53" t="n"/>
-      <c r="G99" s="37">
+      <c r="A99" s="54" t="n"/>
+      <c r="B99" s="55" t="n"/>
+      <c r="C99" s="54" t="n"/>
+      <c r="D99" s="54" t="n"/>
+      <c r="E99" s="61" t="n"/>
+      <c r="F99" s="61" t="n"/>
+      <c r="G99" s="57">
         <f>IF(AND(D99&lt;&gt;"已完成",D99&lt;&gt;"",E99&lt;&gt;"",E99&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H99" s="39" t="n"/>
-      <c r="I99" s="38" t="n"/>
+      <c r="H99" s="54" t="n"/>
+      <c r="I99" s="55" t="n"/>
     </row>
     <row r="100" ht="16.5" customHeight="1" s="50">
-      <c r="A100" s="39" t="n"/>
-      <c r="B100" s="38" t="n"/>
-      <c r="C100" s="39" t="n"/>
-      <c r="D100" s="39" t="n"/>
-      <c r="E100" s="53" t="n"/>
-      <c r="F100" s="53" t="n"/>
-      <c r="G100" s="37">
+      <c r="A100" s="54" t="n"/>
+      <c r="B100" s="55" t="n"/>
+      <c r="C100" s="54" t="n"/>
+      <c r="D100" s="54" t="n"/>
+      <c r="E100" s="61" t="n"/>
+      <c r="F100" s="61" t="n"/>
+      <c r="G100" s="57">
         <f>IF(AND(D100&lt;&gt;"已完成",D100&lt;&gt;"",E100&lt;&gt;"",E100&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H100" s="39" t="n"/>
-      <c r="I100" s="38" t="n"/>
+      <c r="H100" s="54" t="n"/>
+      <c r="I100" s="55" t="n"/>
     </row>
     <row r="101" ht="16.5" customHeight="1" s="50">
-      <c r="A101" s="39" t="n"/>
-      <c r="B101" s="38" t="n"/>
-      <c r="C101" s="39" t="n"/>
-      <c r="D101" s="39" t="n"/>
-      <c r="E101" s="53" t="n"/>
-      <c r="F101" s="53" t="n"/>
-      <c r="G101" s="37">
+      <c r="A101" s="54" t="n"/>
+      <c r="B101" s="55" t="n"/>
+      <c r="C101" s="54" t="n"/>
+      <c r="D101" s="54" t="n"/>
+      <c r="E101" s="61" t="n"/>
+      <c r="F101" s="61" t="n"/>
+      <c r="G101" s="57">
         <f>IF(AND(D101&lt;&gt;"已完成",D101&lt;&gt;"",E101&lt;&gt;"",E101&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H101" s="39" t="n"/>
-      <c r="I101" s="38" t="n"/>
+      <c r="H101" s="54" t="n"/>
+      <c r="I101" s="55" t="n"/>
     </row>
     <row r="102" ht="16.5" customHeight="1" s="50">
-      <c r="A102" s="39" t="n"/>
-      <c r="B102" s="38" t="n"/>
-      <c r="C102" s="39" t="n"/>
-      <c r="D102" s="39" t="n"/>
-      <c r="E102" s="53" t="n"/>
-      <c r="F102" s="53" t="n"/>
-      <c r="G102" s="37">
+      <c r="A102" s="54" t="n"/>
+      <c r="B102" s="55" t="n"/>
+      <c r="C102" s="54" t="n"/>
+      <c r="D102" s="54" t="n"/>
+      <c r="E102" s="61" t="n"/>
+      <c r="F102" s="61" t="n"/>
+      <c r="G102" s="57">
         <f>IF(AND(D102&lt;&gt;"已完成",D102&lt;&gt;"",E102&lt;&gt;"",E102&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H102" s="39" t="n"/>
-      <c r="I102" s="38" t="n"/>
+      <c r="H102" s="54" t="n"/>
+      <c r="I102" s="55" t="n"/>
     </row>
     <row r="103" ht="16.5" customHeight="1" s="50">
-      <c r="A103" s="39" t="n"/>
-      <c r="B103" s="38" t="n"/>
-      <c r="C103" s="39" t="n"/>
-      <c r="D103" s="39" t="n"/>
-      <c r="E103" s="53" t="n"/>
-      <c r="F103" s="53" t="n"/>
-      <c r="G103" s="37">
+      <c r="A103" s="54" t="n"/>
+      <c r="B103" s="55" t="n"/>
+      <c r="C103" s="54" t="n"/>
+      <c r="D103" s="54" t="n"/>
+      <c r="E103" s="61" t="n"/>
+      <c r="F103" s="61" t="n"/>
+      <c r="G103" s="57">
         <f>IF(AND(D103&lt;&gt;"已完成",D103&lt;&gt;"",E103&lt;&gt;"",E103&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H103" s="39" t="n"/>
-      <c r="I103" s="38" t="n"/>
+      <c r="H103" s="54" t="n"/>
+      <c r="I103" s="55" t="n"/>
     </row>
     <row r="104" ht="16.5" customHeight="1" s="50">
-      <c r="A104" s="39" t="n"/>
-      <c r="B104" s="38" t="n"/>
-      <c r="C104" s="39" t="n"/>
-      <c r="D104" s="39" t="n"/>
-      <c r="E104" s="53" t="n"/>
-      <c r="F104" s="53" t="n"/>
-      <c r="G104" s="37">
+      <c r="A104" s="54" t="n"/>
+      <c r="B104" s="55" t="n"/>
+      <c r="C104" s="54" t="n"/>
+      <c r="D104" s="54" t="n"/>
+      <c r="E104" s="61" t="n"/>
+      <c r="F104" s="61" t="n"/>
+      <c r="G104" s="57">
         <f>IF(AND(D104&lt;&gt;"已完成",D104&lt;&gt;"",E104&lt;&gt;"",E104&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H104" s="39" t="n"/>
-      <c r="I104" s="38" t="n"/>
+      <c r="H104" s="54" t="n"/>
+      <c r="I104" s="55" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" s="50">
-      <c r="A105" s="39" t="n"/>
-      <c r="B105" s="38" t="n"/>
-      <c r="C105" s="39" t="n"/>
-      <c r="D105" s="39" t="n"/>
-      <c r="E105" s="53" t="n"/>
-      <c r="F105" s="53" t="n"/>
-      <c r="G105" s="37">
+      <c r="A105" s="54" t="n"/>
+      <c r="B105" s="55" t="n"/>
+      <c r="C105" s="54" t="n"/>
+      <c r="D105" s="54" t="n"/>
+      <c r="E105" s="61" t="n"/>
+      <c r="F105" s="61" t="n"/>
+      <c r="G105" s="57">
         <f>IF(AND(D105&lt;&gt;"已完成",D105&lt;&gt;"",E105&lt;&gt;"",E105&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H105" s="39" t="n"/>
-      <c r="I105" s="38" t="n"/>
+      <c r="H105" s="54" t="n"/>
+      <c r="I105" s="55" t="n"/>
     </row>
     <row r="106" ht="16.5" customHeight="1" s="50">
-      <c r="A106" s="39" t="n"/>
-      <c r="B106" s="38" t="n"/>
-      <c r="C106" s="39" t="n"/>
-      <c r="D106" s="39" t="n"/>
-      <c r="E106" s="53" t="n"/>
-      <c r="F106" s="53" t="n"/>
-      <c r="G106" s="37">
+      <c r="A106" s="54" t="n"/>
+      <c r="B106" s="55" t="n"/>
+      <c r="C106" s="54" t="n"/>
+      <c r="D106" s="54" t="n"/>
+      <c r="E106" s="61" t="n"/>
+      <c r="F106" s="61" t="n"/>
+      <c r="G106" s="57">
         <f>IF(AND(D106&lt;&gt;"已完成",D106&lt;&gt;"",E106&lt;&gt;"",E106&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H106" s="39" t="n"/>
-      <c r="I106" s="38" t="n"/>
+      <c r="H106" s="54" t="n"/>
+      <c r="I106" s="55" t="n"/>
     </row>
     <row r="107" ht="16.5" customHeight="1" s="50">
-      <c r="A107" s="39" t="n"/>
-      <c r="B107" s="38" t="n"/>
-      <c r="C107" s="39" t="n"/>
-      <c r="D107" s="39" t="n"/>
-      <c r="E107" s="53" t="n"/>
-      <c r="F107" s="53" t="n"/>
-      <c r="G107" s="37">
+      <c r="A107" s="54" t="n"/>
+      <c r="B107" s="55" t="n"/>
+      <c r="C107" s="54" t="n"/>
+      <c r="D107" s="54" t="n"/>
+      <c r="E107" s="61" t="n"/>
+      <c r="F107" s="61" t="n"/>
+      <c r="G107" s="57">
         <f>IF(AND(D107&lt;&gt;"已完成",D107&lt;&gt;"",E107&lt;&gt;"",E107&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H107" s="39" t="n"/>
-      <c r="I107" s="38" t="n"/>
+      <c r="H107" s="54" t="n"/>
+      <c r="I107" s="55" t="n"/>
     </row>
     <row r="108" ht="16.5" customHeight="1" s="50">
-      <c r="A108" s="39" t="n"/>
-      <c r="B108" s="38" t="n"/>
-      <c r="C108" s="39" t="n"/>
-      <c r="D108" s="39" t="n"/>
-      <c r="E108" s="53" t="n"/>
-      <c r="F108" s="53" t="n"/>
-      <c r="G108" s="37">
+      <c r="A108" s="54" t="n"/>
+      <c r="B108" s="55" t="n"/>
+      <c r="C108" s="54" t="n"/>
+      <c r="D108" s="54" t="n"/>
+      <c r="E108" s="61" t="n"/>
+      <c r="F108" s="61" t="n"/>
+      <c r="G108" s="57">
         <f>IF(AND(D108&lt;&gt;"已完成",D108&lt;&gt;"",E108&lt;&gt;"",E108&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H108" s="39" t="n"/>
-      <c r="I108" s="38" t="n"/>
+      <c r="H108" s="54" t="n"/>
+      <c r="I108" s="55" t="n"/>
     </row>
     <row r="109" ht="16.5" customHeight="1" s="50">
-      <c r="A109" s="39" t="n"/>
-      <c r="B109" s="38" t="n"/>
-      <c r="C109" s="39" t="n"/>
-      <c r="D109" s="39" t="n"/>
-      <c r="E109" s="53" t="n"/>
-      <c r="F109" s="53" t="n"/>
-      <c r="G109" s="37">
+      <c r="A109" s="54" t="n"/>
+      <c r="B109" s="55" t="n"/>
+      <c r="C109" s="54" t="n"/>
+      <c r="D109" s="54" t="n"/>
+      <c r="E109" s="61" t="n"/>
+      <c r="F109" s="61" t="n"/>
+      <c r="G109" s="57">
         <f>IF(AND(D109&lt;&gt;"已完成",D109&lt;&gt;"",E109&lt;&gt;"",E109&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H109" s="39" t="n"/>
-      <c r="I109" s="38" t="n"/>
+      <c r="H109" s="54" t="n"/>
+      <c r="I109" s="55" t="n"/>
     </row>
     <row r="110" ht="16.5" customHeight="1" s="50">
-      <c r="A110" s="39" t="n"/>
-      <c r="B110" s="38" t="n"/>
-      <c r="C110" s="39" t="n"/>
-      <c r="D110" s="39" t="n"/>
-      <c r="E110" s="53" t="n"/>
-      <c r="F110" s="53" t="n"/>
-      <c r="G110" s="37">
+      <c r="A110" s="54" t="n"/>
+      <c r="B110" s="55" t="n"/>
+      <c r="C110" s="54" t="n"/>
+      <c r="D110" s="54" t="n"/>
+      <c r="E110" s="61" t="n"/>
+      <c r="F110" s="61" t="n"/>
+      <c r="G110" s="57">
         <f>IF(AND(D110&lt;&gt;"已完成",D110&lt;&gt;"",E110&lt;&gt;"",E110&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H110" s="39" t="n"/>
-      <c r="I110" s="38" t="n"/>
+      <c r="H110" s="54" t="n"/>
+      <c r="I110" s="55" t="n"/>
     </row>
     <row r="111" ht="16.5" customHeight="1" s="50">
-      <c r="A111" s="39" t="n"/>
-      <c r="B111" s="38" t="n"/>
-      <c r="C111" s="39" t="n"/>
-      <c r="D111" s="39" t="n"/>
-      <c r="E111" s="53" t="n"/>
-      <c r="F111" s="53" t="n"/>
-      <c r="G111" s="37">
+      <c r="A111" s="54" t="n"/>
+      <c r="B111" s="55" t="n"/>
+      <c r="C111" s="54" t="n"/>
+      <c r="D111" s="54" t="n"/>
+      <c r="E111" s="61" t="n"/>
+      <c r="F111" s="61" t="n"/>
+      <c r="G111" s="57">
         <f>IF(AND(D111&lt;&gt;"已完成",D111&lt;&gt;"",E111&lt;&gt;"",E111&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H111" s="39" t="n"/>
-      <c r="I111" s="38" t="n"/>
+      <c r="H111" s="54" t="n"/>
+      <c r="I111" s="55" t="n"/>
     </row>
     <row r="112" ht="16.5" customHeight="1" s="50">
-      <c r="A112" s="39" t="n"/>
-      <c r="B112" s="38" t="n"/>
-      <c r="C112" s="39" t="n"/>
-      <c r="D112" s="39" t="n"/>
-      <c r="E112" s="53" t="n"/>
-      <c r="F112" s="53" t="n"/>
-      <c r="G112" s="37">
+      <c r="A112" s="54" t="n"/>
+      <c r="B112" s="55" t="n"/>
+      <c r="C112" s="54" t="n"/>
+      <c r="D112" s="54" t="n"/>
+      <c r="E112" s="61" t="n"/>
+      <c r="F112" s="61" t="n"/>
+      <c r="G112" s="57">
         <f>IF(AND(D112&lt;&gt;"已完成",D112&lt;&gt;"",E112&lt;&gt;"",E112&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H112" s="39" t="n"/>
-      <c r="I112" s="38" t="n"/>
+      <c r="H112" s="54" t="n"/>
+      <c r="I112" s="55" t="n"/>
     </row>
     <row r="113" ht="16.5" customHeight="1" s="50">
-      <c r="A113" s="39" t="n"/>
-      <c r="B113" s="38" t="n"/>
-      <c r="C113" s="39" t="n"/>
-      <c r="D113" s="39" t="n"/>
-      <c r="E113" s="53" t="n"/>
-      <c r="F113" s="53" t="n"/>
-      <c r="G113" s="37">
+      <c r="A113" s="54" t="n"/>
+      <c r="B113" s="55" t="n"/>
+      <c r="C113" s="54" t="n"/>
+      <c r="D113" s="54" t="n"/>
+      <c r="E113" s="61" t="n"/>
+      <c r="F113" s="61" t="n"/>
+      <c r="G113" s="57">
         <f>IF(AND(D113&lt;&gt;"已完成",D113&lt;&gt;"",E113&lt;&gt;"",E113&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H113" s="39" t="n"/>
-      <c r="I113" s="38" t="n"/>
+      <c r="H113" s="54" t="n"/>
+      <c r="I113" s="55" t="n"/>
     </row>
     <row r="114" ht="16.5" customHeight="1" s="50">
-      <c r="A114" s="39" t="n"/>
-      <c r="B114" s="38" t="n"/>
-      <c r="C114" s="39" t="n"/>
-      <c r="D114" s="39" t="n"/>
-      <c r="E114" s="53" t="n"/>
-      <c r="F114" s="53" t="n"/>
-      <c r="G114" s="37">
+      <c r="A114" s="54" t="n"/>
+      <c r="B114" s="55" t="n"/>
+      <c r="C114" s="54" t="n"/>
+      <c r="D114" s="54" t="n"/>
+      <c r="E114" s="61" t="n"/>
+      <c r="F114" s="61" t="n"/>
+      <c r="G114" s="57">
         <f>IF(AND(D114&lt;&gt;"已完成",D114&lt;&gt;"",E114&lt;&gt;"",E114&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H114" s="39" t="n"/>
-      <c r="I114" s="38" t="n"/>
+      <c r="H114" s="54" t="n"/>
+      <c r="I114" s="55" t="n"/>
     </row>
     <row r="115" ht="16.5" customHeight="1" s="50">
-      <c r="A115" s="39" t="n"/>
-      <c r="B115" s="38" t="n"/>
-      <c r="C115" s="39" t="n"/>
-      <c r="D115" s="39" t="n"/>
-      <c r="E115" s="53" t="n"/>
-      <c r="F115" s="53" t="n"/>
-      <c r="G115" s="37">
+      <c r="A115" s="54" t="n"/>
+      <c r="B115" s="55" t="n"/>
+      <c r="C115" s="54" t="n"/>
+      <c r="D115" s="54" t="n"/>
+      <c r="E115" s="61" t="n"/>
+      <c r="F115" s="61" t="n"/>
+      <c r="G115" s="57">
         <f>IF(AND(D115&lt;&gt;"已完成",D115&lt;&gt;"",E115&lt;&gt;"",E115&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H115" s="39" t="n"/>
-      <c r="I115" s="38" t="n"/>
+      <c r="H115" s="54" t="n"/>
+      <c r="I115" s="55" t="n"/>
     </row>
     <row r="116" ht="16.5" customHeight="1" s="50">
-      <c r="A116" s="39" t="n"/>
-      <c r="B116" s="38" t="n"/>
-      <c r="C116" s="39" t="n"/>
-      <c r="D116" s="39" t="n"/>
-      <c r="E116" s="53" t="n"/>
-      <c r="F116" s="53" t="n"/>
-      <c r="G116" s="37">
+      <c r="A116" s="54" t="n"/>
+      <c r="B116" s="55" t="n"/>
+      <c r="C116" s="54" t="n"/>
+      <c r="D116" s="54" t="n"/>
+      <c r="E116" s="61" t="n"/>
+      <c r="F116" s="61" t="n"/>
+      <c r="G116" s="57">
         <f>IF(AND(D116&lt;&gt;"已完成",D116&lt;&gt;"",E116&lt;&gt;"",E116&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H116" s="39" t="n"/>
-      <c r="I116" s="38" t="n"/>
+      <c r="H116" s="54" t="n"/>
+      <c r="I116" s="55" t="n"/>
     </row>
     <row r="117" ht="16.5" customHeight="1" s="50">
-      <c r="A117" s="39" t="n"/>
-      <c r="B117" s="38" t="n"/>
-      <c r="C117" s="39" t="n"/>
-      <c r="D117" s="39" t="n"/>
-      <c r="E117" s="53" t="n"/>
-      <c r="F117" s="53" t="n"/>
-      <c r="G117" s="37">
+      <c r="A117" s="54" t="n"/>
+      <c r="B117" s="55" t="n"/>
+      <c r="C117" s="54" t="n"/>
+      <c r="D117" s="54" t="n"/>
+      <c r="E117" s="61" t="n"/>
+      <c r="F117" s="61" t="n"/>
+      <c r="G117" s="57">
         <f>IF(AND(D117&lt;&gt;"已完成",D117&lt;&gt;"",E117&lt;&gt;"",E117&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H117" s="39" t="n"/>
-      <c r="I117" s="38" t="n"/>
+      <c r="H117" s="54" t="n"/>
+      <c r="I117" s="55" t="n"/>
     </row>
     <row r="118" ht="16.5" customHeight="1" s="50">
-      <c r="A118" s="39" t="n"/>
-      <c r="B118" s="38" t="n"/>
-      <c r="C118" s="39" t="n"/>
-      <c r="D118" s="39" t="n"/>
-      <c r="E118" s="53" t="n"/>
-      <c r="F118" s="53" t="n"/>
-      <c r="G118" s="37">
+      <c r="A118" s="54" t="n"/>
+      <c r="B118" s="55" t="n"/>
+      <c r="C118" s="54" t="n"/>
+      <c r="D118" s="54" t="n"/>
+      <c r="E118" s="61" t="n"/>
+      <c r="F118" s="61" t="n"/>
+      <c r="G118" s="57">
         <f>IF(AND(D118&lt;&gt;"已完成",D118&lt;&gt;"",E118&lt;&gt;"",E118&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H118" s="39" t="n"/>
-      <c r="I118" s="38" t="n"/>
+      <c r="H118" s="54" t="n"/>
+      <c r="I118" s="55" t="n"/>
     </row>
     <row r="119" ht="16.5" customHeight="1" s="50">
-      <c r="A119" s="39" t="n"/>
-      <c r="B119" s="38" t="n"/>
-      <c r="C119" s="39" t="n"/>
-      <c r="D119" s="39" t="n"/>
-      <c r="E119" s="53" t="n"/>
-      <c r="F119" s="53" t="n"/>
-      <c r="G119" s="37">
+      <c r="A119" s="54" t="n"/>
+      <c r="B119" s="55" t="n"/>
+      <c r="C119" s="54" t="n"/>
+      <c r="D119" s="54" t="n"/>
+      <c r="E119" s="61" t="n"/>
+      <c r="F119" s="61" t="n"/>
+      <c r="G119" s="57">
         <f>IF(AND(D119&lt;&gt;"已完成",D119&lt;&gt;"",E119&lt;&gt;"",E119&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H119" s="39" t="n"/>
-      <c r="I119" s="38" t="n"/>
+      <c r="H119" s="54" t="n"/>
+      <c r="I119" s="55" t="n"/>
     </row>
     <row r="120" ht="16.5" customHeight="1" s="50">
-      <c r="A120" s="39" t="n"/>
-      <c r="B120" s="38" t="n"/>
-      <c r="C120" s="39" t="n"/>
-      <c r="D120" s="39" t="n"/>
-      <c r="E120" s="53" t="n"/>
-      <c r="F120" s="53" t="n"/>
-      <c r="G120" s="37">
+      <c r="A120" s="54" t="n"/>
+      <c r="B120" s="55" t="n"/>
+      <c r="C120" s="54" t="n"/>
+      <c r="D120" s="54" t="n"/>
+      <c r="E120" s="61" t="n"/>
+      <c r="F120" s="61" t="n"/>
+      <c r="G120" s="57">
         <f>IF(AND(D120&lt;&gt;"已完成",D120&lt;&gt;"",E120&lt;&gt;"",E120&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H120" s="39" t="n"/>
-      <c r="I120" s="38" t="n"/>
+      <c r="H120" s="54" t="n"/>
+      <c r="I120" s="55" t="n"/>
     </row>
     <row r="121" ht="16.5" customHeight="1" s="50">
-      <c r="A121" s="39" t="n"/>
-      <c r="B121" s="38" t="n"/>
-      <c r="C121" s="39" t="n"/>
-      <c r="D121" s="39" t="n"/>
-      <c r="E121" s="53" t="n"/>
-      <c r="F121" s="53" t="n"/>
-      <c r="G121" s="37">
+      <c r="A121" s="54" t="n"/>
+      <c r="B121" s="55" t="n"/>
+      <c r="C121" s="54" t="n"/>
+      <c r="D121" s="54" t="n"/>
+      <c r="E121" s="61" t="n"/>
+      <c r="F121" s="61" t="n"/>
+      <c r="G121" s="57">
         <f>IF(AND(D121&lt;&gt;"已完成",D121&lt;&gt;"",E121&lt;&gt;"",E121&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H121" s="39" t="n"/>
-      <c r="I121" s="38" t="n"/>
+      <c r="H121" s="54" t="n"/>
+      <c r="I121" s="55" t="n"/>
     </row>
     <row r="122" ht="16.5" customHeight="1" s="50">
-      <c r="A122" s="39" t="n"/>
-      <c r="B122" s="38" t="n"/>
-      <c r="C122" s="39" t="n"/>
-      <c r="D122" s="39" t="n"/>
-      <c r="E122" s="53" t="n"/>
-      <c r="F122" s="53" t="n"/>
-      <c r="G122" s="37">
+      <c r="A122" s="54" t="n"/>
+      <c r="B122" s="55" t="n"/>
+      <c r="C122" s="54" t="n"/>
+      <c r="D122" s="54" t="n"/>
+      <c r="E122" s="61" t="n"/>
+      <c r="F122" s="61" t="n"/>
+      <c r="G122" s="57">
         <f>IF(AND(D122&lt;&gt;"已完成",D122&lt;&gt;"",E122&lt;&gt;"",E122&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H122" s="39" t="n"/>
-      <c r="I122" s="38" t="n"/>
+      <c r="H122" s="54" t="n"/>
+      <c r="I122" s="55" t="n"/>
     </row>
     <row r="123" ht="16.5" customHeight="1" s="50">
-      <c r="A123" s="39" t="n"/>
-      <c r="B123" s="38" t="n"/>
-      <c r="C123" s="39" t="n"/>
-      <c r="D123" s="39" t="n"/>
-      <c r="E123" s="53" t="n"/>
-      <c r="F123" s="53" t="n"/>
-      <c r="G123" s="37">
+      <c r="A123" s="54" t="n"/>
+      <c r="B123" s="55" t="n"/>
+      <c r="C123" s="54" t="n"/>
+      <c r="D123" s="54" t="n"/>
+      <c r="E123" s="61" t="n"/>
+      <c r="F123" s="61" t="n"/>
+      <c r="G123" s="57">
         <f>IF(AND(D123&lt;&gt;"已完成",D123&lt;&gt;"",E123&lt;&gt;"",E123&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H123" s="39" t="n"/>
-      <c r="I123" s="38" t="n"/>
+      <c r="H123" s="54" t="n"/>
+      <c r="I123" s="55" t="n"/>
     </row>
     <row r="124" ht="16.5" customHeight="1" s="50">
-      <c r="A124" s="39" t="n"/>
-      <c r="B124" s="38" t="n"/>
-      <c r="C124" s="39" t="n"/>
-      <c r="D124" s="39" t="n"/>
-      <c r="E124" s="53" t="n"/>
-      <c r="F124" s="53" t="n"/>
-      <c r="G124" s="37">
+      <c r="A124" s="54" t="n"/>
+      <c r="B124" s="55" t="n"/>
+      <c r="C124" s="54" t="n"/>
+      <c r="D124" s="54" t="n"/>
+      <c r="E124" s="61" t="n"/>
+      <c r="F124" s="61" t="n"/>
+      <c r="G124" s="57">
         <f>IF(AND(D124&lt;&gt;"已完成",D124&lt;&gt;"",E124&lt;&gt;"",E124&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H124" s="39" t="n"/>
-      <c r="I124" s="38" t="n"/>
+      <c r="H124" s="54" t="n"/>
+      <c r="I124" s="55" t="n"/>
     </row>
     <row r="125" ht="16.5" customHeight="1" s="50">
-      <c r="A125" s="39" t="n"/>
-      <c r="B125" s="38" t="n"/>
-      <c r="C125" s="39" t="n"/>
-      <c r="D125" s="39" t="n"/>
-      <c r="E125" s="53" t="n"/>
-      <c r="F125" s="53" t="n"/>
-      <c r="G125" s="37">
+      <c r="A125" s="54" t="n"/>
+      <c r="B125" s="55" t="n"/>
+      <c r="C125" s="54" t="n"/>
+      <c r="D125" s="54" t="n"/>
+      <c r="E125" s="61" t="n"/>
+      <c r="F125" s="61" t="n"/>
+      <c r="G125" s="57">
         <f>IF(AND(D125&lt;&gt;"已完成",D125&lt;&gt;"",E125&lt;&gt;"",E125&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H125" s="39" t="n"/>
-      <c r="I125" s="38" t="n"/>
+      <c r="H125" s="54" t="n"/>
+      <c r="I125" s="55" t="n"/>
     </row>
     <row r="126" ht="16.5" customHeight="1" s="50">
-      <c r="A126" s="39" t="n"/>
-      <c r="B126" s="38" t="n"/>
-      <c r="C126" s="39" t="n"/>
-      <c r="D126" s="39" t="n"/>
-      <c r="E126" s="53" t="n"/>
-      <c r="F126" s="53" t="n"/>
-      <c r="G126" s="37">
+      <c r="A126" s="54" t="n"/>
+      <c r="B126" s="55" t="n"/>
+      <c r="C126" s="54" t="n"/>
+      <c r="D126" s="54" t="n"/>
+      <c r="E126" s="61" t="n"/>
+      <c r="F126" s="61" t="n"/>
+      <c r="G126" s="57">
         <f>IF(AND(D126&lt;&gt;"已完成",D126&lt;&gt;"",E126&lt;&gt;"",E126&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H126" s="39" t="n"/>
-      <c r="I126" s="38" t="n"/>
+      <c r="H126" s="54" t="n"/>
+      <c r="I126" s="55" t="n"/>
     </row>
     <row r="127" ht="16.5" customHeight="1" s="50">
-      <c r="A127" s="39" t="n"/>
-      <c r="B127" s="38" t="n"/>
-      <c r="C127" s="39" t="n"/>
-      <c r="D127" s="39" t="n"/>
-      <c r="E127" s="53" t="n"/>
-      <c r="F127" s="53" t="n"/>
-      <c r="G127" s="37">
+      <c r="A127" s="54" t="n"/>
+      <c r="B127" s="55" t="n"/>
+      <c r="C127" s="54" t="n"/>
+      <c r="D127" s="54" t="n"/>
+      <c r="E127" s="61" t="n"/>
+      <c r="F127" s="61" t="n"/>
+      <c r="G127" s="57">
         <f>IF(AND(D127&lt;&gt;"已完成",D127&lt;&gt;"",E127&lt;&gt;"",E127&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H127" s="39" t="n"/>
-      <c r="I127" s="38" t="n"/>
+      <c r="H127" s="54" t="n"/>
+      <c r="I127" s="55" t="n"/>
     </row>
     <row r="128" ht="16.5" customHeight="1" s="50">
-      <c r="A128" s="39" t="n"/>
-      <c r="B128" s="38" t="n"/>
-      <c r="C128" s="39" t="n"/>
-      <c r="D128" s="39" t="n"/>
-      <c r="E128" s="53" t="n"/>
-      <c r="F128" s="53" t="n"/>
-      <c r="G128" s="37">
+      <c r="A128" s="54" t="n"/>
+      <c r="B128" s="55" t="n"/>
+      <c r="C128" s="54" t="n"/>
+      <c r="D128" s="54" t="n"/>
+      <c r="E128" s="61" t="n"/>
+      <c r="F128" s="61" t="n"/>
+      <c r="G128" s="57">
         <f>IF(AND(D128&lt;&gt;"已完成",D128&lt;&gt;"",E128&lt;&gt;"",E128&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H128" s="39" t="n"/>
-      <c r="I128" s="38" t="n"/>
+      <c r="H128" s="54" t="n"/>
+      <c r="I128" s="55" t="n"/>
     </row>
     <row r="129" ht="16.5" customHeight="1" s="50">
-      <c r="A129" s="39" t="n"/>
-      <c r="B129" s="38" t="n"/>
-      <c r="C129" s="39" t="n"/>
-      <c r="D129" s="39" t="n"/>
-      <c r="E129" s="53" t="n"/>
-      <c r="F129" s="53" t="n"/>
-      <c r="G129" s="37">
+      <c r="A129" s="54" t="n"/>
+      <c r="B129" s="55" t="n"/>
+      <c r="C129" s="54" t="n"/>
+      <c r="D129" s="54" t="n"/>
+      <c r="E129" s="61" t="n"/>
+      <c r="F129" s="61" t="n"/>
+      <c r="G129" s="57">
         <f>IF(AND(D129&lt;&gt;"已完成",D129&lt;&gt;"",E129&lt;&gt;"",E129&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H129" s="39" t="n"/>
-      <c r="I129" s="38" t="n"/>
+      <c r="H129" s="54" t="n"/>
+      <c r="I129" s="55" t="n"/>
     </row>
     <row r="130" ht="16.5" customHeight="1" s="50">
-      <c r="A130" s="39" t="n"/>
-      <c r="B130" s="38" t="n"/>
-      <c r="C130" s="39" t="n"/>
-      <c r="D130" s="39" t="n"/>
-      <c r="E130" s="53" t="n"/>
-      <c r="F130" s="53" t="n"/>
-      <c r="G130" s="37">
+      <c r="A130" s="54" t="n"/>
+      <c r="B130" s="55" t="n"/>
+      <c r="C130" s="54" t="n"/>
+      <c r="D130" s="54" t="n"/>
+      <c r="E130" s="61" t="n"/>
+      <c r="F130" s="61" t="n"/>
+      <c r="G130" s="57">
         <f>IF(AND(D130&lt;&gt;"已完成",D130&lt;&gt;"",E130&lt;&gt;"",E130&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H130" s="39" t="n"/>
-      <c r="I130" s="38" t="n"/>
+      <c r="H130" s="54" t="n"/>
+      <c r="I130" s="55" t="n"/>
     </row>
     <row r="131" ht="16.5" customHeight="1" s="50">
-      <c r="A131" s="39" t="n"/>
-      <c r="B131" s="38" t="n"/>
-      <c r="C131" s="39" t="n"/>
-      <c r="D131" s="39" t="n"/>
-      <c r="E131" s="53" t="n"/>
-      <c r="F131" s="53" t="n"/>
-      <c r="G131" s="37">
+      <c r="A131" s="54" t="n"/>
+      <c r="B131" s="55" t="n"/>
+      <c r="C131" s="54" t="n"/>
+      <c r="D131" s="54" t="n"/>
+      <c r="E131" s="61" t="n"/>
+      <c r="F131" s="61" t="n"/>
+      <c r="G131" s="57">
         <f>IF(AND(D131&lt;&gt;"已完成",D131&lt;&gt;"",E131&lt;&gt;"",E131&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H131" s="39" t="n"/>
-      <c r="I131" s="38" t="n"/>
+      <c r="H131" s="54" t="n"/>
+      <c r="I131" s="55" t="n"/>
     </row>
     <row r="132" ht="16.5" customHeight="1" s="50">
-      <c r="A132" s="39" t="n"/>
-      <c r="B132" s="38" t="n"/>
-      <c r="C132" s="39" t="n"/>
-      <c r="D132" s="39" t="n"/>
-      <c r="E132" s="53" t="n"/>
-      <c r="F132" s="53" t="n"/>
-      <c r="G132" s="37">
+      <c r="A132" s="54" t="n"/>
+      <c r="B132" s="55" t="n"/>
+      <c r="C132" s="54" t="n"/>
+      <c r="D132" s="54" t="n"/>
+      <c r="E132" s="61" t="n"/>
+      <c r="F132" s="61" t="n"/>
+      <c r="G132" s="57">
         <f>IF(AND(D132&lt;&gt;"已完成",D132&lt;&gt;"",E132&lt;&gt;"",E132&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H132" s="39" t="n"/>
-      <c r="I132" s="38" t="n"/>
+      <c r="H132" s="54" t="n"/>
+      <c r="I132" s="55" t="n"/>
     </row>
     <row r="133" ht="16.5" customHeight="1" s="50">
-      <c r="A133" s="39" t="n"/>
-      <c r="B133" s="38" t="n"/>
-      <c r="C133" s="39" t="n"/>
-      <c r="D133" s="39" t="n"/>
-      <c r="E133" s="53" t="n"/>
-      <c r="F133" s="53" t="n"/>
-      <c r="G133" s="37">
+      <c r="A133" s="54" t="n"/>
+      <c r="B133" s="55" t="n"/>
+      <c r="C133" s="54" t="n"/>
+      <c r="D133" s="54" t="n"/>
+      <c r="E133" s="61" t="n"/>
+      <c r="F133" s="61" t="n"/>
+      <c r="G133" s="57">
         <f>IF(AND(D133&lt;&gt;"已完成",D133&lt;&gt;"",E133&lt;&gt;"",E133&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H133" s="39" t="n"/>
-      <c r="I133" s="38" t="n"/>
+      <c r="H133" s="54" t="n"/>
+      <c r="I133" s="55" t="n"/>
     </row>
     <row r="134" ht="16.5" customHeight="1" s="50">
-      <c r="A134" s="39" t="n"/>
-      <c r="B134" s="38" t="n"/>
-      <c r="C134" s="39" t="n"/>
-      <c r="D134" s="39" t="n"/>
-      <c r="E134" s="53" t="n"/>
-      <c r="F134" s="53" t="n"/>
-      <c r="G134" s="37">
+      <c r="A134" s="54" t="n"/>
+      <c r="B134" s="55" t="n"/>
+      <c r="C134" s="54" t="n"/>
+      <c r="D134" s="54" t="n"/>
+      <c r="E134" s="61" t="n"/>
+      <c r="F134" s="61" t="n"/>
+      <c r="G134" s="57">
         <f>IF(AND(D134&lt;&gt;"已完成",D134&lt;&gt;"",E134&lt;&gt;"",E134&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H134" s="39" t="n"/>
-      <c r="I134" s="38" t="n"/>
+      <c r="H134" s="54" t="n"/>
+      <c r="I134" s="55" t="n"/>
     </row>
     <row r="135" ht="16.5" customHeight="1" s="50">
-      <c r="A135" s="39" t="n"/>
-      <c r="B135" s="38" t="n"/>
-      <c r="C135" s="39" t="n"/>
-      <c r="D135" s="39" t="n"/>
-      <c r="E135" s="53" t="n"/>
-      <c r="F135" s="53" t="n"/>
-      <c r="G135" s="37">
+      <c r="A135" s="54" t="n"/>
+      <c r="B135" s="55" t="n"/>
+      <c r="C135" s="54" t="n"/>
+      <c r="D135" s="54" t="n"/>
+      <c r="E135" s="61" t="n"/>
+      <c r="F135" s="61" t="n"/>
+      <c r="G135" s="57">
         <f>IF(AND(D135&lt;&gt;"已完成",D135&lt;&gt;"",E135&lt;&gt;"",E135&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H135" s="39" t="n"/>
-      <c r="I135" s="38" t="n"/>
+      <c r="H135" s="54" t="n"/>
+      <c r="I135" s="55" t="n"/>
     </row>
     <row r="136" ht="16.5" customHeight="1" s="50">
-      <c r="A136" s="39" t="n"/>
-      <c r="B136" s="38" t="n"/>
-      <c r="C136" s="39" t="n"/>
-      <c r="D136" s="39" t="n"/>
-      <c r="E136" s="53" t="n"/>
-      <c r="F136" s="53" t="n"/>
-      <c r="G136" s="37">
+      <c r="A136" s="54" t="n"/>
+      <c r="B136" s="55" t="n"/>
+      <c r="C136" s="54" t="n"/>
+      <c r="D136" s="54" t="n"/>
+      <c r="E136" s="61" t="n"/>
+      <c r="F136" s="61" t="n"/>
+      <c r="G136" s="57">
         <f>IF(AND(D136&lt;&gt;"已完成",D136&lt;&gt;"",E136&lt;&gt;"",E136&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H136" s="39" t="n"/>
-      <c r="I136" s="38" t="n"/>
+      <c r="H136" s="54" t="n"/>
+      <c r="I136" s="55" t="n"/>
     </row>
     <row r="137" ht="16.5" customHeight="1" s="50">
-      <c r="A137" s="39" t="n"/>
-      <c r="B137" s="38" t="n"/>
-      <c r="C137" s="39" t="n"/>
-      <c r="D137" s="39" t="n"/>
-      <c r="E137" s="53" t="n"/>
-      <c r="F137" s="53" t="n"/>
-      <c r="G137" s="37">
+      <c r="A137" s="54" t="n"/>
+      <c r="B137" s="55" t="n"/>
+      <c r="C137" s="54" t="n"/>
+      <c r="D137" s="54" t="n"/>
+      <c r="E137" s="61" t="n"/>
+      <c r="F137" s="61" t="n"/>
+      <c r="G137" s="57">
         <f>IF(AND(D137&lt;&gt;"已完成",D137&lt;&gt;"",E137&lt;&gt;"",E137&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H137" s="39" t="n"/>
-      <c r="I137" s="38" t="n"/>
+      <c r="H137" s="54" t="n"/>
+      <c r="I137" s="55" t="n"/>
     </row>
     <row r="138" ht="16.5" customHeight="1" s="50">
-      <c r="A138" s="39" t="n"/>
-      <c r="B138" s="38" t="n"/>
-      <c r="C138" s="39" t="n"/>
-      <c r="D138" s="39" t="n"/>
-      <c r="E138" s="53" t="n"/>
-      <c r="F138" s="53" t="n"/>
-      <c r="G138" s="37">
+      <c r="A138" s="54" t="n"/>
+      <c r="B138" s="55" t="n"/>
+      <c r="C138" s="54" t="n"/>
+      <c r="D138" s="54" t="n"/>
+      <c r="E138" s="61" t="n"/>
+      <c r="F138" s="61" t="n"/>
+      <c r="G138" s="57">
         <f>IF(AND(D138&lt;&gt;"已完成",D138&lt;&gt;"",E138&lt;&gt;"",E138&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H138" s="39" t="n"/>
-      <c r="I138" s="38" t="n"/>
+      <c r="H138" s="54" t="n"/>
+      <c r="I138" s="55" t="n"/>
     </row>
     <row r="139" ht="16.5" customHeight="1" s="50">
-      <c r="A139" s="39" t="n"/>
-      <c r="B139" s="38" t="n"/>
-      <c r="C139" s="39" t="n"/>
-      <c r="D139" s="39" t="n"/>
-      <c r="E139" s="53" t="n"/>
-      <c r="F139" s="53" t="n"/>
-      <c r="G139" s="37">
+      <c r="A139" s="54" t="n"/>
+      <c r="B139" s="55" t="n"/>
+      <c r="C139" s="54" t="n"/>
+      <c r="D139" s="54" t="n"/>
+      <c r="E139" s="61" t="n"/>
+      <c r="F139" s="61" t="n"/>
+      <c r="G139" s="57">
         <f>IF(AND(D139&lt;&gt;"已完成",D139&lt;&gt;"",E139&lt;&gt;"",E139&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H139" s="39" t="n"/>
-      <c r="I139" s="38" t="n"/>
+      <c r="H139" s="54" t="n"/>
+      <c r="I139" s="55" t="n"/>
     </row>
     <row r="140" ht="16.5" customHeight="1" s="50">
-      <c r="A140" s="39" t="n"/>
-      <c r="B140" s="38" t="n"/>
-      <c r="C140" s="39" t="n"/>
-      <c r="D140" s="39" t="n"/>
-      <c r="E140" s="53" t="n"/>
-      <c r="F140" s="53" t="n"/>
-      <c r="G140" s="37">
+      <c r="A140" s="54" t="n"/>
+      <c r="B140" s="55" t="n"/>
+      <c r="C140" s="54" t="n"/>
+      <c r="D140" s="54" t="n"/>
+      <c r="E140" s="61" t="n"/>
+      <c r="F140" s="61" t="n"/>
+      <c r="G140" s="57">
         <f>IF(AND(D140&lt;&gt;"已完成",D140&lt;&gt;"",E140&lt;&gt;"",E140&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H140" s="39" t="n"/>
-      <c r="I140" s="38" t="n"/>
+      <c r="H140" s="54" t="n"/>
+      <c r="I140" s="55" t="n"/>
     </row>
     <row r="141" ht="16.5" customHeight="1" s="50">
-      <c r="A141" s="39" t="n"/>
-      <c r="B141" s="38" t="n"/>
-      <c r="C141" s="39" t="n"/>
-      <c r="D141" s="39" t="n"/>
-      <c r="E141" s="53" t="n"/>
-      <c r="F141" s="53" t="n"/>
-      <c r="G141" s="37">
+      <c r="A141" s="54" t="n"/>
+      <c r="B141" s="55" t="n"/>
+      <c r="C141" s="54" t="n"/>
+      <c r="D141" s="54" t="n"/>
+      <c r="E141" s="61" t="n"/>
+      <c r="F141" s="61" t="n"/>
+      <c r="G141" s="57">
         <f>IF(AND(D141&lt;&gt;"已完成",D141&lt;&gt;"",E141&lt;&gt;"",E141&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H141" s="39" t="n"/>
-      <c r="I141" s="38" t="n"/>
+      <c r="H141" s="54" t="n"/>
+      <c r="I141" s="55" t="n"/>
     </row>
     <row r="142" ht="16.5" customHeight="1" s="50">
-      <c r="A142" s="39" t="n"/>
-      <c r="B142" s="38" t="n"/>
-      <c r="C142" s="39" t="n"/>
-      <c r="D142" s="39" t="n"/>
-      <c r="E142" s="53" t="n"/>
-      <c r="F142" s="53" t="n"/>
-      <c r="G142" s="37">
+      <c r="A142" s="54" t="n"/>
+      <c r="B142" s="55" t="n"/>
+      <c r="C142" s="54" t="n"/>
+      <c r="D142" s="54" t="n"/>
+      <c r="E142" s="61" t="n"/>
+      <c r="F142" s="61" t="n"/>
+      <c r="G142" s="57">
         <f>IF(AND(D142&lt;&gt;"已完成",D142&lt;&gt;"",E142&lt;&gt;"",E142&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H142" s="39" t="n"/>
-      <c r="I142" s="38" t="n"/>
+      <c r="H142" s="54" t="n"/>
+      <c r="I142" s="55" t="n"/>
     </row>
     <row r="143" ht="16.5" customHeight="1" s="50">
-      <c r="A143" s="39" t="n"/>
-      <c r="B143" s="38" t="n"/>
-      <c r="C143" s="39" t="n"/>
-      <c r="D143" s="39" t="n"/>
-      <c r="E143" s="53" t="n"/>
-      <c r="F143" s="53" t="n"/>
-      <c r="G143" s="37">
+      <c r="A143" s="54" t="n"/>
+      <c r="B143" s="55" t="n"/>
+      <c r="C143" s="54" t="n"/>
+      <c r="D143" s="54" t="n"/>
+      <c r="E143" s="61" t="n"/>
+      <c r="F143" s="61" t="n"/>
+      <c r="G143" s="57">
         <f>IF(AND(D143&lt;&gt;"已完成",D143&lt;&gt;"",E143&lt;&gt;"",E143&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H143" s="39" t="n"/>
-      <c r="I143" s="38" t="n"/>
+      <c r="H143" s="54" t="n"/>
+      <c r="I143" s="55" t="n"/>
     </row>
     <row r="144" ht="16.5" customHeight="1" s="50">
-      <c r="A144" s="39" t="n"/>
-      <c r="B144" s="38" t="n"/>
-      <c r="C144" s="39" t="n"/>
-      <c r="D144" s="39" t="n"/>
-      <c r="E144" s="53" t="n"/>
-      <c r="F144" s="53" t="n"/>
-      <c r="G144" s="37">
+      <c r="A144" s="54" t="n"/>
+      <c r="B144" s="55" t="n"/>
+      <c r="C144" s="54" t="n"/>
+      <c r="D144" s="54" t="n"/>
+      <c r="E144" s="61" t="n"/>
+      <c r="F144" s="61" t="n"/>
+      <c r="G144" s="57">
         <f>IF(AND(D144&lt;&gt;"已完成",D144&lt;&gt;"",E144&lt;&gt;"",E144&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H144" s="39" t="n"/>
-      <c r="I144" s="38" t="n"/>
+      <c r="H144" s="54" t="n"/>
+      <c r="I144" s="55" t="n"/>
     </row>
     <row r="145" ht="16.5" customHeight="1" s="50">
-      <c r="A145" s="39" t="n"/>
-      <c r="B145" s="38" t="n"/>
-      <c r="C145" s="39" t="n"/>
-      <c r="D145" s="39" t="n"/>
-      <c r="E145" s="53" t="n"/>
-      <c r="F145" s="53" t="n"/>
-      <c r="G145" s="37">
+      <c r="A145" s="54" t="n"/>
+      <c r="B145" s="55" t="n"/>
+      <c r="C145" s="54" t="n"/>
+      <c r="D145" s="54" t="n"/>
+      <c r="E145" s="61" t="n"/>
+      <c r="F145" s="61" t="n"/>
+      <c r="G145" s="57">
         <f>IF(AND(D145&lt;&gt;"已完成",D145&lt;&gt;"",E145&lt;&gt;"",E145&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H145" s="39" t="n"/>
-      <c r="I145" s="38" t="n"/>
+      <c r="H145" s="54" t="n"/>
+      <c r="I145" s="55" t="n"/>
     </row>
     <row r="146" ht="16.5" customHeight="1" s="50">
-      <c r="A146" s="39" t="n"/>
-      <c r="B146" s="38" t="n"/>
-      <c r="C146" s="39" t="n"/>
-      <c r="D146" s="39" t="n"/>
-      <c r="E146" s="53" t="n"/>
-      <c r="F146" s="53" t="n"/>
-      <c r="G146" s="37">
+      <c r="A146" s="54" t="n"/>
+      <c r="B146" s="55" t="n"/>
+      <c r="C146" s="54" t="n"/>
+      <c r="D146" s="54" t="n"/>
+      <c r="E146" s="61" t="n"/>
+      <c r="F146" s="61" t="n"/>
+      <c r="G146" s="57">
         <f>IF(AND(D146&lt;&gt;"已完成",D146&lt;&gt;"",E146&lt;&gt;"",E146&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H146" s="39" t="n"/>
-      <c r="I146" s="38" t="n"/>
+      <c r="H146" s="54" t="n"/>
+      <c r="I146" s="55" t="n"/>
     </row>
     <row r="147" ht="16.5" customHeight="1" s="50">
-      <c r="A147" s="39" t="n"/>
-      <c r="B147" s="38" t="n"/>
-      <c r="C147" s="39" t="n"/>
-      <c r="D147" s="39" t="n"/>
-      <c r="E147" s="53" t="n"/>
-      <c r="F147" s="53" t="n"/>
-      <c r="G147" s="37">
+      <c r="A147" s="54" t="n"/>
+      <c r="B147" s="55" t="n"/>
+      <c r="C147" s="54" t="n"/>
+      <c r="D147" s="54" t="n"/>
+      <c r="E147" s="61" t="n"/>
+      <c r="F147" s="61" t="n"/>
+      <c r="G147" s="57">
         <f>IF(AND(D147&lt;&gt;"已完成",D147&lt;&gt;"",E147&lt;&gt;"",E147&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H147" s="39" t="n"/>
-      <c r="I147" s="38" t="n"/>
+      <c r="H147" s="54" t="n"/>
+      <c r="I147" s="55" t="n"/>
     </row>
     <row r="148" ht="16.5" customHeight="1" s="50">
-      <c r="A148" s="39" t="n"/>
-      <c r="B148" s="38" t="n"/>
-      <c r="C148" s="39" t="n"/>
-      <c r="D148" s="39" t="n"/>
-      <c r="E148" s="53" t="n"/>
-      <c r="F148" s="53" t="n"/>
-      <c r="G148" s="37">
+      <c r="A148" s="54" t="n"/>
+      <c r="B148" s="55" t="n"/>
+      <c r="C148" s="54" t="n"/>
+      <c r="D148" s="54" t="n"/>
+      <c r="E148" s="61" t="n"/>
+      <c r="F148" s="61" t="n"/>
+      <c r="G148" s="57">
         <f>IF(AND(D148&lt;&gt;"已完成",D148&lt;&gt;"",E148&lt;&gt;"",E148&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H148" s="39" t="n"/>
-      <c r="I148" s="38" t="n"/>
+      <c r="H148" s="54" t="n"/>
+      <c r="I148" s="55" t="n"/>
     </row>
     <row r="149" ht="16.5" customHeight="1" s="50">
-      <c r="A149" s="39" t="n"/>
-      <c r="B149" s="38" t="n"/>
-      <c r="C149" s="39" t="n"/>
-      <c r="D149" s="39" t="n"/>
-      <c r="E149" s="53" t="n"/>
-      <c r="F149" s="53" t="n"/>
-      <c r="G149" s="37">
+      <c r="A149" s="54" t="n"/>
+      <c r="B149" s="55" t="n"/>
+      <c r="C149" s="54" t="n"/>
+      <c r="D149" s="54" t="n"/>
+      <c r="E149" s="61" t="n"/>
+      <c r="F149" s="61" t="n"/>
+      <c r="G149" s="57">
         <f>IF(AND(D149&lt;&gt;"已完成",D149&lt;&gt;"",E149&lt;&gt;"",E149&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H149" s="39" t="n"/>
-      <c r="I149" s="38" t="n"/>
+      <c r="H149" s="54" t="n"/>
+      <c r="I149" s="55" t="n"/>
     </row>
     <row r="150" ht="16.5" customHeight="1" s="50">
-      <c r="A150" s="39" t="n"/>
-      <c r="B150" s="38" t="n"/>
-      <c r="C150" s="39" t="n"/>
-      <c r="D150" s="39" t="n"/>
-      <c r="E150" s="53" t="n"/>
-      <c r="F150" s="53" t="n"/>
-      <c r="G150" s="37">
+      <c r="A150" s="54" t="n"/>
+      <c r="B150" s="55" t="n"/>
+      <c r="C150" s="54" t="n"/>
+      <c r="D150" s="54" t="n"/>
+      <c r="E150" s="61" t="n"/>
+      <c r="F150" s="61" t="n"/>
+      <c r="G150" s="57">
         <f>IF(AND(D150&lt;&gt;"已完成",D150&lt;&gt;"",E150&lt;&gt;"",E150&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H150" s="39" t="n"/>
-      <c r="I150" s="38" t="n"/>
+      <c r="H150" s="54" t="n"/>
+      <c r="I150" s="55" t="n"/>
     </row>
     <row r="151" ht="16.5" customHeight="1" s="50">
-      <c r="A151" s="39" t="n"/>
-      <c r="B151" s="38" t="n"/>
-      <c r="C151" s="39" t="n"/>
-      <c r="D151" s="39" t="n"/>
-      <c r="E151" s="53" t="n"/>
-      <c r="F151" s="53" t="n"/>
-      <c r="G151" s="37">
+      <c r="A151" s="54" t="n"/>
+      <c r="B151" s="55" t="n"/>
+      <c r="C151" s="54" t="n"/>
+      <c r="D151" s="54" t="n"/>
+      <c r="E151" s="61" t="n"/>
+      <c r="F151" s="61" t="n"/>
+      <c r="G151" s="57">
         <f>IF(AND(D151&lt;&gt;"已完成",D151&lt;&gt;"",E151&lt;&gt;"",E151&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H151" s="39" t="n"/>
-      <c r="I151" s="38" t="n"/>
+      <c r="H151" s="54" t="n"/>
+      <c r="I151" s="55" t="n"/>
     </row>
     <row r="152" ht="16.5" customHeight="1" s="50">
-      <c r="A152" s="39" t="n"/>
-      <c r="B152" s="38" t="n"/>
-      <c r="C152" s="39" t="n"/>
-      <c r="D152" s="39" t="n"/>
-      <c r="E152" s="53" t="n"/>
-      <c r="F152" s="53" t="n"/>
-      <c r="G152" s="37">
+      <c r="A152" s="54" t="n"/>
+      <c r="B152" s="55" t="n"/>
+      <c r="C152" s="54" t="n"/>
+      <c r="D152" s="54" t="n"/>
+      <c r="E152" s="61" t="n"/>
+      <c r="F152" s="61" t="n"/>
+      <c r="G152" s="57">
         <f>IF(AND(D152&lt;&gt;"已完成",D152&lt;&gt;"",E152&lt;&gt;"",E152&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H152" s="39" t="n"/>
-      <c r="I152" s="38" t="n"/>
+      <c r="H152" s="54" t="n"/>
+      <c r="I152" s="55" t="n"/>
     </row>
     <row r="153" ht="16.5" customHeight="1" s="50">
-      <c r="A153" s="39" t="n"/>
-      <c r="B153" s="38" t="n"/>
-      <c r="C153" s="39" t="n"/>
-      <c r="D153" s="39" t="n"/>
-      <c r="E153" s="53" t="n"/>
-      <c r="F153" s="53" t="n"/>
-      <c r="G153" s="37">
+      <c r="A153" s="54" t="n"/>
+      <c r="B153" s="55" t="n"/>
+      <c r="C153" s="54" t="n"/>
+      <c r="D153" s="54" t="n"/>
+      <c r="E153" s="61" t="n"/>
+      <c r="F153" s="61" t="n"/>
+      <c r="G153" s="57">
         <f>IF(AND(D153&lt;&gt;"已完成",D153&lt;&gt;"",E153&lt;&gt;"",E153&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H153" s="39" t="n"/>
-      <c r="I153" s="38" t="n"/>
+      <c r="H153" s="54" t="n"/>
+      <c r="I153" s="55" t="n"/>
     </row>
     <row r="154" ht="16.5" customHeight="1" s="50">
-      <c r="A154" s="39" t="n"/>
-      <c r="B154" s="38" t="n"/>
-      <c r="C154" s="39" t="n"/>
-      <c r="D154" s="39" t="n"/>
-      <c r="E154" s="53" t="n"/>
-      <c r="F154" s="53" t="n"/>
-      <c r="G154" s="37">
+      <c r="A154" s="54" t="n"/>
+      <c r="B154" s="55" t="n"/>
+      <c r="C154" s="54" t="n"/>
+      <c r="D154" s="54" t="n"/>
+      <c r="E154" s="61" t="n"/>
+      <c r="F154" s="61" t="n"/>
+      <c r="G154" s="57">
         <f>IF(AND(D154&lt;&gt;"已完成",D154&lt;&gt;"",E154&lt;&gt;"",E154&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H154" s="39" t="n"/>
-      <c r="I154" s="38" t="n"/>
+      <c r="H154" s="54" t="n"/>
+      <c r="I154" s="55" t="n"/>
     </row>
     <row r="155" ht="16.5" customHeight="1" s="50">
-      <c r="A155" s="39" t="n"/>
-      <c r="B155" s="38" t="n"/>
-      <c r="C155" s="39" t="n"/>
-      <c r="D155" s="39" t="n"/>
-      <c r="E155" s="53" t="n"/>
-      <c r="F155" s="53" t="n"/>
-      <c r="G155" s="37">
+      <c r="A155" s="54" t="n"/>
+      <c r="B155" s="55" t="n"/>
+      <c r="C155" s="54" t="n"/>
+      <c r="D155" s="54" t="n"/>
+      <c r="E155" s="61" t="n"/>
+      <c r="F155" s="61" t="n"/>
+      <c r="G155" s="57">
         <f>IF(AND(D155&lt;&gt;"已完成",D155&lt;&gt;"",E155&lt;&gt;"",E155&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H155" s="39" t="n"/>
-      <c r="I155" s="38" t="n"/>
+      <c r="H155" s="54" t="n"/>
+      <c r="I155" s="55" t="n"/>
     </row>
     <row r="156" ht="16.5" customHeight="1" s="50">
-      <c r="A156" s="39" t="n"/>
-      <c r="B156" s="38" t="n"/>
-      <c r="C156" s="39" t="n"/>
-      <c r="D156" s="39" t="n"/>
-      <c r="E156" s="53" t="n"/>
-      <c r="F156" s="53" t="n"/>
-      <c r="G156" s="37">
+      <c r="A156" s="54" t="n"/>
+      <c r="B156" s="55" t="n"/>
+      <c r="C156" s="54" t="n"/>
+      <c r="D156" s="54" t="n"/>
+      <c r="E156" s="61" t="n"/>
+      <c r="F156" s="61" t="n"/>
+      <c r="G156" s="57">
         <f>IF(AND(D156&lt;&gt;"已完成",D156&lt;&gt;"",E156&lt;&gt;"",E156&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H156" s="39" t="n"/>
-      <c r="I156" s="38" t="n"/>
+      <c r="H156" s="54" t="n"/>
+      <c r="I156" s="55" t="n"/>
     </row>
     <row r="157" ht="16.5" customHeight="1" s="50">
-      <c r="A157" s="39" t="n"/>
-      <c r="B157" s="38" t="n"/>
-      <c r="C157" s="39" t="n"/>
-      <c r="D157" s="39" t="n"/>
-      <c r="E157" s="53" t="n"/>
-      <c r="F157" s="53" t="n"/>
-      <c r="G157" s="37">
+      <c r="A157" s="54" t="n"/>
+      <c r="B157" s="55" t="n"/>
+      <c r="C157" s="54" t="n"/>
+      <c r="D157" s="54" t="n"/>
+      <c r="E157" s="61" t="n"/>
+      <c r="F157" s="61" t="n"/>
+      <c r="G157" s="57">
         <f>IF(AND(D157&lt;&gt;"已完成",D157&lt;&gt;"",E157&lt;&gt;"",E157&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H157" s="39" t="n"/>
-      <c r="I157" s="38" t="n"/>
+      <c r="H157" s="54" t="n"/>
+      <c r="I157" s="55" t="n"/>
     </row>
     <row r="158" ht="16.5" customHeight="1" s="50">
-      <c r="A158" s="39" t="n"/>
-      <c r="B158" s="38" t="n"/>
-      <c r="C158" s="39" t="n"/>
-      <c r="D158" s="39" t="n"/>
-      <c r="E158" s="53" t="n"/>
-      <c r="F158" s="53" t="n"/>
-      <c r="G158" s="37">
+      <c r="A158" s="54" t="n"/>
+      <c r="B158" s="55" t="n"/>
+      <c r="C158" s="54" t="n"/>
+      <c r="D158" s="54" t="n"/>
+      <c r="E158" s="61" t="n"/>
+      <c r="F158" s="61" t="n"/>
+      <c r="G158" s="57">
         <f>IF(AND(D158&lt;&gt;"已完成",D158&lt;&gt;"",E158&lt;&gt;"",E158&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H158" s="39" t="n"/>
-      <c r="I158" s="38" t="n"/>
+      <c r="H158" s="54" t="n"/>
+      <c r="I158" s="55" t="n"/>
     </row>
     <row r="159" ht="16.5" customHeight="1" s="50">
-      <c r="A159" s="39" t="n"/>
-      <c r="B159" s="38" t="n"/>
-      <c r="C159" s="39" t="n"/>
-      <c r="D159" s="39" t="n"/>
-      <c r="E159" s="53" t="n"/>
-      <c r="F159" s="53" t="n"/>
-      <c r="G159" s="37">
+      <c r="A159" s="54" t="n"/>
+      <c r="B159" s="55" t="n"/>
+      <c r="C159" s="54" t="n"/>
+      <c r="D159" s="54" t="n"/>
+      <c r="E159" s="61" t="n"/>
+      <c r="F159" s="61" t="n"/>
+      <c r="G159" s="57">
         <f>IF(AND(D159&lt;&gt;"已完成",D159&lt;&gt;"",E159&lt;&gt;"",E159&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H159" s="39" t="n"/>
-      <c r="I159" s="38" t="n"/>
+      <c r="H159" s="54" t="n"/>
+      <c r="I159" s="55" t="n"/>
     </row>
     <row r="160" ht="16.5" customHeight="1" s="50">
-      <c r="A160" s="39" t="n"/>
-      <c r="B160" s="38" t="n"/>
-      <c r="C160" s="39" t="n"/>
-      <c r="D160" s="39" t="n"/>
-      <c r="E160" s="53" t="n"/>
-      <c r="F160" s="53" t="n"/>
-      <c r="G160" s="37">
+      <c r="A160" s="54" t="n"/>
+      <c r="B160" s="55" t="n"/>
+      <c r="C160" s="54" t="n"/>
+      <c r="D160" s="54" t="n"/>
+      <c r="E160" s="61" t="n"/>
+      <c r="F160" s="61" t="n"/>
+      <c r="G160" s="57">
         <f>IF(AND(D160&lt;&gt;"已完成",D160&lt;&gt;"",E160&lt;&gt;"",E160&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H160" s="39" t="n"/>
-      <c r="I160" s="38" t="n"/>
+      <c r="H160" s="54" t="n"/>
+      <c r="I160" s="55" t="n"/>
     </row>
     <row r="161" ht="16.5" customHeight="1" s="50">
-      <c r="A161" s="39" t="n"/>
-      <c r="B161" s="38" t="n"/>
-      <c r="C161" s="39" t="n"/>
-      <c r="D161" s="39" t="n"/>
-      <c r="E161" s="53" t="n"/>
-      <c r="F161" s="53" t="n"/>
-      <c r="G161" s="37">
+      <c r="A161" s="54" t="n"/>
+      <c r="B161" s="55" t="n"/>
+      <c r="C161" s="54" t="n"/>
+      <c r="D161" s="54" t="n"/>
+      <c r="E161" s="61" t="n"/>
+      <c r="F161" s="61" t="n"/>
+      <c r="G161" s="57">
         <f>IF(AND(D161&lt;&gt;"已完成",D161&lt;&gt;"",E161&lt;&gt;"",E161&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H161" s="39" t="n"/>
-      <c r="I161" s="38" t="n"/>
+      <c r="H161" s="54" t="n"/>
+      <c r="I161" s="55" t="n"/>
     </row>
     <row r="162" ht="16.5" customHeight="1" s="50">
-      <c r="A162" s="39" t="n"/>
-      <c r="B162" s="38" t="n"/>
-      <c r="C162" s="39" t="n"/>
-      <c r="D162" s="39" t="n"/>
-      <c r="E162" s="53" t="n"/>
-      <c r="F162" s="53" t="n"/>
-      <c r="G162" s="37">
+      <c r="A162" s="54" t="n"/>
+      <c r="B162" s="55" t="n"/>
+      <c r="C162" s="54" t="n"/>
+      <c r="D162" s="54" t="n"/>
+      <c r="E162" s="61" t="n"/>
+      <c r="F162" s="61" t="n"/>
+      <c r="G162" s="57">
         <f>IF(AND(D162&lt;&gt;"已完成",D162&lt;&gt;"",E162&lt;&gt;"",E162&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H162" s="39" t="n"/>
-      <c r="I162" s="38" t="n"/>
+      <c r="H162" s="54" t="n"/>
+      <c r="I162" s="55" t="n"/>
     </row>
     <row r="163" ht="16.5" customHeight="1" s="50">
-      <c r="A163" s="39" t="n"/>
-      <c r="B163" s="38" t="n"/>
-      <c r="C163" s="39" t="n"/>
-      <c r="D163" s="39" t="n"/>
-      <c r="E163" s="53" t="n"/>
-      <c r="F163" s="53" t="n"/>
-      <c r="G163" s="37">
+      <c r="A163" s="54" t="n"/>
+      <c r="B163" s="55" t="n"/>
+      <c r="C163" s="54" t="n"/>
+      <c r="D163" s="54" t="n"/>
+      <c r="E163" s="61" t="n"/>
+      <c r="F163" s="61" t="n"/>
+      <c r="G163" s="57">
         <f>IF(AND(D163&lt;&gt;"已完成",D163&lt;&gt;"",E163&lt;&gt;"",E163&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H163" s="39" t="n"/>
-      <c r="I163" s="38" t="n"/>
+      <c r="H163" s="54" t="n"/>
+      <c r="I163" s="55" t="n"/>
     </row>
     <row r="164" ht="16.5" customHeight="1" s="50">
-      <c r="A164" s="39" t="n"/>
-      <c r="B164" s="38" t="n"/>
-      <c r="C164" s="39" t="n"/>
-      <c r="D164" s="39" t="n"/>
-      <c r="E164" s="53" t="n"/>
-      <c r="F164" s="53" t="n"/>
-      <c r="G164" s="37">
+      <c r="A164" s="54" t="n"/>
+      <c r="B164" s="55" t="n"/>
+      <c r="C164" s="54" t="n"/>
+      <c r="D164" s="54" t="n"/>
+      <c r="E164" s="61" t="n"/>
+      <c r="F164" s="61" t="n"/>
+      <c r="G164" s="57">
         <f>IF(AND(D164&lt;&gt;"已完成",D164&lt;&gt;"",E164&lt;&gt;"",E164&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H164" s="39" t="n"/>
-      <c r="I164" s="38" t="n"/>
+      <c r="H164" s="54" t="n"/>
+      <c r="I164" s="55" t="n"/>
     </row>
     <row r="165" ht="16.5" customHeight="1" s="50">
-      <c r="A165" s="39" t="n"/>
-      <c r="B165" s="38" t="n"/>
-      <c r="C165" s="39" t="n"/>
-      <c r="D165" s="39" t="n"/>
-      <c r="E165" s="53" t="n"/>
-      <c r="F165" s="53" t="n"/>
-      <c r="G165" s="37">
+      <c r="A165" s="54" t="n"/>
+      <c r="B165" s="55" t="n"/>
+      <c r="C165" s="54" t="n"/>
+      <c r="D165" s="54" t="n"/>
+      <c r="E165" s="61" t="n"/>
+      <c r="F165" s="61" t="n"/>
+      <c r="G165" s="57">
         <f>IF(AND(D165&lt;&gt;"已完成",D165&lt;&gt;"",E165&lt;&gt;"",E165&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H165" s="39" t="n"/>
-      <c r="I165" s="38" t="n"/>
+      <c r="H165" s="54" t="n"/>
+      <c r="I165" s="55" t="n"/>
     </row>
     <row r="166" ht="16.5" customHeight="1" s="50">
-      <c r="A166" s="39" t="n"/>
-      <c r="B166" s="38" t="n"/>
-      <c r="C166" s="39" t="n"/>
-      <c r="D166" s="39" t="n"/>
-      <c r="E166" s="53" t="n"/>
-      <c r="F166" s="53" t="n"/>
-      <c r="G166" s="37">
+      <c r="A166" s="54" t="n"/>
+      <c r="B166" s="55" t="n"/>
+      <c r="C166" s="54" t="n"/>
+      <c r="D166" s="54" t="n"/>
+      <c r="E166" s="61" t="n"/>
+      <c r="F166" s="61" t="n"/>
+      <c r="G166" s="57">
         <f>IF(AND(D166&lt;&gt;"已完成",D166&lt;&gt;"",E166&lt;&gt;"",E166&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H166" s="39" t="n"/>
-      <c r="I166" s="38" t="n"/>
+      <c r="H166" s="54" t="n"/>
+      <c r="I166" s="55" t="n"/>
     </row>
     <row r="167" ht="16.5" customHeight="1" s="50">
-      <c r="A167" s="39" t="n"/>
-      <c r="B167" s="38" t="n"/>
-      <c r="C167" s="39" t="n"/>
-      <c r="D167" s="39" t="n"/>
-      <c r="E167" s="53" t="n"/>
-      <c r="F167" s="53" t="n"/>
-      <c r="G167" s="37">
+      <c r="A167" s="54" t="n"/>
+      <c r="B167" s="55" t="n"/>
+      <c r="C167" s="54" t="n"/>
+      <c r="D167" s="54" t="n"/>
+      <c r="E167" s="61" t="n"/>
+      <c r="F167" s="61" t="n"/>
+      <c r="G167" s="57">
         <f>IF(AND(D167&lt;&gt;"已完成",D167&lt;&gt;"",E167&lt;&gt;"",E167&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H167" s="39" t="n"/>
-      <c r="I167" s="38" t="n"/>
+      <c r="H167" s="54" t="n"/>
+      <c r="I167" s="55" t="n"/>
     </row>
     <row r="168" ht="16.5" customHeight="1" s="50">
-      <c r="A168" s="39" t="n"/>
-      <c r="B168" s="38" t="n"/>
-      <c r="C168" s="39" t="n"/>
-      <c r="D168" s="39" t="n"/>
-      <c r="E168" s="53" t="n"/>
-      <c r="F168" s="53" t="n"/>
-      <c r="G168" s="37">
+      <c r="A168" s="54" t="n"/>
+      <c r="B168" s="55" t="n"/>
+      <c r="C168" s="54" t="n"/>
+      <c r="D168" s="54" t="n"/>
+      <c r="E168" s="61" t="n"/>
+      <c r="F168" s="61" t="n"/>
+      <c r="G168" s="57">
         <f>IF(AND(D168&lt;&gt;"已完成",D168&lt;&gt;"",E168&lt;&gt;"",E168&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H168" s="39" t="n"/>
-      <c r="I168" s="38" t="n"/>
+      <c r="H168" s="54" t="n"/>
+      <c r="I168" s="55" t="n"/>
     </row>
     <row r="169" ht="16.5" customHeight="1" s="50">
-      <c r="A169" s="39" t="n"/>
-      <c r="B169" s="38" t="n"/>
-      <c r="C169" s="39" t="n"/>
-      <c r="D169" s="39" t="n"/>
-      <c r="E169" s="53" t="n"/>
-      <c r="F169" s="53" t="n"/>
-      <c r="G169" s="37">
+      <c r="A169" s="54" t="n"/>
+      <c r="B169" s="55" t="n"/>
+      <c r="C169" s="54" t="n"/>
+      <c r="D169" s="54" t="n"/>
+      <c r="E169" s="61" t="n"/>
+      <c r="F169" s="61" t="n"/>
+      <c r="G169" s="57">
         <f>IF(AND(D169&lt;&gt;"已完成",D169&lt;&gt;"",E169&lt;&gt;"",E169&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H169" s="39" t="n"/>
-      <c r="I169" s="38" t="n"/>
+      <c r="H169" s="54" t="n"/>
+      <c r="I169" s="55" t="n"/>
     </row>
     <row r="170" ht="16.5" customHeight="1" s="50">
-      <c r="A170" s="39" t="n"/>
-      <c r="B170" s="38" t="n"/>
-      <c r="C170" s="39" t="n"/>
-      <c r="D170" s="39" t="n"/>
-      <c r="E170" s="53" t="n"/>
-      <c r="F170" s="53" t="n"/>
-      <c r="G170" s="37">
+      <c r="A170" s="54" t="n"/>
+      <c r="B170" s="55" t="n"/>
+      <c r="C170" s="54" t="n"/>
+      <c r="D170" s="54" t="n"/>
+      <c r="E170" s="61" t="n"/>
+      <c r="F170" s="61" t="n"/>
+      <c r="G170" s="57">
         <f>IF(AND(D170&lt;&gt;"已完成",D170&lt;&gt;"",E170&lt;&gt;"",E170&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H170" s="39" t="n"/>
-      <c r="I170" s="38" t="n"/>
+      <c r="H170" s="54" t="n"/>
+      <c r="I170" s="55" t="n"/>
     </row>
     <row r="171" ht="16.5" customHeight="1" s="50">
-      <c r="A171" s="39" t="n"/>
-      <c r="B171" s="38" t="n"/>
-      <c r="C171" s="39" t="n"/>
-      <c r="D171" s="39" t="n"/>
-      <c r="E171" s="53" t="n"/>
-      <c r="F171" s="53" t="n"/>
-      <c r="G171" s="37">
+      <c r="A171" s="54" t="n"/>
+      <c r="B171" s="55" t="n"/>
+      <c r="C171" s="54" t="n"/>
+      <c r="D171" s="54" t="n"/>
+      <c r="E171" s="61" t="n"/>
+      <c r="F171" s="61" t="n"/>
+      <c r="G171" s="57">
         <f>IF(AND(D171&lt;&gt;"已完成",D171&lt;&gt;"",E171&lt;&gt;"",E171&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H171" s="39" t="n"/>
-      <c r="I171" s="38" t="n"/>
+      <c r="H171" s="54" t="n"/>
+      <c r="I171" s="55" t="n"/>
     </row>
     <row r="172" ht="16.5" customHeight="1" s="50">
-      <c r="A172" s="39" t="n"/>
-      <c r="B172" s="38" t="n"/>
-      <c r="C172" s="39" t="n"/>
-      <c r="D172" s="39" t="n"/>
-      <c r="E172" s="53" t="n"/>
-      <c r="F172" s="53" t="n"/>
-      <c r="G172" s="37">
+      <c r="A172" s="54" t="n"/>
+      <c r="B172" s="55" t="n"/>
+      <c r="C172" s="54" t="n"/>
+      <c r="D172" s="54" t="n"/>
+      <c r="E172" s="61" t="n"/>
+      <c r="F172" s="61" t="n"/>
+      <c r="G172" s="57">
         <f>IF(AND(D172&lt;&gt;"已完成",D172&lt;&gt;"",E172&lt;&gt;"",E172&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H172" s="39" t="n"/>
-      <c r="I172" s="38" t="n"/>
+      <c r="H172" s="54" t="n"/>
+      <c r="I172" s="55" t="n"/>
     </row>
     <row r="173" ht="16.5" customHeight="1" s="50">
-      <c r="A173" s="39" t="n"/>
-      <c r="B173" s="38" t="n"/>
-      <c r="C173" s="39" t="n"/>
-      <c r="D173" s="39" t="n"/>
-      <c r="E173" s="53" t="n"/>
-      <c r="F173" s="53" t="n"/>
-      <c r="G173" s="37">
+      <c r="A173" s="54" t="n"/>
+      <c r="B173" s="55" t="n"/>
+      <c r="C173" s="54" t="n"/>
+      <c r="D173" s="54" t="n"/>
+      <c r="E173" s="61" t="n"/>
+      <c r="F173" s="61" t="n"/>
+      <c r="G173" s="57">
         <f>IF(AND(D173&lt;&gt;"已完成",D173&lt;&gt;"",E173&lt;&gt;"",E173&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H173" s="39" t="n"/>
-      <c r="I173" s="38" t="n"/>
+      <c r="H173" s="54" t="n"/>
+      <c r="I173" s="55" t="n"/>
     </row>
     <row r="174" ht="16.5" customHeight="1" s="50">
-      <c r="A174" s="39" t="n"/>
-      <c r="B174" s="38" t="n"/>
-      <c r="C174" s="39" t="n"/>
-      <c r="D174" s="39" t="n"/>
-      <c r="E174" s="53" t="n"/>
-      <c r="F174" s="53" t="n"/>
-      <c r="G174" s="37">
+      <c r="A174" s="54" t="n"/>
+      <c r="B174" s="55" t="n"/>
+      <c r="C174" s="54" t="n"/>
+      <c r="D174" s="54" t="n"/>
+      <c r="E174" s="61" t="n"/>
+      <c r="F174" s="61" t="n"/>
+      <c r="G174" s="57">
         <f>IF(AND(D174&lt;&gt;"已完成",D174&lt;&gt;"",E174&lt;&gt;"",E174&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H174" s="39" t="n"/>
-      <c r="I174" s="38" t="n"/>
+      <c r="H174" s="54" t="n"/>
+      <c r="I174" s="55" t="n"/>
     </row>
     <row r="175" ht="16.5" customHeight="1" s="50">
-      <c r="A175" s="39" t="n"/>
-      <c r="B175" s="38" t="n"/>
-      <c r="C175" s="39" t="n"/>
-      <c r="D175" s="39" t="n"/>
-      <c r="E175" s="53" t="n"/>
-      <c r="F175" s="53" t="n"/>
-      <c r="G175" s="37">
+      <c r="A175" s="54" t="n"/>
+      <c r="B175" s="55" t="n"/>
+      <c r="C175" s="54" t="n"/>
+      <c r="D175" s="54" t="n"/>
+      <c r="E175" s="61" t="n"/>
+      <c r="F175" s="61" t="n"/>
+      <c r="G175" s="57">
         <f>IF(AND(D175&lt;&gt;"已完成",D175&lt;&gt;"",E175&lt;&gt;"",E175&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H175" s="39" t="n"/>
-      <c r="I175" s="38" t="n"/>
+      <c r="H175" s="54" t="n"/>
+      <c r="I175" s="55" t="n"/>
     </row>
     <row r="176" ht="16.5" customHeight="1" s="50">
-      <c r="A176" s="39" t="n"/>
-      <c r="B176" s="38" t="n"/>
-      <c r="C176" s="39" t="n"/>
-      <c r="D176" s="39" t="n"/>
-      <c r="E176" s="53" t="n"/>
-      <c r="F176" s="53" t="n"/>
-      <c r="G176" s="37">
+      <c r="A176" s="54" t="n"/>
+      <c r="B176" s="55" t="n"/>
+      <c r="C176" s="54" t="n"/>
+      <c r="D176" s="54" t="n"/>
+      <c r="E176" s="61" t="n"/>
+      <c r="F176" s="61" t="n"/>
+      <c r="G176" s="57">
         <f>IF(AND(D176&lt;&gt;"已完成",D176&lt;&gt;"",E176&lt;&gt;"",E176&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H176" s="39" t="n"/>
-      <c r="I176" s="38" t="n"/>
+      <c r="H176" s="54" t="n"/>
+      <c r="I176" s="55" t="n"/>
     </row>
     <row r="177" ht="16.5" customHeight="1" s="50">
-      <c r="A177" s="39" t="n"/>
-      <c r="B177" s="38" t="n"/>
-      <c r="C177" s="39" t="n"/>
-      <c r="D177" s="39" t="n"/>
-      <c r="E177" s="53" t="n"/>
-      <c r="F177" s="53" t="n"/>
-      <c r="G177" s="37">
+      <c r="A177" s="54" t="n"/>
+      <c r="B177" s="55" t="n"/>
+      <c r="C177" s="54" t="n"/>
+      <c r="D177" s="54" t="n"/>
+      <c r="E177" s="61" t="n"/>
+      <c r="F177" s="61" t="n"/>
+      <c r="G177" s="57">
         <f>IF(AND(D177&lt;&gt;"已完成",D177&lt;&gt;"",E177&lt;&gt;"",E177&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H177" s="39" t="n"/>
-      <c r="I177" s="38" t="n"/>
+      <c r="H177" s="54" t="n"/>
+      <c r="I177" s="55" t="n"/>
     </row>
     <row r="178" ht="16.5" customHeight="1" s="50">
-      <c r="A178" s="39" t="n"/>
-      <c r="B178" s="38" t="n"/>
-      <c r="C178" s="39" t="n"/>
-      <c r="D178" s="39" t="n"/>
-      <c r="E178" s="53" t="n"/>
-      <c r="F178" s="53" t="n"/>
-      <c r="G178" s="37">
+      <c r="A178" s="54" t="n"/>
+      <c r="B178" s="55" t="n"/>
+      <c r="C178" s="54" t="n"/>
+      <c r="D178" s="54" t="n"/>
+      <c r="E178" s="61" t="n"/>
+      <c r="F178" s="61" t="n"/>
+      <c r="G178" s="57">
         <f>IF(AND(D178&lt;&gt;"已完成",D178&lt;&gt;"",E178&lt;&gt;"",E178&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H178" s="39" t="n"/>
-      <c r="I178" s="38" t="n"/>
+      <c r="H178" s="54" t="n"/>
+      <c r="I178" s="55" t="n"/>
     </row>
     <row r="179" ht="16.5" customHeight="1" s="50">
-      <c r="A179" s="39" t="n"/>
-      <c r="B179" s="38" t="n"/>
-      <c r="C179" s="39" t="n"/>
-      <c r="D179" s="39" t="n"/>
-      <c r="E179" s="53" t="n"/>
-      <c r="F179" s="53" t="n"/>
-      <c r="G179" s="37">
+      <c r="A179" s="54" t="n"/>
+      <c r="B179" s="55" t="n"/>
+      <c r="C179" s="54" t="n"/>
+      <c r="D179" s="54" t="n"/>
+      <c r="E179" s="61" t="n"/>
+      <c r="F179" s="61" t="n"/>
+      <c r="G179" s="57">
         <f>IF(AND(D179&lt;&gt;"已完成",D179&lt;&gt;"",E179&lt;&gt;"",E179&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H179" s="39" t="n"/>
-      <c r="I179" s="38" t="n"/>
+      <c r="H179" s="54" t="n"/>
+      <c r="I179" s="55" t="n"/>
     </row>
     <row r="180" ht="16.5" customHeight="1" s="50">
-      <c r="A180" s="39" t="n"/>
-      <c r="B180" s="38" t="n"/>
-      <c r="C180" s="39" t="n"/>
-      <c r="D180" s="39" t="n"/>
-      <c r="E180" s="53" t="n"/>
-      <c r="F180" s="53" t="n"/>
-      <c r="G180" s="37">
+      <c r="A180" s="54" t="n"/>
+      <c r="B180" s="55" t="n"/>
+      <c r="C180" s="54" t="n"/>
+      <c r="D180" s="54" t="n"/>
+      <c r="E180" s="61" t="n"/>
+      <c r="F180" s="61" t="n"/>
+      <c r="G180" s="57">
         <f>IF(AND(D180&lt;&gt;"已完成",D180&lt;&gt;"",E180&lt;&gt;"",E180&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H180" s="39" t="n"/>
-      <c r="I180" s="38" t="n"/>
+      <c r="H180" s="54" t="n"/>
+      <c r="I180" s="55" t="n"/>
     </row>
     <row r="181" ht="16.5" customHeight="1" s="50">
-      <c r="A181" s="39" t="n"/>
-      <c r="B181" s="38" t="n"/>
-      <c r="C181" s="39" t="n"/>
-      <c r="D181" s="39" t="n"/>
-      <c r="E181" s="53" t="n"/>
-      <c r="F181" s="53" t="n"/>
-      <c r="G181" s="37">
+      <c r="A181" s="54" t="n"/>
+      <c r="B181" s="55" t="n"/>
+      <c r="C181" s="54" t="n"/>
+      <c r="D181" s="54" t="n"/>
+      <c r="E181" s="61" t="n"/>
+      <c r="F181" s="61" t="n"/>
+      <c r="G181" s="57">
         <f>IF(AND(D181&lt;&gt;"已完成",D181&lt;&gt;"",E181&lt;&gt;"",E181&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H181" s="39" t="n"/>
-      <c r="I181" s="38" t="n"/>
+      <c r="H181" s="54" t="n"/>
+      <c r="I181" s="55" t="n"/>
     </row>
     <row r="182" ht="16.5" customHeight="1" s="50">
-      <c r="A182" s="39" t="n"/>
-      <c r="B182" s="38" t="n"/>
-      <c r="C182" s="39" t="n"/>
-      <c r="D182" s="39" t="n"/>
-      <c r="E182" s="53" t="n"/>
-      <c r="F182" s="53" t="n"/>
-      <c r="G182" s="37">
+      <c r="A182" s="54" t="n"/>
+      <c r="B182" s="55" t="n"/>
+      <c r="C182" s="54" t="n"/>
+      <c r="D182" s="54" t="n"/>
+      <c r="E182" s="61" t="n"/>
+      <c r="F182" s="61" t="n"/>
+      <c r="G182" s="57">
         <f>IF(AND(D182&lt;&gt;"已完成",D182&lt;&gt;"",E182&lt;&gt;"",E182&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H182" s="39" t="n"/>
-      <c r="I182" s="38" t="n"/>
+      <c r="H182" s="54" t="n"/>
+      <c r="I182" s="55" t="n"/>
     </row>
     <row r="183" ht="16.5" customHeight="1" s="50">
-      <c r="A183" s="39" t="n"/>
-      <c r="B183" s="38" t="n"/>
-      <c r="C183" s="39" t="n"/>
-      <c r="D183" s="39" t="n"/>
-      <c r="E183" s="53" t="n"/>
-      <c r="F183" s="53" t="n"/>
-      <c r="G183" s="37">
+      <c r="A183" s="54" t="n"/>
+      <c r="B183" s="55" t="n"/>
+      <c r="C183" s="54" t="n"/>
+      <c r="D183" s="54" t="n"/>
+      <c r="E183" s="61" t="n"/>
+      <c r="F183" s="61" t="n"/>
+      <c r="G183" s="57">
         <f>IF(AND(D183&lt;&gt;"已完成",D183&lt;&gt;"",E183&lt;&gt;"",E183&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H183" s="39" t="n"/>
-      <c r="I183" s="38" t="n"/>
+      <c r="H183" s="54" t="n"/>
+      <c r="I183" s="55" t="n"/>
     </row>
     <row r="184" ht="16.5" customHeight="1" s="50">
-      <c r="A184" s="39" t="n"/>
-      <c r="B184" s="38" t="n"/>
-      <c r="C184" s="39" t="n"/>
-      <c r="D184" s="39" t="n"/>
-      <c r="E184" s="53" t="n"/>
-      <c r="F184" s="53" t="n"/>
-      <c r="G184" s="37">
+      <c r="A184" s="54" t="n"/>
+      <c r="B184" s="55" t="n"/>
+      <c r="C184" s="54" t="n"/>
+      <c r="D184" s="54" t="n"/>
+      <c r="E184" s="61" t="n"/>
+      <c r="F184" s="61" t="n"/>
+      <c r="G184" s="57">
         <f>IF(AND(D184&lt;&gt;"已完成",D184&lt;&gt;"",E184&lt;&gt;"",E184&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H184" s="39" t="n"/>
-      <c r="I184" s="38" t="n"/>
+      <c r="H184" s="54" t="n"/>
+      <c r="I184" s="55" t="n"/>
     </row>
     <row r="185" ht="16.5" customHeight="1" s="50">
-      <c r="A185" s="39" t="n"/>
-      <c r="B185" s="38" t="n"/>
-      <c r="C185" s="39" t="n"/>
-      <c r="D185" s="39" t="n"/>
-      <c r="E185" s="53" t="n"/>
-      <c r="F185" s="53" t="n"/>
-      <c r="G185" s="37">
+      <c r="A185" s="54" t="n"/>
+      <c r="B185" s="55" t="n"/>
+      <c r="C185" s="54" t="n"/>
+      <c r="D185" s="54" t="n"/>
+      <c r="E185" s="61" t="n"/>
+      <c r="F185" s="61" t="n"/>
+      <c r="G185" s="57">
         <f>IF(AND(D185&lt;&gt;"已完成",D185&lt;&gt;"",E185&lt;&gt;"",E185&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H185" s="39" t="n"/>
-      <c r="I185" s="38" t="n"/>
+      <c r="H185" s="54" t="n"/>
+      <c r="I185" s="55" t="n"/>
     </row>
     <row r="186" ht="16.5" customHeight="1" s="50">
-      <c r="A186" s="39" t="n"/>
-      <c r="B186" s="38" t="n"/>
-      <c r="C186" s="39" t="n"/>
-      <c r="D186" s="39" t="n"/>
-      <c r="E186" s="53" t="n"/>
-      <c r="F186" s="53" t="n"/>
-      <c r="G186" s="37">
+      <c r="A186" s="54" t="n"/>
+      <c r="B186" s="55" t="n"/>
+      <c r="C186" s="54" t="n"/>
+      <c r="D186" s="54" t="n"/>
+      <c r="E186" s="61" t="n"/>
+      <c r="F186" s="61" t="n"/>
+      <c r="G186" s="57">
         <f>IF(AND(D186&lt;&gt;"已完成",D186&lt;&gt;"",E186&lt;&gt;"",E186&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H186" s="39" t="n"/>
-      <c r="I186" s="38" t="n"/>
+      <c r="H186" s="54" t="n"/>
+      <c r="I186" s="55" t="n"/>
     </row>
     <row r="187" ht="16.5" customHeight="1" s="50">
-      <c r="A187" s="39" t="n"/>
-      <c r="B187" s="38" t="n"/>
-      <c r="C187" s="39" t="n"/>
-      <c r="D187" s="39" t="n"/>
-      <c r="E187" s="53" t="n"/>
-      <c r="F187" s="53" t="n"/>
-      <c r="G187" s="37">
+      <c r="A187" s="54" t="n"/>
+      <c r="B187" s="55" t="n"/>
+      <c r="C187" s="54" t="n"/>
+      <c r="D187" s="54" t="n"/>
+      <c r="E187" s="61" t="n"/>
+      <c r="F187" s="61" t="n"/>
+      <c r="G187" s="57">
         <f>IF(AND(D187&lt;&gt;"已完成",D187&lt;&gt;"",E187&lt;&gt;"",E187&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H187" s="39" t="n"/>
-      <c r="I187" s="38" t="n"/>
+      <c r="H187" s="54" t="n"/>
+      <c r="I187" s="55" t="n"/>
     </row>
     <row r="188" ht="16.5" customHeight="1" s="50">
-      <c r="A188" s="39" t="n"/>
-      <c r="B188" s="38" t="n"/>
-      <c r="C188" s="39" t="n"/>
-      <c r="D188" s="39" t="n"/>
-      <c r="E188" s="53" t="n"/>
-      <c r="F188" s="53" t="n"/>
-      <c r="G188" s="37">
+      <c r="A188" s="54" t="n"/>
+      <c r="B188" s="55" t="n"/>
+      <c r="C188" s="54" t="n"/>
+      <c r="D188" s="54" t="n"/>
+      <c r="E188" s="61" t="n"/>
+      <c r="F188" s="61" t="n"/>
+      <c r="G188" s="57">
         <f>IF(AND(D188&lt;&gt;"已完成",D188&lt;&gt;"",E188&lt;&gt;"",E188&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H188" s="39" t="n"/>
-      <c r="I188" s="38" t="n"/>
+      <c r="H188" s="54" t="n"/>
+      <c r="I188" s="55" t="n"/>
     </row>
     <row r="189" ht="16.5" customHeight="1" s="50">
-      <c r="A189" s="39" t="n"/>
-      <c r="B189" s="38" t="n"/>
-      <c r="C189" s="39" t="n"/>
-      <c r="D189" s="39" t="n"/>
-      <c r="E189" s="53" t="n"/>
-      <c r="F189" s="53" t="n"/>
-      <c r="G189" s="37">
+      <c r="A189" s="54" t="n"/>
+      <c r="B189" s="55" t="n"/>
+      <c r="C189" s="54" t="n"/>
+      <c r="D189" s="54" t="n"/>
+      <c r="E189" s="61" t="n"/>
+      <c r="F189" s="61" t="n"/>
+      <c r="G189" s="57">
         <f>IF(AND(D189&lt;&gt;"已完成",D189&lt;&gt;"",E189&lt;&gt;"",E189&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H189" s="39" t="n"/>
-      <c r="I189" s="38" t="n"/>
+      <c r="H189" s="54" t="n"/>
+      <c r="I189" s="55" t="n"/>
     </row>
     <row r="190" ht="16.5" customHeight="1" s="50">
-      <c r="A190" s="39" t="n"/>
-      <c r="B190" s="38" t="n"/>
-      <c r="C190" s="39" t="n"/>
-      <c r="D190" s="39" t="n"/>
-      <c r="E190" s="53" t="n"/>
-      <c r="F190" s="53" t="n"/>
-      <c r="G190" s="37">
+      <c r="A190" s="54" t="n"/>
+      <c r="B190" s="55" t="n"/>
+      <c r="C190" s="54" t="n"/>
+      <c r="D190" s="54" t="n"/>
+      <c r="E190" s="61" t="n"/>
+      <c r="F190" s="61" t="n"/>
+      <c r="G190" s="57">
         <f>IF(AND(D190&lt;&gt;"已完成",D190&lt;&gt;"",E190&lt;&gt;"",E190&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H190" s="39" t="n"/>
-      <c r="I190" s="38" t="n"/>
+      <c r="H190" s="54" t="n"/>
+      <c r="I190" s="55" t="n"/>
     </row>
     <row r="191" ht="16.5" customHeight="1" s="50">
-      <c r="A191" s="39" t="n"/>
-      <c r="B191" s="38" t="n"/>
-      <c r="C191" s="39" t="n"/>
-      <c r="D191" s="39" t="n"/>
-      <c r="E191" s="53" t="n"/>
-      <c r="F191" s="53" t="n"/>
-      <c r="G191" s="37">
+      <c r="A191" s="54" t="n"/>
+      <c r="B191" s="55" t="n"/>
+      <c r="C191" s="54" t="n"/>
+      <c r="D191" s="54" t="n"/>
+      <c r="E191" s="61" t="n"/>
+      <c r="F191" s="61" t="n"/>
+      <c r="G191" s="57">
         <f>IF(AND(D191&lt;&gt;"已完成",D191&lt;&gt;"",E191&lt;&gt;"",E191&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H191" s="39" t="n"/>
-      <c r="I191" s="38" t="n"/>
+      <c r="H191" s="54" t="n"/>
+      <c r="I191" s="55" t="n"/>
     </row>
     <row r="192" ht="16.5" customHeight="1" s="50">
-      <c r="A192" s="39" t="n"/>
-      <c r="B192" s="38" t="n"/>
-      <c r="C192" s="39" t="n"/>
-      <c r="D192" s="39" t="n"/>
-      <c r="E192" s="53" t="n"/>
-      <c r="F192" s="53" t="n"/>
-      <c r="G192" s="37">
+      <c r="A192" s="54" t="n"/>
+      <c r="B192" s="55" t="n"/>
+      <c r="C192" s="54" t="n"/>
+      <c r="D192" s="54" t="n"/>
+      <c r="E192" s="61" t="n"/>
+      <c r="F192" s="61" t="n"/>
+      <c r="G192" s="57">
         <f>IF(AND(D192&lt;&gt;"已完成",D192&lt;&gt;"",E192&lt;&gt;"",E192&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H192" s="39" t="n"/>
-      <c r="I192" s="38" t="n"/>
+      <c r="H192" s="54" t="n"/>
+      <c r="I192" s="55" t="n"/>
     </row>
     <row r="193" ht="16.5" customHeight="1" s="50">
-      <c r="A193" s="39" t="n"/>
-      <c r="B193" s="38" t="n"/>
-      <c r="C193" s="39" t="n"/>
-      <c r="D193" s="39" t="n"/>
-      <c r="E193" s="53" t="n"/>
-      <c r="F193" s="53" t="n"/>
-      <c r="G193" s="37">
+      <c r="A193" s="54" t="n"/>
+      <c r="B193" s="55" t="n"/>
+      <c r="C193" s="54" t="n"/>
+      <c r="D193" s="54" t="n"/>
+      <c r="E193" s="61" t="n"/>
+      <c r="F193" s="61" t="n"/>
+      <c r="G193" s="57">
         <f>IF(AND(D193&lt;&gt;"已完成",D193&lt;&gt;"",E193&lt;&gt;"",E193&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H193" s="39" t="n"/>
-      <c r="I193" s="38" t="n"/>
+      <c r="H193" s="54" t="n"/>
+      <c r="I193" s="55" t="n"/>
     </row>
     <row r="194" ht="16.5" customHeight="1" s="50">
-      <c r="A194" s="39" t="n"/>
-      <c r="B194" s="38" t="n"/>
-      <c r="C194" s="39" t="n"/>
-      <c r="D194" s="39" t="n"/>
-      <c r="E194" s="53" t="n"/>
-      <c r="F194" s="53" t="n"/>
-      <c r="G194" s="37">
+      <c r="A194" s="54" t="n"/>
+      <c r="B194" s="55" t="n"/>
+      <c r="C194" s="54" t="n"/>
+      <c r="D194" s="54" t="n"/>
+      <c r="E194" s="61" t="n"/>
+      <c r="F194" s="61" t="n"/>
+      <c r="G194" s="57">
         <f>IF(AND(D194&lt;&gt;"已完成",D194&lt;&gt;"",E194&lt;&gt;"",E194&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H194" s="39" t="n"/>
-      <c r="I194" s="38" t="n"/>
+      <c r="H194" s="54" t="n"/>
+      <c r="I194" s="55" t="n"/>
     </row>
     <row r="195" ht="16.5" customHeight="1" s="50">
-      <c r="A195" s="39" t="n"/>
-      <c r="B195" s="38" t="n"/>
-      <c r="C195" s="39" t="n"/>
-      <c r="D195" s="39" t="n"/>
-      <c r="E195" s="53" t="n"/>
-      <c r="F195" s="53" t="n"/>
-      <c r="G195" s="37">
+      <c r="A195" s="54" t="n"/>
+      <c r="B195" s="55" t="n"/>
+      <c r="C195" s="54" t="n"/>
+      <c r="D195" s="54" t="n"/>
+      <c r="E195" s="61" t="n"/>
+      <c r="F195" s="61" t="n"/>
+      <c r="G195" s="57">
         <f>IF(AND(D195&lt;&gt;"已完成",D195&lt;&gt;"",E195&lt;&gt;"",E195&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H195" s="39" t="n"/>
-      <c r="I195" s="38" t="n"/>
+      <c r="H195" s="54" t="n"/>
+      <c r="I195" s="55" t="n"/>
     </row>
     <row r="196" ht="16.5" customHeight="1" s="50">
-      <c r="A196" s="39" t="n"/>
-      <c r="B196" s="38" t="n"/>
-      <c r="C196" s="39" t="n"/>
-      <c r="D196" s="39" t="n"/>
-      <c r="E196" s="53" t="n"/>
-      <c r="F196" s="53" t="n"/>
-      <c r="G196" s="37">
+      <c r="A196" s="54" t="n"/>
+      <c r="B196" s="55" t="n"/>
+      <c r="C196" s="54" t="n"/>
+      <c r="D196" s="54" t="n"/>
+      <c r="E196" s="61" t="n"/>
+      <c r="F196" s="61" t="n"/>
+      <c r="G196" s="57">
         <f>IF(AND(D196&lt;&gt;"已完成",D196&lt;&gt;"",E196&lt;&gt;"",E196&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H196" s="39" t="n"/>
-      <c r="I196" s="38" t="n"/>
+      <c r="H196" s="54" t="n"/>
+      <c r="I196" s="55" t="n"/>
     </row>
     <row r="197" ht="16.5" customHeight="1" s="50">
-      <c r="A197" s="39" t="n"/>
-      <c r="B197" s="38" t="n"/>
-      <c r="C197" s="39" t="n"/>
-      <c r="D197" s="39" t="n"/>
-      <c r="E197" s="53" t="n"/>
-      <c r="F197" s="53" t="n"/>
-      <c r="G197" s="37">
+      <c r="A197" s="54" t="n"/>
+      <c r="B197" s="55" t="n"/>
+      <c r="C197" s="54" t="n"/>
+      <c r="D197" s="54" t="n"/>
+      <c r="E197" s="61" t="n"/>
+      <c r="F197" s="61" t="n"/>
+      <c r="G197" s="57">
         <f>IF(AND(D197&lt;&gt;"已完成",D197&lt;&gt;"",E197&lt;&gt;"",E197&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H197" s="39" t="n"/>
-      <c r="I197" s="38" t="n"/>
+      <c r="H197" s="54" t="n"/>
+      <c r="I197" s="55" t="n"/>
     </row>
     <row r="198" ht="16.5" customHeight="1" s="50">
-      <c r="A198" s="39" t="n"/>
-      <c r="B198" s="38" t="n"/>
-      <c r="C198" s="39" t="n"/>
-      <c r="D198" s="39" t="n"/>
-      <c r="E198" s="53" t="n"/>
-      <c r="F198" s="53" t="n"/>
-      <c r="G198" s="37">
+      <c r="A198" s="54" t="n"/>
+      <c r="B198" s="55" t="n"/>
+      <c r="C198" s="54" t="n"/>
+      <c r="D198" s="54" t="n"/>
+      <c r="E198" s="61" t="n"/>
+      <c r="F198" s="61" t="n"/>
+      <c r="G198" s="57">
         <f>IF(AND(D198&lt;&gt;"已完成",D198&lt;&gt;"",E198&lt;&gt;"",E198&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H198" s="39" t="n"/>
-      <c r="I198" s="38" t="n"/>
+      <c r="H198" s="54" t="n"/>
+      <c r="I198" s="55" t="n"/>
     </row>
     <row r="199" ht="16.5" customHeight="1" s="50">
-      <c r="A199" s="39" t="n"/>
-      <c r="B199" s="38" t="n"/>
-      <c r="C199" s="39" t="n"/>
-      <c r="D199" s="39" t="n"/>
-      <c r="E199" s="53" t="n"/>
-      <c r="F199" s="53" t="n"/>
-      <c r="G199" s="37">
+      <c r="A199" s="54" t="n"/>
+      <c r="B199" s="55" t="n"/>
+      <c r="C199" s="54" t="n"/>
+      <c r="D199" s="54" t="n"/>
+      <c r="E199" s="61" t="n"/>
+      <c r="F199" s="61" t="n"/>
+      <c r="G199" s="57">
         <f>IF(AND(D199&lt;&gt;"已完成",D199&lt;&gt;"",E199&lt;&gt;"",E199&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H199" s="39" t="n"/>
-      <c r="I199" s="38" t="n"/>
+      <c r="H199" s="54" t="n"/>
+      <c r="I199" s="55" t="n"/>
     </row>
     <row r="200" ht="16.5" customHeight="1" s="50">
-      <c r="A200" s="39" t="n"/>
-      <c r="B200" s="38" t="n"/>
-      <c r="C200" s="39" t="n"/>
-      <c r="D200" s="39" t="n"/>
-      <c r="E200" s="53" t="n"/>
-      <c r="F200" s="53" t="n"/>
-      <c r="G200" s="37">
+      <c r="A200" s="54" t="n"/>
+      <c r="B200" s="55" t="n"/>
+      <c r="C200" s="54" t="n"/>
+      <c r="D200" s="54" t="n"/>
+      <c r="E200" s="61" t="n"/>
+      <c r="F200" s="61" t="n"/>
+      <c r="G200" s="57">
         <f>IF(AND(D200&lt;&gt;"已完成",D200&lt;&gt;"",E200&lt;&gt;"",E200&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H200" s="39" t="n"/>
-      <c r="I200" s="38" t="n"/>
+      <c r="H200" s="54" t="n"/>
+      <c r="I200" s="55" t="n"/>
     </row>
     <row r="201" ht="16.5" customHeight="1" s="50">
-      <c r="A201" s="39" t="n"/>
-      <c r="B201" s="38" t="n"/>
-      <c r="C201" s="39" t="n"/>
-      <c r="D201" s="39" t="n"/>
-      <c r="E201" s="53" t="n"/>
-      <c r="F201" s="53" t="n"/>
-      <c r="G201" s="37">
+      <c r="A201" s="54" t="n"/>
+      <c r="B201" s="55" t="n"/>
+      <c r="C201" s="54" t="n"/>
+      <c r="D201" s="54" t="n"/>
+      <c r="E201" s="61" t="n"/>
+      <c r="F201" s="61" t="n"/>
+      <c r="G201" s="57">
         <f>IF(AND(D201&lt;&gt;"已完成",D201&lt;&gt;"",E201&lt;&gt;"",E201&lt;TODAY()),"⚠️延期","")</f>
         <v/>
       </c>
-      <c r="H201" s="39" t="n"/>
-      <c r="I201" s="38" t="n"/>
+      <c r="H201" s="54" t="n"/>
+      <c r="I201" s="55" t="n"/>
     </row>
     <row r="202" ht="16.5" customHeight="1" s="50">
       <c r="A202" s="54" t="n"/>
       <c r="B202" s="55" t="n"/>
       <c r="C202" s="54" t="n"/>
       <c r="D202" s="54" t="n"/>
-      <c r="E202" s="56" t="n"/>
-      <c r="F202" s="56" t="n"/>
+      <c r="E202" s="61" t="n"/>
+      <c r="F202" s="61" t="n"/>
       <c r="G202" s="57">
         <f>IF(AND(D202&lt;&gt;"已完成",D202&lt;&gt;"",E202&lt;&gt;"",E202&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5530,8 +5541,8 @@
       <c r="B203" s="55" t="n"/>
       <c r="C203" s="54" t="n"/>
       <c r="D203" s="54" t="n"/>
-      <c r="E203" s="56" t="n"/>
-      <c r="F203" s="56" t="n"/>
+      <c r="E203" s="61" t="n"/>
+      <c r="F203" s="61" t="n"/>
       <c r="G203" s="57">
         <f>IF(AND(D203&lt;&gt;"已完成",D203&lt;&gt;"",E203&lt;&gt;"",E203&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5544,8 +5555,8 @@
       <c r="B204" s="55" t="n"/>
       <c r="C204" s="54" t="n"/>
       <c r="D204" s="54" t="n"/>
-      <c r="E204" s="56" t="n"/>
-      <c r="F204" s="56" t="n"/>
+      <c r="E204" s="61" t="n"/>
+      <c r="F204" s="61" t="n"/>
       <c r="G204" s="57">
         <f>IF(AND(D204&lt;&gt;"已完成",D204&lt;&gt;"",E204&lt;&gt;"",E204&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5558,8 +5569,8 @@
       <c r="B205" s="55" t="n"/>
       <c r="C205" s="54" t="n"/>
       <c r="D205" s="54" t="n"/>
-      <c r="E205" s="56" t="n"/>
-      <c r="F205" s="56" t="n"/>
+      <c r="E205" s="61" t="n"/>
+      <c r="F205" s="61" t="n"/>
       <c r="G205" s="57">
         <f>IF(AND(D205&lt;&gt;"已完成",D205&lt;&gt;"",E205&lt;&gt;"",E205&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5572,8 +5583,8 @@
       <c r="B206" s="55" t="n"/>
       <c r="C206" s="54" t="n"/>
       <c r="D206" s="54" t="n"/>
-      <c r="E206" s="56" t="n"/>
-      <c r="F206" s="56" t="n"/>
+      <c r="E206" s="61" t="n"/>
+      <c r="F206" s="61" t="n"/>
       <c r="G206" s="57">
         <f>IF(AND(D206&lt;&gt;"已完成",D206&lt;&gt;"",E206&lt;&gt;"",E206&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5586,8 +5597,8 @@
       <c r="B207" s="55" t="n"/>
       <c r="C207" s="54" t="n"/>
       <c r="D207" s="54" t="n"/>
-      <c r="E207" s="56" t="n"/>
-      <c r="F207" s="56" t="n"/>
+      <c r="E207" s="61" t="n"/>
+      <c r="F207" s="61" t="n"/>
       <c r="G207" s="57">
         <f>IF(AND(D207&lt;&gt;"已完成",D207&lt;&gt;"",E207&lt;&gt;"",E207&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5600,8 +5611,8 @@
       <c r="B208" s="55" t="n"/>
       <c r="C208" s="54" t="n"/>
       <c r="D208" s="54" t="n"/>
-      <c r="E208" s="56" t="n"/>
-      <c r="F208" s="56" t="n"/>
+      <c r="E208" s="61" t="n"/>
+      <c r="F208" s="61" t="n"/>
       <c r="G208" s="57">
         <f>IF(AND(D208&lt;&gt;"已完成",D208&lt;&gt;"",E208&lt;&gt;"",E208&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5614,8 +5625,8 @@
       <c r="B209" s="55" t="n"/>
       <c r="C209" s="54" t="n"/>
       <c r="D209" s="54" t="n"/>
-      <c r="E209" s="56" t="n"/>
-      <c r="F209" s="56" t="n"/>
+      <c r="E209" s="61" t="n"/>
+      <c r="F209" s="61" t="n"/>
       <c r="G209" s="57">
         <f>IF(AND(D209&lt;&gt;"已完成",D209&lt;&gt;"",E209&lt;&gt;"",E209&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5628,8 +5639,8 @@
       <c r="B210" s="55" t="n"/>
       <c r="C210" s="54" t="n"/>
       <c r="D210" s="54" t="n"/>
-      <c r="E210" s="56" t="n"/>
-      <c r="F210" s="56" t="n"/>
+      <c r="E210" s="61" t="n"/>
+      <c r="F210" s="61" t="n"/>
       <c r="G210" s="57">
         <f>IF(AND(D210&lt;&gt;"已完成",D210&lt;&gt;"",E210&lt;&gt;"",E210&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5642,8 +5653,8 @@
       <c r="B211" s="55" t="n"/>
       <c r="C211" s="54" t="n"/>
       <c r="D211" s="54" t="n"/>
-      <c r="E211" s="56" t="n"/>
-      <c r="F211" s="56" t="n"/>
+      <c r="E211" s="61" t="n"/>
+      <c r="F211" s="61" t="n"/>
       <c r="G211" s="57">
         <f>IF(AND(D211&lt;&gt;"已完成",D211&lt;&gt;"",E211&lt;&gt;"",E211&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5656,8 +5667,8 @@
       <c r="B212" s="55" t="n"/>
       <c r="C212" s="54" t="n"/>
       <c r="D212" s="54" t="n"/>
-      <c r="E212" s="56" t="n"/>
-      <c r="F212" s="56" t="n"/>
+      <c r="E212" s="61" t="n"/>
+      <c r="F212" s="61" t="n"/>
       <c r="G212" s="57">
         <f>IF(AND(D212&lt;&gt;"已完成",D212&lt;&gt;"",E212&lt;&gt;"",E212&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5670,8 +5681,8 @@
       <c r="B213" s="55" t="n"/>
       <c r="C213" s="54" t="n"/>
       <c r="D213" s="54" t="n"/>
-      <c r="E213" s="56" t="n"/>
-      <c r="F213" s="56" t="n"/>
+      <c r="E213" s="61" t="n"/>
+      <c r="F213" s="61" t="n"/>
       <c r="G213" s="57">
         <f>IF(AND(D213&lt;&gt;"已完成",D213&lt;&gt;"",E213&lt;&gt;"",E213&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5684,8 +5695,8 @@
       <c r="B214" s="55" t="n"/>
       <c r="C214" s="54" t="n"/>
       <c r="D214" s="54" t="n"/>
-      <c r="E214" s="56" t="n"/>
-      <c r="F214" s="56" t="n"/>
+      <c r="E214" s="61" t="n"/>
+      <c r="F214" s="61" t="n"/>
       <c r="G214" s="57">
         <f>IF(AND(D214&lt;&gt;"已完成",D214&lt;&gt;"",E214&lt;&gt;"",E214&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5698,8 +5709,8 @@
       <c r="B215" s="55" t="n"/>
       <c r="C215" s="54" t="n"/>
       <c r="D215" s="54" t="n"/>
-      <c r="E215" s="56" t="n"/>
-      <c r="F215" s="56" t="n"/>
+      <c r="E215" s="61" t="n"/>
+      <c r="F215" s="61" t="n"/>
       <c r="G215" s="57">
         <f>IF(AND(D215&lt;&gt;"已完成",D215&lt;&gt;"",E215&lt;&gt;"",E215&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5712,8 +5723,8 @@
       <c r="B216" s="55" t="n"/>
       <c r="C216" s="54" t="n"/>
       <c r="D216" s="54" t="n"/>
-      <c r="E216" s="56" t="n"/>
-      <c r="F216" s="56" t="n"/>
+      <c r="E216" s="61" t="n"/>
+      <c r="F216" s="61" t="n"/>
       <c r="G216" s="57">
         <f>IF(AND(D216&lt;&gt;"已完成",D216&lt;&gt;"",E216&lt;&gt;"",E216&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5726,8 +5737,8 @@
       <c r="B217" s="55" t="n"/>
       <c r="C217" s="54" t="n"/>
       <c r="D217" s="54" t="n"/>
-      <c r="E217" s="56" t="n"/>
-      <c r="F217" s="56" t="n"/>
+      <c r="E217" s="61" t="n"/>
+      <c r="F217" s="61" t="n"/>
       <c r="G217" s="57">
         <f>IF(AND(D217&lt;&gt;"已完成",D217&lt;&gt;"",E217&lt;&gt;"",E217&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5740,8 +5751,8 @@
       <c r="B218" s="55" t="n"/>
       <c r="C218" s="54" t="n"/>
       <c r="D218" s="54" t="n"/>
-      <c r="E218" s="56" t="n"/>
-      <c r="F218" s="56" t="n"/>
+      <c r="E218" s="61" t="n"/>
+      <c r="F218" s="61" t="n"/>
       <c r="G218" s="57">
         <f>IF(AND(D218&lt;&gt;"已完成",D218&lt;&gt;"",E218&lt;&gt;"",E218&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5754,8 +5765,8 @@
       <c r="B219" s="55" t="n"/>
       <c r="C219" s="54" t="n"/>
       <c r="D219" s="54" t="n"/>
-      <c r="E219" s="56" t="n"/>
-      <c r="F219" s="56" t="n"/>
+      <c r="E219" s="61" t="n"/>
+      <c r="F219" s="61" t="n"/>
       <c r="G219" s="57">
         <f>IF(AND(D219&lt;&gt;"已完成",D219&lt;&gt;"",E219&lt;&gt;"",E219&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5768,8 +5779,8 @@
       <c r="B220" s="55" t="n"/>
       <c r="C220" s="54" t="n"/>
       <c r="D220" s="54" t="n"/>
-      <c r="E220" s="56" t="n"/>
-      <c r="F220" s="56" t="n"/>
+      <c r="E220" s="61" t="n"/>
+      <c r="F220" s="61" t="n"/>
       <c r="G220" s="57">
         <f>IF(AND(D220&lt;&gt;"已完成",D220&lt;&gt;"",E220&lt;&gt;"",E220&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5782,8 +5793,8 @@
       <c r="B221" s="55" t="n"/>
       <c r="C221" s="54" t="n"/>
       <c r="D221" s="54" t="n"/>
-      <c r="E221" s="56" t="n"/>
-      <c r="F221" s="56" t="n"/>
+      <c r="E221" s="61" t="n"/>
+      <c r="F221" s="61" t="n"/>
       <c r="G221" s="57">
         <f>IF(AND(D221&lt;&gt;"已完成",D221&lt;&gt;"",E221&lt;&gt;"",E221&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5796,8 +5807,8 @@
       <c r="B222" s="55" t="n"/>
       <c r="C222" s="54" t="n"/>
       <c r="D222" s="54" t="n"/>
-      <c r="E222" s="56" t="n"/>
-      <c r="F222" s="56" t="n"/>
+      <c r="E222" s="61" t="n"/>
+      <c r="F222" s="61" t="n"/>
       <c r="G222" s="57">
         <f>IF(AND(D222&lt;&gt;"已完成",D222&lt;&gt;"",E222&lt;&gt;"",E222&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5810,8 +5821,8 @@
       <c r="B223" s="55" t="n"/>
       <c r="C223" s="54" t="n"/>
       <c r="D223" s="54" t="n"/>
-      <c r="E223" s="56" t="n"/>
-      <c r="F223" s="56" t="n"/>
+      <c r="E223" s="61" t="n"/>
+      <c r="F223" s="61" t="n"/>
       <c r="G223" s="57">
         <f>IF(AND(D223&lt;&gt;"已完成",D223&lt;&gt;"",E223&lt;&gt;"",E223&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5824,8 +5835,8 @@
       <c r="B224" s="55" t="n"/>
       <c r="C224" s="54" t="n"/>
       <c r="D224" s="54" t="n"/>
-      <c r="E224" s="56" t="n"/>
-      <c r="F224" s="56" t="n"/>
+      <c r="E224" s="61" t="n"/>
+      <c r="F224" s="61" t="n"/>
       <c r="G224" s="57">
         <f>IF(AND(D224&lt;&gt;"已完成",D224&lt;&gt;"",E224&lt;&gt;"",E224&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5838,8 +5849,8 @@
       <c r="B225" s="55" t="n"/>
       <c r="C225" s="54" t="n"/>
       <c r="D225" s="54" t="n"/>
-      <c r="E225" s="56" t="n"/>
-      <c r="F225" s="56" t="n"/>
+      <c r="E225" s="61" t="n"/>
+      <c r="F225" s="61" t="n"/>
       <c r="G225" s="57">
         <f>IF(AND(D225&lt;&gt;"已完成",D225&lt;&gt;"",E225&lt;&gt;"",E225&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5852,8 +5863,8 @@
       <c r="B226" s="55" t="n"/>
       <c r="C226" s="54" t="n"/>
       <c r="D226" s="54" t="n"/>
-      <c r="E226" s="56" t="n"/>
-      <c r="F226" s="56" t="n"/>
+      <c r="E226" s="61" t="n"/>
+      <c r="F226" s="61" t="n"/>
       <c r="G226" s="57">
         <f>IF(AND(D226&lt;&gt;"已完成",D226&lt;&gt;"",E226&lt;&gt;"",E226&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5866,8 +5877,8 @@
       <c r="B227" s="55" t="n"/>
       <c r="C227" s="54" t="n"/>
       <c r="D227" s="54" t="n"/>
-      <c r="E227" s="56" t="n"/>
-      <c r="F227" s="56" t="n"/>
+      <c r="E227" s="61" t="n"/>
+      <c r="F227" s="61" t="n"/>
       <c r="G227" s="57">
         <f>IF(AND(D227&lt;&gt;"已完成",D227&lt;&gt;"",E227&lt;&gt;"",E227&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5880,8 +5891,8 @@
       <c r="B228" s="55" t="n"/>
       <c r="C228" s="54" t="n"/>
       <c r="D228" s="54" t="n"/>
-      <c r="E228" s="56" t="n"/>
-      <c r="F228" s="56" t="n"/>
+      <c r="E228" s="61" t="n"/>
+      <c r="F228" s="61" t="n"/>
       <c r="G228" s="57">
         <f>IF(AND(D228&lt;&gt;"已完成",D228&lt;&gt;"",E228&lt;&gt;"",E228&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5894,8 +5905,8 @@
       <c r="B229" s="55" t="n"/>
       <c r="C229" s="54" t="n"/>
       <c r="D229" s="54" t="n"/>
-      <c r="E229" s="56" t="n"/>
-      <c r="F229" s="56" t="n"/>
+      <c r="E229" s="61" t="n"/>
+      <c r="F229" s="61" t="n"/>
       <c r="G229" s="57">
         <f>IF(AND(D229&lt;&gt;"已完成",D229&lt;&gt;"",E229&lt;&gt;"",E229&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5908,8 +5919,8 @@
       <c r="B230" s="55" t="n"/>
       <c r="C230" s="54" t="n"/>
       <c r="D230" s="54" t="n"/>
-      <c r="E230" s="56" t="n"/>
-      <c r="F230" s="56" t="n"/>
+      <c r="E230" s="61" t="n"/>
+      <c r="F230" s="61" t="n"/>
       <c r="G230" s="57">
         <f>IF(AND(D230&lt;&gt;"已完成",D230&lt;&gt;"",E230&lt;&gt;"",E230&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5922,8 +5933,8 @@
       <c r="B231" s="55" t="n"/>
       <c r="C231" s="54" t="n"/>
       <c r="D231" s="54" t="n"/>
-      <c r="E231" s="56" t="n"/>
-      <c r="F231" s="56" t="n"/>
+      <c r="E231" s="61" t="n"/>
+      <c r="F231" s="61" t="n"/>
       <c r="G231" s="57">
         <f>IF(AND(D231&lt;&gt;"已完成",D231&lt;&gt;"",E231&lt;&gt;"",E231&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5936,8 +5947,8 @@
       <c r="B232" s="55" t="n"/>
       <c r="C232" s="54" t="n"/>
       <c r="D232" s="54" t="n"/>
-      <c r="E232" s="56" t="n"/>
-      <c r="F232" s="56" t="n"/>
+      <c r="E232" s="61" t="n"/>
+      <c r="F232" s="61" t="n"/>
       <c r="G232" s="57">
         <f>IF(AND(D232&lt;&gt;"已完成",D232&lt;&gt;"",E232&lt;&gt;"",E232&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5950,8 +5961,8 @@
       <c r="B233" s="55" t="n"/>
       <c r="C233" s="54" t="n"/>
       <c r="D233" s="54" t="n"/>
-      <c r="E233" s="56" t="n"/>
-      <c r="F233" s="56" t="n"/>
+      <c r="E233" s="61" t="n"/>
+      <c r="F233" s="61" t="n"/>
       <c r="G233" s="57">
         <f>IF(AND(D233&lt;&gt;"已完成",D233&lt;&gt;"",E233&lt;&gt;"",E233&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5964,8 +5975,8 @@
       <c r="B234" s="55" t="n"/>
       <c r="C234" s="54" t="n"/>
       <c r="D234" s="54" t="n"/>
-      <c r="E234" s="56" t="n"/>
-      <c r="F234" s="56" t="n"/>
+      <c r="E234" s="61" t="n"/>
+      <c r="F234" s="61" t="n"/>
       <c r="G234" s="57">
         <f>IF(AND(D234&lt;&gt;"已完成",D234&lt;&gt;"",E234&lt;&gt;"",E234&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5978,8 +5989,8 @@
       <c r="B235" s="55" t="n"/>
       <c r="C235" s="54" t="n"/>
       <c r="D235" s="54" t="n"/>
-      <c r="E235" s="56" t="n"/>
-      <c r="F235" s="56" t="n"/>
+      <c r="E235" s="61" t="n"/>
+      <c r="F235" s="61" t="n"/>
       <c r="G235" s="57">
         <f>IF(AND(D235&lt;&gt;"已完成",D235&lt;&gt;"",E235&lt;&gt;"",E235&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -5992,8 +6003,8 @@
       <c r="B236" s="55" t="n"/>
       <c r="C236" s="54" t="n"/>
       <c r="D236" s="54" t="n"/>
-      <c r="E236" s="56" t="n"/>
-      <c r="F236" s="56" t="n"/>
+      <c r="E236" s="61" t="n"/>
+      <c r="F236" s="61" t="n"/>
       <c r="G236" s="57">
         <f>IF(AND(D236&lt;&gt;"已完成",D236&lt;&gt;"",E236&lt;&gt;"",E236&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6006,8 +6017,8 @@
       <c r="B237" s="55" t="n"/>
       <c r="C237" s="54" t="n"/>
       <c r="D237" s="54" t="n"/>
-      <c r="E237" s="56" t="n"/>
-      <c r="F237" s="56" t="n"/>
+      <c r="E237" s="61" t="n"/>
+      <c r="F237" s="61" t="n"/>
       <c r="G237" s="57">
         <f>IF(AND(D237&lt;&gt;"已完成",D237&lt;&gt;"",E237&lt;&gt;"",E237&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6020,8 +6031,8 @@
       <c r="B238" s="55" t="n"/>
       <c r="C238" s="54" t="n"/>
       <c r="D238" s="54" t="n"/>
-      <c r="E238" s="56" t="n"/>
-      <c r="F238" s="56" t="n"/>
+      <c r="E238" s="61" t="n"/>
+      <c r="F238" s="61" t="n"/>
       <c r="G238" s="57">
         <f>IF(AND(D238&lt;&gt;"已完成",D238&lt;&gt;"",E238&lt;&gt;"",E238&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6034,8 +6045,8 @@
       <c r="B239" s="55" t="n"/>
       <c r="C239" s="54" t="n"/>
       <c r="D239" s="54" t="n"/>
-      <c r="E239" s="56" t="n"/>
-      <c r="F239" s="56" t="n"/>
+      <c r="E239" s="61" t="n"/>
+      <c r="F239" s="61" t="n"/>
       <c r="G239" s="57">
         <f>IF(AND(D239&lt;&gt;"已完成",D239&lt;&gt;"",E239&lt;&gt;"",E239&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6048,8 +6059,8 @@
       <c r="B240" s="55" t="n"/>
       <c r="C240" s="54" t="n"/>
       <c r="D240" s="54" t="n"/>
-      <c r="E240" s="56" t="n"/>
-      <c r="F240" s="56" t="n"/>
+      <c r="E240" s="61" t="n"/>
+      <c r="F240" s="61" t="n"/>
       <c r="G240" s="57">
         <f>IF(AND(D240&lt;&gt;"已完成",D240&lt;&gt;"",E240&lt;&gt;"",E240&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6062,8 +6073,8 @@
       <c r="B241" s="55" t="n"/>
       <c r="C241" s="54" t="n"/>
       <c r="D241" s="54" t="n"/>
-      <c r="E241" s="56" t="n"/>
-      <c r="F241" s="56" t="n"/>
+      <c r="E241" s="61" t="n"/>
+      <c r="F241" s="61" t="n"/>
       <c r="G241" s="57">
         <f>IF(AND(D241&lt;&gt;"已完成",D241&lt;&gt;"",E241&lt;&gt;"",E241&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6076,8 +6087,8 @@
       <c r="B242" s="55" t="n"/>
       <c r="C242" s="54" t="n"/>
       <c r="D242" s="54" t="n"/>
-      <c r="E242" s="56" t="n"/>
-      <c r="F242" s="56" t="n"/>
+      <c r="E242" s="61" t="n"/>
+      <c r="F242" s="61" t="n"/>
       <c r="G242" s="57">
         <f>IF(AND(D242&lt;&gt;"已完成",D242&lt;&gt;"",E242&lt;&gt;"",E242&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6090,8 +6101,8 @@
       <c r="B243" s="55" t="n"/>
       <c r="C243" s="54" t="n"/>
       <c r="D243" s="54" t="n"/>
-      <c r="E243" s="56" t="n"/>
-      <c r="F243" s="56" t="n"/>
+      <c r="E243" s="61" t="n"/>
+      <c r="F243" s="61" t="n"/>
       <c r="G243" s="57">
         <f>IF(AND(D243&lt;&gt;"已完成",D243&lt;&gt;"",E243&lt;&gt;"",E243&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6104,8 +6115,8 @@
       <c r="B244" s="55" t="n"/>
       <c r="C244" s="54" t="n"/>
       <c r="D244" s="54" t="n"/>
-      <c r="E244" s="56" t="n"/>
-      <c r="F244" s="56" t="n"/>
+      <c r="E244" s="61" t="n"/>
+      <c r="F244" s="61" t="n"/>
       <c r="G244" s="57">
         <f>IF(AND(D244&lt;&gt;"已完成",D244&lt;&gt;"",E244&lt;&gt;"",E244&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6118,8 +6129,8 @@
       <c r="B245" s="55" t="n"/>
       <c r="C245" s="54" t="n"/>
       <c r="D245" s="54" t="n"/>
-      <c r="E245" s="56" t="n"/>
-      <c r="F245" s="56" t="n"/>
+      <c r="E245" s="61" t="n"/>
+      <c r="F245" s="61" t="n"/>
       <c r="G245" s="57">
         <f>IF(AND(D245&lt;&gt;"已完成",D245&lt;&gt;"",E245&lt;&gt;"",E245&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6132,8 +6143,8 @@
       <c r="B246" s="55" t="n"/>
       <c r="C246" s="54" t="n"/>
       <c r="D246" s="54" t="n"/>
-      <c r="E246" s="56" t="n"/>
-      <c r="F246" s="56" t="n"/>
+      <c r="E246" s="61" t="n"/>
+      <c r="F246" s="61" t="n"/>
       <c r="G246" s="57">
         <f>IF(AND(D246&lt;&gt;"已完成",D246&lt;&gt;"",E246&lt;&gt;"",E246&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6146,8 +6157,8 @@
       <c r="B247" s="55" t="n"/>
       <c r="C247" s="54" t="n"/>
       <c r="D247" s="54" t="n"/>
-      <c r="E247" s="56" t="n"/>
-      <c r="F247" s="56" t="n"/>
+      <c r="E247" s="61" t="n"/>
+      <c r="F247" s="61" t="n"/>
       <c r="G247" s="57">
         <f>IF(AND(D247&lt;&gt;"已完成",D247&lt;&gt;"",E247&lt;&gt;"",E247&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6160,8 +6171,8 @@
       <c r="B248" s="55" t="n"/>
       <c r="C248" s="54" t="n"/>
       <c r="D248" s="54" t="n"/>
-      <c r="E248" s="56" t="n"/>
-      <c r="F248" s="56" t="n"/>
+      <c r="E248" s="61" t="n"/>
+      <c r="F248" s="61" t="n"/>
       <c r="G248" s="57">
         <f>IF(AND(D248&lt;&gt;"已完成",D248&lt;&gt;"",E248&lt;&gt;"",E248&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6174,8 +6185,8 @@
       <c r="B249" s="55" t="n"/>
       <c r="C249" s="54" t="n"/>
       <c r="D249" s="54" t="n"/>
-      <c r="E249" s="56" t="n"/>
-      <c r="F249" s="56" t="n"/>
+      <c r="E249" s="61" t="n"/>
+      <c r="F249" s="61" t="n"/>
       <c r="G249" s="57">
         <f>IF(AND(D249&lt;&gt;"已完成",D249&lt;&gt;"",E249&lt;&gt;"",E249&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6188,8 +6199,8 @@
       <c r="B250" s="55" t="n"/>
       <c r="C250" s="54" t="n"/>
       <c r="D250" s="54" t="n"/>
-      <c r="E250" s="56" t="n"/>
-      <c r="F250" s="56" t="n"/>
+      <c r="E250" s="61" t="n"/>
+      <c r="F250" s="61" t="n"/>
       <c r="G250" s="57">
         <f>IF(AND(D250&lt;&gt;"已完成",D250&lt;&gt;"",E250&lt;&gt;"",E250&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6202,8 +6213,8 @@
       <c r="B251" s="55" t="n"/>
       <c r="C251" s="54" t="n"/>
       <c r="D251" s="54" t="n"/>
-      <c r="E251" s="56" t="n"/>
-      <c r="F251" s="56" t="n"/>
+      <c r="E251" s="61" t="n"/>
+      <c r="F251" s="61" t="n"/>
       <c r="G251" s="57">
         <f>IF(AND(D251&lt;&gt;"已完成",D251&lt;&gt;"",E251&lt;&gt;"",E251&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6216,8 +6227,8 @@
       <c r="B252" s="55" t="n"/>
       <c r="C252" s="54" t="n"/>
       <c r="D252" s="54" t="n"/>
-      <c r="E252" s="56" t="n"/>
-      <c r="F252" s="56" t="n"/>
+      <c r="E252" s="61" t="n"/>
+      <c r="F252" s="61" t="n"/>
       <c r="G252" s="57">
         <f>IF(AND(D252&lt;&gt;"已完成",D252&lt;&gt;"",E252&lt;&gt;"",E252&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6230,8 +6241,8 @@
       <c r="B253" s="55" t="n"/>
       <c r="C253" s="54" t="n"/>
       <c r="D253" s="54" t="n"/>
-      <c r="E253" s="56" t="n"/>
-      <c r="F253" s="56" t="n"/>
+      <c r="E253" s="61" t="n"/>
+      <c r="F253" s="61" t="n"/>
       <c r="G253" s="57">
         <f>IF(AND(D253&lt;&gt;"已完成",D253&lt;&gt;"",E253&lt;&gt;"",E253&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6244,8 +6255,8 @@
       <c r="B254" s="55" t="n"/>
       <c r="C254" s="54" t="n"/>
       <c r="D254" s="54" t="n"/>
-      <c r="E254" s="56" t="n"/>
-      <c r="F254" s="56" t="n"/>
+      <c r="E254" s="61" t="n"/>
+      <c r="F254" s="61" t="n"/>
       <c r="G254" s="57">
         <f>IF(AND(D254&lt;&gt;"已完成",D254&lt;&gt;"",E254&lt;&gt;"",E254&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6258,8 +6269,8 @@
       <c r="B255" s="55" t="n"/>
       <c r="C255" s="54" t="n"/>
       <c r="D255" s="54" t="n"/>
-      <c r="E255" s="56" t="n"/>
-      <c r="F255" s="56" t="n"/>
+      <c r="E255" s="61" t="n"/>
+      <c r="F255" s="61" t="n"/>
       <c r="G255" s="57">
         <f>IF(AND(D255&lt;&gt;"已完成",D255&lt;&gt;"",E255&lt;&gt;"",E255&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6272,8 +6283,8 @@
       <c r="B256" s="55" t="n"/>
       <c r="C256" s="54" t="n"/>
       <c r="D256" s="54" t="n"/>
-      <c r="E256" s="56" t="n"/>
-      <c r="F256" s="56" t="n"/>
+      <c r="E256" s="61" t="n"/>
+      <c r="F256" s="61" t="n"/>
       <c r="G256" s="57">
         <f>IF(AND(D256&lt;&gt;"已完成",D256&lt;&gt;"",E256&lt;&gt;"",E256&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6286,8 +6297,8 @@
       <c r="B257" s="55" t="n"/>
       <c r="C257" s="54" t="n"/>
       <c r="D257" s="54" t="n"/>
-      <c r="E257" s="56" t="n"/>
-      <c r="F257" s="56" t="n"/>
+      <c r="E257" s="61" t="n"/>
+      <c r="F257" s="61" t="n"/>
       <c r="G257" s="57">
         <f>IF(AND(D257&lt;&gt;"已完成",D257&lt;&gt;"",E257&lt;&gt;"",E257&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6300,8 +6311,8 @@
       <c r="B258" s="55" t="n"/>
       <c r="C258" s="54" t="n"/>
       <c r="D258" s="54" t="n"/>
-      <c r="E258" s="56" t="n"/>
-      <c r="F258" s="56" t="n"/>
+      <c r="E258" s="61" t="n"/>
+      <c r="F258" s="61" t="n"/>
       <c r="G258" s="57">
         <f>IF(AND(D258&lt;&gt;"已完成",D258&lt;&gt;"",E258&lt;&gt;"",E258&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6314,8 +6325,8 @@
       <c r="B259" s="55" t="n"/>
       <c r="C259" s="54" t="n"/>
       <c r="D259" s="54" t="n"/>
-      <c r="E259" s="56" t="n"/>
-      <c r="F259" s="56" t="n"/>
+      <c r="E259" s="61" t="n"/>
+      <c r="F259" s="61" t="n"/>
       <c r="G259" s="57">
         <f>IF(AND(D259&lt;&gt;"已完成",D259&lt;&gt;"",E259&lt;&gt;"",E259&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6328,8 +6339,8 @@
       <c r="B260" s="55" t="n"/>
       <c r="C260" s="54" t="n"/>
       <c r="D260" s="54" t="n"/>
-      <c r="E260" s="56" t="n"/>
-      <c r="F260" s="56" t="n"/>
+      <c r="E260" s="61" t="n"/>
+      <c r="F260" s="61" t="n"/>
       <c r="G260" s="57">
         <f>IF(AND(D260&lt;&gt;"已完成",D260&lt;&gt;"",E260&lt;&gt;"",E260&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6342,8 +6353,8 @@
       <c r="B261" s="55" t="n"/>
       <c r="C261" s="54" t="n"/>
       <c r="D261" s="54" t="n"/>
-      <c r="E261" s="56" t="n"/>
-      <c r="F261" s="56" t="n"/>
+      <c r="E261" s="61" t="n"/>
+      <c r="F261" s="61" t="n"/>
       <c r="G261" s="57">
         <f>IF(AND(D261&lt;&gt;"已完成",D261&lt;&gt;"",E261&lt;&gt;"",E261&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6356,8 +6367,8 @@
       <c r="B262" s="55" t="n"/>
       <c r="C262" s="54" t="n"/>
       <c r="D262" s="54" t="n"/>
-      <c r="E262" s="56" t="n"/>
-      <c r="F262" s="56" t="n"/>
+      <c r="E262" s="61" t="n"/>
+      <c r="F262" s="61" t="n"/>
       <c r="G262" s="57">
         <f>IF(AND(D262&lt;&gt;"已完成",D262&lt;&gt;"",E262&lt;&gt;"",E262&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6370,8 +6381,8 @@
       <c r="B263" s="55" t="n"/>
       <c r="C263" s="54" t="n"/>
       <c r="D263" s="54" t="n"/>
-      <c r="E263" s="56" t="n"/>
-      <c r="F263" s="56" t="n"/>
+      <c r="E263" s="61" t="n"/>
+      <c r="F263" s="61" t="n"/>
       <c r="G263" s="57">
         <f>IF(AND(D263&lt;&gt;"已完成",D263&lt;&gt;"",E263&lt;&gt;"",E263&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6384,8 +6395,8 @@
       <c r="B264" s="55" t="n"/>
       <c r="C264" s="54" t="n"/>
       <c r="D264" s="54" t="n"/>
-      <c r="E264" s="56" t="n"/>
-      <c r="F264" s="56" t="n"/>
+      <c r="E264" s="61" t="n"/>
+      <c r="F264" s="61" t="n"/>
       <c r="G264" s="57">
         <f>IF(AND(D264&lt;&gt;"已完成",D264&lt;&gt;"",E264&lt;&gt;"",E264&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6398,8 +6409,8 @@
       <c r="B265" s="55" t="n"/>
       <c r="C265" s="54" t="n"/>
       <c r="D265" s="54" t="n"/>
-      <c r="E265" s="56" t="n"/>
-      <c r="F265" s="56" t="n"/>
+      <c r="E265" s="61" t="n"/>
+      <c r="F265" s="61" t="n"/>
       <c r="G265" s="57">
         <f>IF(AND(D265&lt;&gt;"已完成",D265&lt;&gt;"",E265&lt;&gt;"",E265&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6412,8 +6423,8 @@
       <c r="B266" s="55" t="n"/>
       <c r="C266" s="54" t="n"/>
       <c r="D266" s="54" t="n"/>
-      <c r="E266" s="56" t="n"/>
-      <c r="F266" s="56" t="n"/>
+      <c r="E266" s="61" t="n"/>
+      <c r="F266" s="61" t="n"/>
       <c r="G266" s="57">
         <f>IF(AND(D266&lt;&gt;"已完成",D266&lt;&gt;"",E266&lt;&gt;"",E266&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6426,8 +6437,8 @@
       <c r="B267" s="55" t="n"/>
       <c r="C267" s="54" t="n"/>
       <c r="D267" s="54" t="n"/>
-      <c r="E267" s="56" t="n"/>
-      <c r="F267" s="56" t="n"/>
+      <c r="E267" s="61" t="n"/>
+      <c r="F267" s="61" t="n"/>
       <c r="G267" s="57">
         <f>IF(AND(D267&lt;&gt;"已完成",D267&lt;&gt;"",E267&lt;&gt;"",E267&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6440,8 +6451,8 @@
       <c r="B268" s="55" t="n"/>
       <c r="C268" s="54" t="n"/>
       <c r="D268" s="54" t="n"/>
-      <c r="E268" s="56" t="n"/>
-      <c r="F268" s="56" t="n"/>
+      <c r="E268" s="61" t="n"/>
+      <c r="F268" s="61" t="n"/>
       <c r="G268" s="57">
         <f>IF(AND(D268&lt;&gt;"已完成",D268&lt;&gt;"",E268&lt;&gt;"",E268&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6454,8 +6465,8 @@
       <c r="B269" s="55" t="n"/>
       <c r="C269" s="54" t="n"/>
       <c r="D269" s="54" t="n"/>
-      <c r="E269" s="56" t="n"/>
-      <c r="F269" s="56" t="n"/>
+      <c r="E269" s="61" t="n"/>
+      <c r="F269" s="61" t="n"/>
       <c r="G269" s="57">
         <f>IF(AND(D269&lt;&gt;"已完成",D269&lt;&gt;"",E269&lt;&gt;"",E269&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6468,8 +6479,8 @@
       <c r="B270" s="55" t="n"/>
       <c r="C270" s="54" t="n"/>
       <c r="D270" s="54" t="n"/>
-      <c r="E270" s="56" t="n"/>
-      <c r="F270" s="56" t="n"/>
+      <c r="E270" s="61" t="n"/>
+      <c r="F270" s="61" t="n"/>
       <c r="G270" s="57">
         <f>IF(AND(D270&lt;&gt;"已完成",D270&lt;&gt;"",E270&lt;&gt;"",E270&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6482,8 +6493,8 @@
       <c r="B271" s="55" t="n"/>
       <c r="C271" s="54" t="n"/>
       <c r="D271" s="54" t="n"/>
-      <c r="E271" s="56" t="n"/>
-      <c r="F271" s="56" t="n"/>
+      <c r="E271" s="61" t="n"/>
+      <c r="F271" s="61" t="n"/>
       <c r="G271" s="57">
         <f>IF(AND(D271&lt;&gt;"已完成",D271&lt;&gt;"",E271&lt;&gt;"",E271&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6496,8 +6507,8 @@
       <c r="B272" s="55" t="n"/>
       <c r="C272" s="54" t="n"/>
       <c r="D272" s="54" t="n"/>
-      <c r="E272" s="56" t="n"/>
-      <c r="F272" s="56" t="n"/>
+      <c r="E272" s="61" t="n"/>
+      <c r="F272" s="61" t="n"/>
       <c r="G272" s="57">
         <f>IF(AND(D272&lt;&gt;"已完成",D272&lt;&gt;"",E272&lt;&gt;"",E272&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6510,8 +6521,8 @@
       <c r="B273" s="55" t="n"/>
       <c r="C273" s="54" t="n"/>
       <c r="D273" s="54" t="n"/>
-      <c r="E273" s="56" t="n"/>
-      <c r="F273" s="56" t="n"/>
+      <c r="E273" s="61" t="n"/>
+      <c r="F273" s="61" t="n"/>
       <c r="G273" s="57">
         <f>IF(AND(D273&lt;&gt;"已完成",D273&lt;&gt;"",E273&lt;&gt;"",E273&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6524,8 +6535,8 @@
       <c r="B274" s="55" t="n"/>
       <c r="C274" s="54" t="n"/>
       <c r="D274" s="54" t="n"/>
-      <c r="E274" s="56" t="n"/>
-      <c r="F274" s="56" t="n"/>
+      <c r="E274" s="61" t="n"/>
+      <c r="F274" s="61" t="n"/>
       <c r="G274" s="57">
         <f>IF(AND(D274&lt;&gt;"已完成",D274&lt;&gt;"",E274&lt;&gt;"",E274&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6538,8 +6549,8 @@
       <c r="B275" s="55" t="n"/>
       <c r="C275" s="54" t="n"/>
       <c r="D275" s="54" t="n"/>
-      <c r="E275" s="56" t="n"/>
-      <c r="F275" s="56" t="n"/>
+      <c r="E275" s="61" t="n"/>
+      <c r="F275" s="61" t="n"/>
       <c r="G275" s="57">
         <f>IF(AND(D275&lt;&gt;"已完成",D275&lt;&gt;"",E275&lt;&gt;"",E275&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6552,8 +6563,8 @@
       <c r="B276" s="55" t="n"/>
       <c r="C276" s="54" t="n"/>
       <c r="D276" s="54" t="n"/>
-      <c r="E276" s="56" t="n"/>
-      <c r="F276" s="56" t="n"/>
+      <c r="E276" s="61" t="n"/>
+      <c r="F276" s="61" t="n"/>
       <c r="G276" s="57">
         <f>IF(AND(D276&lt;&gt;"已完成",D276&lt;&gt;"",E276&lt;&gt;"",E276&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6566,8 +6577,8 @@
       <c r="B277" s="55" t="n"/>
       <c r="C277" s="54" t="n"/>
       <c r="D277" s="54" t="n"/>
-      <c r="E277" s="56" t="n"/>
-      <c r="F277" s="56" t="n"/>
+      <c r="E277" s="61" t="n"/>
+      <c r="F277" s="61" t="n"/>
       <c r="G277" s="57">
         <f>IF(AND(D277&lt;&gt;"已完成",D277&lt;&gt;"",E277&lt;&gt;"",E277&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6580,8 +6591,8 @@
       <c r="B278" s="55" t="n"/>
       <c r="C278" s="54" t="n"/>
       <c r="D278" s="54" t="n"/>
-      <c r="E278" s="56" t="n"/>
-      <c r="F278" s="56" t="n"/>
+      <c r="E278" s="61" t="n"/>
+      <c r="F278" s="61" t="n"/>
       <c r="G278" s="57">
         <f>IF(AND(D278&lt;&gt;"已完成",D278&lt;&gt;"",E278&lt;&gt;"",E278&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6594,8 +6605,8 @@
       <c r="B279" s="55" t="n"/>
       <c r="C279" s="54" t="n"/>
       <c r="D279" s="54" t="n"/>
-      <c r="E279" s="56" t="n"/>
-      <c r="F279" s="56" t="n"/>
+      <c r="E279" s="61" t="n"/>
+      <c r="F279" s="61" t="n"/>
       <c r="G279" s="57">
         <f>IF(AND(D279&lt;&gt;"已完成",D279&lt;&gt;"",E279&lt;&gt;"",E279&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6608,8 +6619,8 @@
       <c r="B280" s="55" t="n"/>
       <c r="C280" s="54" t="n"/>
       <c r="D280" s="54" t="n"/>
-      <c r="E280" s="56" t="n"/>
-      <c r="F280" s="56" t="n"/>
+      <c r="E280" s="61" t="n"/>
+      <c r="F280" s="61" t="n"/>
       <c r="G280" s="57">
         <f>IF(AND(D280&lt;&gt;"已完成",D280&lt;&gt;"",E280&lt;&gt;"",E280&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6622,8 +6633,8 @@
       <c r="B281" s="55" t="n"/>
       <c r="C281" s="54" t="n"/>
       <c r="D281" s="54" t="n"/>
-      <c r="E281" s="56" t="n"/>
-      <c r="F281" s="56" t="n"/>
+      <c r="E281" s="61" t="n"/>
+      <c r="F281" s="61" t="n"/>
       <c r="G281" s="57">
         <f>IF(AND(D281&lt;&gt;"已完成",D281&lt;&gt;"",E281&lt;&gt;"",E281&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6636,8 +6647,8 @@
       <c r="B282" s="55" t="n"/>
       <c r="C282" s="54" t="n"/>
       <c r="D282" s="54" t="n"/>
-      <c r="E282" s="56" t="n"/>
-      <c r="F282" s="56" t="n"/>
+      <c r="E282" s="61" t="n"/>
+      <c r="F282" s="61" t="n"/>
       <c r="G282" s="57">
         <f>IF(AND(D282&lt;&gt;"已完成",D282&lt;&gt;"",E282&lt;&gt;"",E282&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6650,8 +6661,8 @@
       <c r="B283" s="55" t="n"/>
       <c r="C283" s="54" t="n"/>
       <c r="D283" s="54" t="n"/>
-      <c r="E283" s="56" t="n"/>
-      <c r="F283" s="56" t="n"/>
+      <c r="E283" s="61" t="n"/>
+      <c r="F283" s="61" t="n"/>
       <c r="G283" s="57">
         <f>IF(AND(D283&lt;&gt;"已完成",D283&lt;&gt;"",E283&lt;&gt;"",E283&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6664,8 +6675,8 @@
       <c r="B284" s="55" t="n"/>
       <c r="C284" s="54" t="n"/>
       <c r="D284" s="54" t="n"/>
-      <c r="E284" s="56" t="n"/>
-      <c r="F284" s="56" t="n"/>
+      <c r="E284" s="61" t="n"/>
+      <c r="F284" s="61" t="n"/>
       <c r="G284" s="57">
         <f>IF(AND(D284&lt;&gt;"已完成",D284&lt;&gt;"",E284&lt;&gt;"",E284&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6678,8 +6689,8 @@
       <c r="B285" s="55" t="n"/>
       <c r="C285" s="54" t="n"/>
       <c r="D285" s="54" t="n"/>
-      <c r="E285" s="56" t="n"/>
-      <c r="F285" s="56" t="n"/>
+      <c r="E285" s="61" t="n"/>
+      <c r="F285" s="61" t="n"/>
       <c r="G285" s="57">
         <f>IF(AND(D285&lt;&gt;"已完成",D285&lt;&gt;"",E285&lt;&gt;"",E285&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6692,8 +6703,8 @@
       <c r="B286" s="55" t="n"/>
       <c r="C286" s="54" t="n"/>
       <c r="D286" s="54" t="n"/>
-      <c r="E286" s="56" t="n"/>
-      <c r="F286" s="56" t="n"/>
+      <c r="E286" s="61" t="n"/>
+      <c r="F286" s="61" t="n"/>
       <c r="G286" s="57">
         <f>IF(AND(D286&lt;&gt;"已完成",D286&lt;&gt;"",E286&lt;&gt;"",E286&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6706,8 +6717,8 @@
       <c r="B287" s="55" t="n"/>
       <c r="C287" s="54" t="n"/>
       <c r="D287" s="54" t="n"/>
-      <c r="E287" s="56" t="n"/>
-      <c r="F287" s="56" t="n"/>
+      <c r="E287" s="61" t="n"/>
+      <c r="F287" s="61" t="n"/>
       <c r="G287" s="57">
         <f>IF(AND(D287&lt;&gt;"已完成",D287&lt;&gt;"",E287&lt;&gt;"",E287&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6720,8 +6731,8 @@
       <c r="B288" s="55" t="n"/>
       <c r="C288" s="54" t="n"/>
       <c r="D288" s="54" t="n"/>
-      <c r="E288" s="56" t="n"/>
-      <c r="F288" s="56" t="n"/>
+      <c r="E288" s="61" t="n"/>
+      <c r="F288" s="61" t="n"/>
       <c r="G288" s="57">
         <f>IF(AND(D288&lt;&gt;"已完成",D288&lt;&gt;"",E288&lt;&gt;"",E288&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6734,8 +6745,8 @@
       <c r="B289" s="55" t="n"/>
       <c r="C289" s="54" t="n"/>
       <c r="D289" s="54" t="n"/>
-      <c r="E289" s="56" t="n"/>
-      <c r="F289" s="56" t="n"/>
+      <c r="E289" s="61" t="n"/>
+      <c r="F289" s="61" t="n"/>
       <c r="G289" s="57">
         <f>IF(AND(D289&lt;&gt;"已完成",D289&lt;&gt;"",E289&lt;&gt;"",E289&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6748,8 +6759,8 @@
       <c r="B290" s="55" t="n"/>
       <c r="C290" s="54" t="n"/>
       <c r="D290" s="54" t="n"/>
-      <c r="E290" s="56" t="n"/>
-      <c r="F290" s="56" t="n"/>
+      <c r="E290" s="61" t="n"/>
+      <c r="F290" s="61" t="n"/>
       <c r="G290" s="57">
         <f>IF(AND(D290&lt;&gt;"已完成",D290&lt;&gt;"",E290&lt;&gt;"",E290&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6762,8 +6773,8 @@
       <c r="B291" s="55" t="n"/>
       <c r="C291" s="54" t="n"/>
       <c r="D291" s="54" t="n"/>
-      <c r="E291" s="56" t="n"/>
-      <c r="F291" s="56" t="n"/>
+      <c r="E291" s="61" t="n"/>
+      <c r="F291" s="61" t="n"/>
       <c r="G291" s="57">
         <f>IF(AND(D291&lt;&gt;"已完成",D291&lt;&gt;"",E291&lt;&gt;"",E291&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6776,8 +6787,8 @@
       <c r="B292" s="55" t="n"/>
       <c r="C292" s="54" t="n"/>
       <c r="D292" s="54" t="n"/>
-      <c r="E292" s="56" t="n"/>
-      <c r="F292" s="56" t="n"/>
+      <c r="E292" s="61" t="n"/>
+      <c r="F292" s="61" t="n"/>
       <c r="G292" s="57">
         <f>IF(AND(D292&lt;&gt;"已完成",D292&lt;&gt;"",E292&lt;&gt;"",E292&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6790,8 +6801,8 @@
       <c r="B293" s="55" t="n"/>
       <c r="C293" s="54" t="n"/>
       <c r="D293" s="54" t="n"/>
-      <c r="E293" s="56" t="n"/>
-      <c r="F293" s="56" t="n"/>
+      <c r="E293" s="61" t="n"/>
+      <c r="F293" s="61" t="n"/>
       <c r="G293" s="57">
         <f>IF(AND(D293&lt;&gt;"已完成",D293&lt;&gt;"",E293&lt;&gt;"",E293&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6804,8 +6815,8 @@
       <c r="B294" s="55" t="n"/>
       <c r="C294" s="54" t="n"/>
       <c r="D294" s="54" t="n"/>
-      <c r="E294" s="56" t="n"/>
-      <c r="F294" s="56" t="n"/>
+      <c r="E294" s="61" t="n"/>
+      <c r="F294" s="61" t="n"/>
       <c r="G294" s="57">
         <f>IF(AND(D294&lt;&gt;"已完成",D294&lt;&gt;"",E294&lt;&gt;"",E294&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6818,8 +6829,8 @@
       <c r="B295" s="55" t="n"/>
       <c r="C295" s="54" t="n"/>
       <c r="D295" s="54" t="n"/>
-      <c r="E295" s="56" t="n"/>
-      <c r="F295" s="56" t="n"/>
+      <c r="E295" s="61" t="n"/>
+      <c r="F295" s="61" t="n"/>
       <c r="G295" s="57">
         <f>IF(AND(D295&lt;&gt;"已完成",D295&lt;&gt;"",E295&lt;&gt;"",E295&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6832,8 +6843,8 @@
       <c r="B296" s="55" t="n"/>
       <c r="C296" s="54" t="n"/>
       <c r="D296" s="54" t="n"/>
-      <c r="E296" s="56" t="n"/>
-      <c r="F296" s="56" t="n"/>
+      <c r="E296" s="61" t="n"/>
+      <c r="F296" s="61" t="n"/>
       <c r="G296" s="57">
         <f>IF(AND(D296&lt;&gt;"已完成",D296&lt;&gt;"",E296&lt;&gt;"",E296&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6846,8 +6857,8 @@
       <c r="B297" s="55" t="n"/>
       <c r="C297" s="54" t="n"/>
       <c r="D297" s="54" t="n"/>
-      <c r="E297" s="56" t="n"/>
-      <c r="F297" s="56" t="n"/>
+      <c r="E297" s="61" t="n"/>
+      <c r="F297" s="61" t="n"/>
       <c r="G297" s="57">
         <f>IF(AND(D297&lt;&gt;"已完成",D297&lt;&gt;"",E297&lt;&gt;"",E297&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6860,8 +6871,8 @@
       <c r="B298" s="55" t="n"/>
       <c r="C298" s="54" t="n"/>
       <c r="D298" s="54" t="n"/>
-      <c r="E298" s="56" t="n"/>
-      <c r="F298" s="56" t="n"/>
+      <c r="E298" s="61" t="n"/>
+      <c r="F298" s="61" t="n"/>
       <c r="G298" s="57">
         <f>IF(AND(D298&lt;&gt;"已完成",D298&lt;&gt;"",E298&lt;&gt;"",E298&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6874,8 +6885,8 @@
       <c r="B299" s="55" t="n"/>
       <c r="C299" s="54" t="n"/>
       <c r="D299" s="54" t="n"/>
-      <c r="E299" s="56" t="n"/>
-      <c r="F299" s="56" t="n"/>
+      <c r="E299" s="61" t="n"/>
+      <c r="F299" s="61" t="n"/>
       <c r="G299" s="57">
         <f>IF(AND(D299&lt;&gt;"已完成",D299&lt;&gt;"",E299&lt;&gt;"",E299&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6888,8 +6899,8 @@
       <c r="B300" s="55" t="n"/>
       <c r="C300" s="54" t="n"/>
       <c r="D300" s="54" t="n"/>
-      <c r="E300" s="56" t="n"/>
-      <c r="F300" s="56" t="n"/>
+      <c r="E300" s="61" t="n"/>
+      <c r="F300" s="61" t="n"/>
       <c r="G300" s="57">
         <f>IF(AND(D300&lt;&gt;"已完成",D300&lt;&gt;"",E300&lt;&gt;"",E300&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6902,8 +6913,8 @@
       <c r="B301" s="55" t="n"/>
       <c r="C301" s="54" t="n"/>
       <c r="D301" s="54" t="n"/>
-      <c r="E301" s="56" t="n"/>
-      <c r="F301" s="56" t="n"/>
+      <c r="E301" s="61" t="n"/>
+      <c r="F301" s="61" t="n"/>
       <c r="G301" s="57">
         <f>IF(AND(D301&lt;&gt;"已完成",D301&lt;&gt;"",E301&lt;&gt;"",E301&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6916,8 +6927,8 @@
       <c r="B302" s="55" t="n"/>
       <c r="C302" s="54" t="n"/>
       <c r="D302" s="54" t="n"/>
-      <c r="E302" s="56" t="n"/>
-      <c r="F302" s="56" t="n"/>
+      <c r="E302" s="61" t="n"/>
+      <c r="F302" s="61" t="n"/>
       <c r="G302" s="57">
         <f>IF(AND(D302&lt;&gt;"已完成",D302&lt;&gt;"",E302&lt;&gt;"",E302&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6930,8 +6941,8 @@
       <c r="B303" s="55" t="n"/>
       <c r="C303" s="54" t="n"/>
       <c r="D303" s="54" t="n"/>
-      <c r="E303" s="56" t="n"/>
-      <c r="F303" s="56" t="n"/>
+      <c r="E303" s="61" t="n"/>
+      <c r="F303" s="61" t="n"/>
       <c r="G303" s="57">
         <f>IF(AND(D303&lt;&gt;"已完成",D303&lt;&gt;"",E303&lt;&gt;"",E303&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6944,8 +6955,8 @@
       <c r="B304" s="55" t="n"/>
       <c r="C304" s="54" t="n"/>
       <c r="D304" s="54" t="n"/>
-      <c r="E304" s="56" t="n"/>
-      <c r="F304" s="56" t="n"/>
+      <c r="E304" s="61" t="n"/>
+      <c r="F304" s="61" t="n"/>
       <c r="G304" s="57">
         <f>IF(AND(D304&lt;&gt;"已完成",D304&lt;&gt;"",E304&lt;&gt;"",E304&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6958,8 +6969,8 @@
       <c r="B305" s="55" t="n"/>
       <c r="C305" s="54" t="n"/>
       <c r="D305" s="54" t="n"/>
-      <c r="E305" s="56" t="n"/>
-      <c r="F305" s="56" t="n"/>
+      <c r="E305" s="61" t="n"/>
+      <c r="F305" s="61" t="n"/>
       <c r="G305" s="57">
         <f>IF(AND(D305&lt;&gt;"已完成",D305&lt;&gt;"",E305&lt;&gt;"",E305&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6972,8 +6983,8 @@
       <c r="B306" s="55" t="n"/>
       <c r="C306" s="54" t="n"/>
       <c r="D306" s="54" t="n"/>
-      <c r="E306" s="56" t="n"/>
-      <c r="F306" s="56" t="n"/>
+      <c r="E306" s="61" t="n"/>
+      <c r="F306" s="61" t="n"/>
       <c r="G306" s="57">
         <f>IF(AND(D306&lt;&gt;"已完成",D306&lt;&gt;"",E306&lt;&gt;"",E306&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -6986,8 +6997,8 @@
       <c r="B307" s="55" t="n"/>
       <c r="C307" s="54" t="n"/>
       <c r="D307" s="54" t="n"/>
-      <c r="E307" s="56" t="n"/>
-      <c r="F307" s="56" t="n"/>
+      <c r="E307" s="61" t="n"/>
+      <c r="F307" s="61" t="n"/>
       <c r="G307" s="57">
         <f>IF(AND(D307&lt;&gt;"已完成",D307&lt;&gt;"",E307&lt;&gt;"",E307&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7000,8 +7011,8 @@
       <c r="B308" s="55" t="n"/>
       <c r="C308" s="54" t="n"/>
       <c r="D308" s="54" t="n"/>
-      <c r="E308" s="56" t="n"/>
-      <c r="F308" s="56" t="n"/>
+      <c r="E308" s="61" t="n"/>
+      <c r="F308" s="61" t="n"/>
       <c r="G308" s="57">
         <f>IF(AND(D308&lt;&gt;"已完成",D308&lt;&gt;"",E308&lt;&gt;"",E308&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7014,8 +7025,8 @@
       <c r="B309" s="55" t="n"/>
       <c r="C309" s="54" t="n"/>
       <c r="D309" s="54" t="n"/>
-      <c r="E309" s="56" t="n"/>
-      <c r="F309" s="56" t="n"/>
+      <c r="E309" s="61" t="n"/>
+      <c r="F309" s="61" t="n"/>
       <c r="G309" s="57">
         <f>IF(AND(D309&lt;&gt;"已完成",D309&lt;&gt;"",E309&lt;&gt;"",E309&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7028,8 +7039,8 @@
       <c r="B310" s="55" t="n"/>
       <c r="C310" s="54" t="n"/>
       <c r="D310" s="54" t="n"/>
-      <c r="E310" s="56" t="n"/>
-      <c r="F310" s="56" t="n"/>
+      <c r="E310" s="61" t="n"/>
+      <c r="F310" s="61" t="n"/>
       <c r="G310" s="57">
         <f>IF(AND(D310&lt;&gt;"已完成",D310&lt;&gt;"",E310&lt;&gt;"",E310&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7042,8 +7053,8 @@
       <c r="B311" s="55" t="n"/>
       <c r="C311" s="54" t="n"/>
       <c r="D311" s="54" t="n"/>
-      <c r="E311" s="56" t="n"/>
-      <c r="F311" s="56" t="n"/>
+      <c r="E311" s="61" t="n"/>
+      <c r="F311" s="61" t="n"/>
       <c r="G311" s="57">
         <f>IF(AND(D311&lt;&gt;"已完成",D311&lt;&gt;"",E311&lt;&gt;"",E311&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7056,8 +7067,8 @@
       <c r="B312" s="55" t="n"/>
       <c r="C312" s="54" t="n"/>
       <c r="D312" s="54" t="n"/>
-      <c r="E312" s="56" t="n"/>
-      <c r="F312" s="56" t="n"/>
+      <c r="E312" s="61" t="n"/>
+      <c r="F312" s="61" t="n"/>
       <c r="G312" s="57">
         <f>IF(AND(D312&lt;&gt;"已完成",D312&lt;&gt;"",E312&lt;&gt;"",E312&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7070,8 +7081,8 @@
       <c r="B313" s="55" t="n"/>
       <c r="C313" s="54" t="n"/>
       <c r="D313" s="54" t="n"/>
-      <c r="E313" s="56" t="n"/>
-      <c r="F313" s="56" t="n"/>
+      <c r="E313" s="61" t="n"/>
+      <c r="F313" s="61" t="n"/>
       <c r="G313" s="57">
         <f>IF(AND(D313&lt;&gt;"已完成",D313&lt;&gt;"",E313&lt;&gt;"",E313&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7084,8 +7095,8 @@
       <c r="B314" s="55" t="n"/>
       <c r="C314" s="54" t="n"/>
       <c r="D314" s="54" t="n"/>
-      <c r="E314" s="56" t="n"/>
-      <c r="F314" s="56" t="n"/>
+      <c r="E314" s="61" t="n"/>
+      <c r="F314" s="61" t="n"/>
       <c r="G314" s="57">
         <f>IF(AND(D314&lt;&gt;"已完成",D314&lt;&gt;"",E314&lt;&gt;"",E314&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7098,8 +7109,8 @@
       <c r="B315" s="55" t="n"/>
       <c r="C315" s="54" t="n"/>
       <c r="D315" s="54" t="n"/>
-      <c r="E315" s="56" t="n"/>
-      <c r="F315" s="56" t="n"/>
+      <c r="E315" s="61" t="n"/>
+      <c r="F315" s="61" t="n"/>
       <c r="G315" s="57">
         <f>IF(AND(D315&lt;&gt;"已完成",D315&lt;&gt;"",E315&lt;&gt;"",E315&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7112,8 +7123,8 @@
       <c r="B316" s="55" t="n"/>
       <c r="C316" s="54" t="n"/>
       <c r="D316" s="54" t="n"/>
-      <c r="E316" s="56" t="n"/>
-      <c r="F316" s="56" t="n"/>
+      <c r="E316" s="61" t="n"/>
+      <c r="F316" s="61" t="n"/>
       <c r="G316" s="57">
         <f>IF(AND(D316&lt;&gt;"已完成",D316&lt;&gt;"",E316&lt;&gt;"",E316&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7126,8 +7137,8 @@
       <c r="B317" s="55" t="n"/>
       <c r="C317" s="54" t="n"/>
       <c r="D317" s="54" t="n"/>
-      <c r="E317" s="56" t="n"/>
-      <c r="F317" s="56" t="n"/>
+      <c r="E317" s="61" t="n"/>
+      <c r="F317" s="61" t="n"/>
       <c r="G317" s="57">
         <f>IF(AND(D317&lt;&gt;"已完成",D317&lt;&gt;"",E317&lt;&gt;"",E317&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7140,8 +7151,8 @@
       <c r="B318" s="55" t="n"/>
       <c r="C318" s="54" t="n"/>
       <c r="D318" s="54" t="n"/>
-      <c r="E318" s="56" t="n"/>
-      <c r="F318" s="56" t="n"/>
+      <c r="E318" s="61" t="n"/>
+      <c r="F318" s="61" t="n"/>
       <c r="G318" s="57">
         <f>IF(AND(D318&lt;&gt;"已完成",D318&lt;&gt;"",E318&lt;&gt;"",E318&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7154,8 +7165,8 @@
       <c r="B319" s="55" t="n"/>
       <c r="C319" s="54" t="n"/>
       <c r="D319" s="54" t="n"/>
-      <c r="E319" s="56" t="n"/>
-      <c r="F319" s="56" t="n"/>
+      <c r="E319" s="61" t="n"/>
+      <c r="F319" s="61" t="n"/>
       <c r="G319" s="57">
         <f>IF(AND(D319&lt;&gt;"已完成",D319&lt;&gt;"",E319&lt;&gt;"",E319&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7168,8 +7179,8 @@
       <c r="B320" s="55" t="n"/>
       <c r="C320" s="54" t="n"/>
       <c r="D320" s="54" t="n"/>
-      <c r="E320" s="56" t="n"/>
-      <c r="F320" s="56" t="n"/>
+      <c r="E320" s="61" t="n"/>
+      <c r="F320" s="61" t="n"/>
       <c r="G320" s="57">
         <f>IF(AND(D320&lt;&gt;"已完成",D320&lt;&gt;"",E320&lt;&gt;"",E320&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7182,8 +7193,8 @@
       <c r="B321" s="55" t="n"/>
       <c r="C321" s="54" t="n"/>
       <c r="D321" s="54" t="n"/>
-      <c r="E321" s="56" t="n"/>
-      <c r="F321" s="56" t="n"/>
+      <c r="E321" s="61" t="n"/>
+      <c r="F321" s="61" t="n"/>
       <c r="G321" s="57">
         <f>IF(AND(D321&lt;&gt;"已完成",D321&lt;&gt;"",E321&lt;&gt;"",E321&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7196,8 +7207,8 @@
       <c r="B322" s="55" t="n"/>
       <c r="C322" s="54" t="n"/>
       <c r="D322" s="54" t="n"/>
-      <c r="E322" s="56" t="n"/>
-      <c r="F322" s="56" t="n"/>
+      <c r="E322" s="61" t="n"/>
+      <c r="F322" s="61" t="n"/>
       <c r="G322" s="57">
         <f>IF(AND(D322&lt;&gt;"已完成",D322&lt;&gt;"",E322&lt;&gt;"",E322&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7210,8 +7221,8 @@
       <c r="B323" s="55" t="n"/>
       <c r="C323" s="54" t="n"/>
       <c r="D323" s="54" t="n"/>
-      <c r="E323" s="56" t="n"/>
-      <c r="F323" s="56" t="n"/>
+      <c r="E323" s="61" t="n"/>
+      <c r="F323" s="61" t="n"/>
       <c r="G323" s="57">
         <f>IF(AND(D323&lt;&gt;"已完成",D323&lt;&gt;"",E323&lt;&gt;"",E323&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7224,8 +7235,8 @@
       <c r="B324" s="55" t="n"/>
       <c r="C324" s="54" t="n"/>
       <c r="D324" s="54" t="n"/>
-      <c r="E324" s="56" t="n"/>
-      <c r="F324" s="56" t="n"/>
+      <c r="E324" s="61" t="n"/>
+      <c r="F324" s="61" t="n"/>
       <c r="G324" s="57">
         <f>IF(AND(D324&lt;&gt;"已完成",D324&lt;&gt;"",E324&lt;&gt;"",E324&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7238,8 +7249,8 @@
       <c r="B325" s="55" t="n"/>
       <c r="C325" s="54" t="n"/>
       <c r="D325" s="54" t="n"/>
-      <c r="E325" s="56" t="n"/>
-      <c r="F325" s="56" t="n"/>
+      <c r="E325" s="61" t="n"/>
+      <c r="F325" s="61" t="n"/>
       <c r="G325" s="57">
         <f>IF(AND(D325&lt;&gt;"已完成",D325&lt;&gt;"",E325&lt;&gt;"",E325&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7252,8 +7263,8 @@
       <c r="B326" s="55" t="n"/>
       <c r="C326" s="54" t="n"/>
       <c r="D326" s="54" t="n"/>
-      <c r="E326" s="56" t="n"/>
-      <c r="F326" s="56" t="n"/>
+      <c r="E326" s="61" t="n"/>
+      <c r="F326" s="61" t="n"/>
       <c r="G326" s="57">
         <f>IF(AND(D326&lt;&gt;"已完成",D326&lt;&gt;"",E326&lt;&gt;"",E326&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7266,8 +7277,8 @@
       <c r="B327" s="55" t="n"/>
       <c r="C327" s="54" t="n"/>
       <c r="D327" s="54" t="n"/>
-      <c r="E327" s="56" t="n"/>
-      <c r="F327" s="56" t="n"/>
+      <c r="E327" s="61" t="n"/>
+      <c r="F327" s="61" t="n"/>
       <c r="G327" s="57">
         <f>IF(AND(D327&lt;&gt;"已完成",D327&lt;&gt;"",E327&lt;&gt;"",E327&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7280,8 +7291,8 @@
       <c r="B328" s="55" t="n"/>
       <c r="C328" s="54" t="n"/>
       <c r="D328" s="54" t="n"/>
-      <c r="E328" s="56" t="n"/>
-      <c r="F328" s="56" t="n"/>
+      <c r="E328" s="61" t="n"/>
+      <c r="F328" s="61" t="n"/>
       <c r="G328" s="57">
         <f>IF(AND(D328&lt;&gt;"已完成",D328&lt;&gt;"",E328&lt;&gt;"",E328&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7294,8 +7305,8 @@
       <c r="B329" s="55" t="n"/>
       <c r="C329" s="54" t="n"/>
       <c r="D329" s="54" t="n"/>
-      <c r="E329" s="56" t="n"/>
-      <c r="F329" s="56" t="n"/>
+      <c r="E329" s="61" t="n"/>
+      <c r="F329" s="61" t="n"/>
       <c r="G329" s="57">
         <f>IF(AND(D329&lt;&gt;"已完成",D329&lt;&gt;"",E329&lt;&gt;"",E329&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7308,8 +7319,8 @@
       <c r="B330" s="55" t="n"/>
       <c r="C330" s="54" t="n"/>
       <c r="D330" s="54" t="n"/>
-      <c r="E330" s="56" t="n"/>
-      <c r="F330" s="56" t="n"/>
+      <c r="E330" s="61" t="n"/>
+      <c r="F330" s="61" t="n"/>
       <c r="G330" s="57">
         <f>IF(AND(D330&lt;&gt;"已完成",D330&lt;&gt;"",E330&lt;&gt;"",E330&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7322,8 +7333,8 @@
       <c r="B331" s="55" t="n"/>
       <c r="C331" s="54" t="n"/>
       <c r="D331" s="54" t="n"/>
-      <c r="E331" s="56" t="n"/>
-      <c r="F331" s="56" t="n"/>
+      <c r="E331" s="61" t="n"/>
+      <c r="F331" s="61" t="n"/>
       <c r="G331" s="57">
         <f>IF(AND(D331&lt;&gt;"已完成",D331&lt;&gt;"",E331&lt;&gt;"",E331&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7336,8 +7347,8 @@
       <c r="B332" s="55" t="n"/>
       <c r="C332" s="54" t="n"/>
       <c r="D332" s="54" t="n"/>
-      <c r="E332" s="56" t="n"/>
-      <c r="F332" s="56" t="n"/>
+      <c r="E332" s="61" t="n"/>
+      <c r="F332" s="61" t="n"/>
       <c r="G332" s="57">
         <f>IF(AND(D332&lt;&gt;"已完成",D332&lt;&gt;"",E332&lt;&gt;"",E332&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7350,8 +7361,8 @@
       <c r="B333" s="55" t="n"/>
       <c r="C333" s="54" t="n"/>
       <c r="D333" s="54" t="n"/>
-      <c r="E333" s="56" t="n"/>
-      <c r="F333" s="56" t="n"/>
+      <c r="E333" s="61" t="n"/>
+      <c r="F333" s="61" t="n"/>
       <c r="G333" s="57">
         <f>IF(AND(D333&lt;&gt;"已完成",D333&lt;&gt;"",E333&lt;&gt;"",E333&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7364,8 +7375,8 @@
       <c r="B334" s="55" t="n"/>
       <c r="C334" s="54" t="n"/>
       <c r="D334" s="54" t="n"/>
-      <c r="E334" s="56" t="n"/>
-      <c r="F334" s="56" t="n"/>
+      <c r="E334" s="61" t="n"/>
+      <c r="F334" s="61" t="n"/>
       <c r="G334" s="57">
         <f>IF(AND(D334&lt;&gt;"已完成",D334&lt;&gt;"",E334&lt;&gt;"",E334&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7378,8 +7389,8 @@
       <c r="B335" s="55" t="n"/>
       <c r="C335" s="54" t="n"/>
       <c r="D335" s="54" t="n"/>
-      <c r="E335" s="56" t="n"/>
-      <c r="F335" s="56" t="n"/>
+      <c r="E335" s="61" t="n"/>
+      <c r="F335" s="61" t="n"/>
       <c r="G335" s="57">
         <f>IF(AND(D335&lt;&gt;"已完成",D335&lt;&gt;"",E335&lt;&gt;"",E335&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7392,8 +7403,8 @@
       <c r="B336" s="55" t="n"/>
       <c r="C336" s="54" t="n"/>
       <c r="D336" s="54" t="n"/>
-      <c r="E336" s="56" t="n"/>
-      <c r="F336" s="56" t="n"/>
+      <c r="E336" s="61" t="n"/>
+      <c r="F336" s="61" t="n"/>
       <c r="G336" s="57">
         <f>IF(AND(D336&lt;&gt;"已完成",D336&lt;&gt;"",E336&lt;&gt;"",E336&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7406,8 +7417,8 @@
       <c r="B337" s="55" t="n"/>
       <c r="C337" s="54" t="n"/>
       <c r="D337" s="54" t="n"/>
-      <c r="E337" s="56" t="n"/>
-      <c r="F337" s="56" t="n"/>
+      <c r="E337" s="61" t="n"/>
+      <c r="F337" s="61" t="n"/>
       <c r="G337" s="57">
         <f>IF(AND(D337&lt;&gt;"已完成",D337&lt;&gt;"",E337&lt;&gt;"",E337&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7420,8 +7431,8 @@
       <c r="B338" s="55" t="n"/>
       <c r="C338" s="54" t="n"/>
       <c r="D338" s="54" t="n"/>
-      <c r="E338" s="56" t="n"/>
-      <c r="F338" s="56" t="n"/>
+      <c r="E338" s="61" t="n"/>
+      <c r="F338" s="61" t="n"/>
       <c r="G338" s="57">
         <f>IF(AND(D338&lt;&gt;"已完成",D338&lt;&gt;"",E338&lt;&gt;"",E338&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7434,8 +7445,8 @@
       <c r="B339" s="55" t="n"/>
       <c r="C339" s="54" t="n"/>
       <c r="D339" s="54" t="n"/>
-      <c r="E339" s="56" t="n"/>
-      <c r="F339" s="56" t="n"/>
+      <c r="E339" s="61" t="n"/>
+      <c r="F339" s="61" t="n"/>
       <c r="G339" s="57">
         <f>IF(AND(D339&lt;&gt;"已完成",D339&lt;&gt;"",E339&lt;&gt;"",E339&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7448,8 +7459,8 @@
       <c r="B340" s="55" t="n"/>
       <c r="C340" s="54" t="n"/>
       <c r="D340" s="54" t="n"/>
-      <c r="E340" s="56" t="n"/>
-      <c r="F340" s="56" t="n"/>
+      <c r="E340" s="61" t="n"/>
+      <c r="F340" s="61" t="n"/>
       <c r="G340" s="57">
         <f>IF(AND(D340&lt;&gt;"已完成",D340&lt;&gt;"",E340&lt;&gt;"",E340&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7462,8 +7473,8 @@
       <c r="B341" s="55" t="n"/>
       <c r="C341" s="54" t="n"/>
       <c r="D341" s="54" t="n"/>
-      <c r="E341" s="56" t="n"/>
-      <c r="F341" s="56" t="n"/>
+      <c r="E341" s="61" t="n"/>
+      <c r="F341" s="61" t="n"/>
       <c r="G341" s="57">
         <f>IF(AND(D341&lt;&gt;"已完成",D341&lt;&gt;"",E341&lt;&gt;"",E341&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7476,8 +7487,8 @@
       <c r="B342" s="55" t="n"/>
       <c r="C342" s="54" t="n"/>
       <c r="D342" s="54" t="n"/>
-      <c r="E342" s="56" t="n"/>
-      <c r="F342" s="56" t="n"/>
+      <c r="E342" s="61" t="n"/>
+      <c r="F342" s="61" t="n"/>
       <c r="G342" s="57">
         <f>IF(AND(D342&lt;&gt;"已完成",D342&lt;&gt;"",E342&lt;&gt;"",E342&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7490,8 +7501,8 @@
       <c r="B343" s="55" t="n"/>
       <c r="C343" s="54" t="n"/>
       <c r="D343" s="54" t="n"/>
-      <c r="E343" s="56" t="n"/>
-      <c r="F343" s="56" t="n"/>
+      <c r="E343" s="61" t="n"/>
+      <c r="F343" s="61" t="n"/>
       <c r="G343" s="57">
         <f>IF(AND(D343&lt;&gt;"已完成",D343&lt;&gt;"",E343&lt;&gt;"",E343&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7504,8 +7515,8 @@
       <c r="B344" s="55" t="n"/>
       <c r="C344" s="54" t="n"/>
       <c r="D344" s="54" t="n"/>
-      <c r="E344" s="56" t="n"/>
-      <c r="F344" s="56" t="n"/>
+      <c r="E344" s="61" t="n"/>
+      <c r="F344" s="61" t="n"/>
       <c r="G344" s="57">
         <f>IF(AND(D344&lt;&gt;"已完成",D344&lt;&gt;"",E344&lt;&gt;"",E344&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7518,8 +7529,8 @@
       <c r="B345" s="55" t="n"/>
       <c r="C345" s="54" t="n"/>
       <c r="D345" s="54" t="n"/>
-      <c r="E345" s="56" t="n"/>
-      <c r="F345" s="56" t="n"/>
+      <c r="E345" s="61" t="n"/>
+      <c r="F345" s="61" t="n"/>
       <c r="G345" s="57">
         <f>IF(AND(D345&lt;&gt;"已完成",D345&lt;&gt;"",E345&lt;&gt;"",E345&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7532,8 +7543,8 @@
       <c r="B346" s="55" t="n"/>
       <c r="C346" s="54" t="n"/>
       <c r="D346" s="54" t="n"/>
-      <c r="E346" s="56" t="n"/>
-      <c r="F346" s="56" t="n"/>
+      <c r="E346" s="61" t="n"/>
+      <c r="F346" s="61" t="n"/>
       <c r="G346" s="57">
         <f>IF(AND(D346&lt;&gt;"已完成",D346&lt;&gt;"",E346&lt;&gt;"",E346&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7546,8 +7557,8 @@
       <c r="B347" s="55" t="n"/>
       <c r="C347" s="54" t="n"/>
       <c r="D347" s="54" t="n"/>
-      <c r="E347" s="56" t="n"/>
-      <c r="F347" s="56" t="n"/>
+      <c r="E347" s="61" t="n"/>
+      <c r="F347" s="61" t="n"/>
       <c r="G347" s="57">
         <f>IF(AND(D347&lt;&gt;"已完成",D347&lt;&gt;"",E347&lt;&gt;"",E347&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7560,8 +7571,8 @@
       <c r="B348" s="55" t="n"/>
       <c r="C348" s="54" t="n"/>
       <c r="D348" s="54" t="n"/>
-      <c r="E348" s="56" t="n"/>
-      <c r="F348" s="56" t="n"/>
+      <c r="E348" s="61" t="n"/>
+      <c r="F348" s="61" t="n"/>
       <c r="G348" s="57">
         <f>IF(AND(D348&lt;&gt;"已完成",D348&lt;&gt;"",E348&lt;&gt;"",E348&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7574,8 +7585,8 @@
       <c r="B349" s="55" t="n"/>
       <c r="C349" s="54" t="n"/>
       <c r="D349" s="54" t="n"/>
-      <c r="E349" s="56" t="n"/>
-      <c r="F349" s="56" t="n"/>
+      <c r="E349" s="61" t="n"/>
+      <c r="F349" s="61" t="n"/>
       <c r="G349" s="57">
         <f>IF(AND(D349&lt;&gt;"已完成",D349&lt;&gt;"",E349&lt;&gt;"",E349&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7588,8 +7599,8 @@
       <c r="B350" s="55" t="n"/>
       <c r="C350" s="54" t="n"/>
       <c r="D350" s="54" t="n"/>
-      <c r="E350" s="56" t="n"/>
-      <c r="F350" s="56" t="n"/>
+      <c r="E350" s="61" t="n"/>
+      <c r="F350" s="61" t="n"/>
       <c r="G350" s="57">
         <f>IF(AND(D350&lt;&gt;"已完成",D350&lt;&gt;"",E350&lt;&gt;"",E350&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7602,8 +7613,8 @@
       <c r="B351" s="55" t="n"/>
       <c r="C351" s="54" t="n"/>
       <c r="D351" s="54" t="n"/>
-      <c r="E351" s="56" t="n"/>
-      <c r="F351" s="56" t="n"/>
+      <c r="E351" s="61" t="n"/>
+      <c r="F351" s="61" t="n"/>
       <c r="G351" s="57">
         <f>IF(AND(D351&lt;&gt;"已完成",D351&lt;&gt;"",E351&lt;&gt;"",E351&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7616,8 +7627,8 @@
       <c r="B352" s="55" t="n"/>
       <c r="C352" s="54" t="n"/>
       <c r="D352" s="54" t="n"/>
-      <c r="E352" s="56" t="n"/>
-      <c r="F352" s="56" t="n"/>
+      <c r="E352" s="61" t="n"/>
+      <c r="F352" s="61" t="n"/>
       <c r="G352" s="57">
         <f>IF(AND(D352&lt;&gt;"已完成",D352&lt;&gt;"",E352&lt;&gt;"",E352&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7630,8 +7641,8 @@
       <c r="B353" s="55" t="n"/>
       <c r="C353" s="54" t="n"/>
       <c r="D353" s="54" t="n"/>
-      <c r="E353" s="56" t="n"/>
-      <c r="F353" s="56" t="n"/>
+      <c r="E353" s="61" t="n"/>
+      <c r="F353" s="61" t="n"/>
       <c r="G353" s="57">
         <f>IF(AND(D353&lt;&gt;"已完成",D353&lt;&gt;"",E353&lt;&gt;"",E353&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7644,8 +7655,8 @@
       <c r="B354" s="55" t="n"/>
       <c r="C354" s="54" t="n"/>
       <c r="D354" s="54" t="n"/>
-      <c r="E354" s="56" t="n"/>
-      <c r="F354" s="56" t="n"/>
+      <c r="E354" s="61" t="n"/>
+      <c r="F354" s="61" t="n"/>
       <c r="G354" s="57">
         <f>IF(AND(D354&lt;&gt;"已完成",D354&lt;&gt;"",E354&lt;&gt;"",E354&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7658,8 +7669,8 @@
       <c r="B355" s="55" t="n"/>
       <c r="C355" s="54" t="n"/>
       <c r="D355" s="54" t="n"/>
-      <c r="E355" s="56" t="n"/>
-      <c r="F355" s="56" t="n"/>
+      <c r="E355" s="61" t="n"/>
+      <c r="F355" s="61" t="n"/>
       <c r="G355" s="57">
         <f>IF(AND(D355&lt;&gt;"已完成",D355&lt;&gt;"",E355&lt;&gt;"",E355&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7672,8 +7683,8 @@
       <c r="B356" s="55" t="n"/>
       <c r="C356" s="54" t="n"/>
       <c r="D356" s="54" t="n"/>
-      <c r="E356" s="56" t="n"/>
-      <c r="F356" s="56" t="n"/>
+      <c r="E356" s="61" t="n"/>
+      <c r="F356" s="61" t="n"/>
       <c r="G356" s="57">
         <f>IF(AND(D356&lt;&gt;"已完成",D356&lt;&gt;"",E356&lt;&gt;"",E356&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7686,8 +7697,8 @@
       <c r="B357" s="55" t="n"/>
       <c r="C357" s="54" t="n"/>
       <c r="D357" s="54" t="n"/>
-      <c r="E357" s="56" t="n"/>
-      <c r="F357" s="56" t="n"/>
+      <c r="E357" s="61" t="n"/>
+      <c r="F357" s="61" t="n"/>
       <c r="G357" s="57">
         <f>IF(AND(D357&lt;&gt;"已完成",D357&lt;&gt;"",E357&lt;&gt;"",E357&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7700,8 +7711,8 @@
       <c r="B358" s="55" t="n"/>
       <c r="C358" s="54" t="n"/>
       <c r="D358" s="54" t="n"/>
-      <c r="E358" s="56" t="n"/>
-      <c r="F358" s="56" t="n"/>
+      <c r="E358" s="61" t="n"/>
+      <c r="F358" s="61" t="n"/>
       <c r="G358" s="57">
         <f>IF(AND(D358&lt;&gt;"已完成",D358&lt;&gt;"",E358&lt;&gt;"",E358&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7714,8 +7725,8 @@
       <c r="B359" s="55" t="n"/>
       <c r="C359" s="54" t="n"/>
       <c r="D359" s="54" t="n"/>
-      <c r="E359" s="56" t="n"/>
-      <c r="F359" s="56" t="n"/>
+      <c r="E359" s="61" t="n"/>
+      <c r="F359" s="61" t="n"/>
       <c r="G359" s="57">
         <f>IF(AND(D359&lt;&gt;"已完成",D359&lt;&gt;"",E359&lt;&gt;"",E359&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7728,8 +7739,8 @@
       <c r="B360" s="55" t="n"/>
       <c r="C360" s="54" t="n"/>
       <c r="D360" s="54" t="n"/>
-      <c r="E360" s="56" t="n"/>
-      <c r="F360" s="56" t="n"/>
+      <c r="E360" s="61" t="n"/>
+      <c r="F360" s="61" t="n"/>
       <c r="G360" s="57">
         <f>IF(AND(D360&lt;&gt;"已完成",D360&lt;&gt;"",E360&lt;&gt;"",E360&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7742,8 +7753,8 @@
       <c r="B361" s="55" t="n"/>
       <c r="C361" s="54" t="n"/>
       <c r="D361" s="54" t="n"/>
-      <c r="E361" s="56" t="n"/>
-      <c r="F361" s="56" t="n"/>
+      <c r="E361" s="61" t="n"/>
+      <c r="F361" s="61" t="n"/>
       <c r="G361" s="57">
         <f>IF(AND(D361&lt;&gt;"已完成",D361&lt;&gt;"",E361&lt;&gt;"",E361&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7756,8 +7767,8 @@
       <c r="B362" s="55" t="n"/>
       <c r="C362" s="54" t="n"/>
       <c r="D362" s="54" t="n"/>
-      <c r="E362" s="56" t="n"/>
-      <c r="F362" s="56" t="n"/>
+      <c r="E362" s="61" t="n"/>
+      <c r="F362" s="61" t="n"/>
       <c r="G362" s="57">
         <f>IF(AND(D362&lt;&gt;"已完成",D362&lt;&gt;"",E362&lt;&gt;"",E362&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7770,8 +7781,8 @@
       <c r="B363" s="55" t="n"/>
       <c r="C363" s="54" t="n"/>
       <c r="D363" s="54" t="n"/>
-      <c r="E363" s="56" t="n"/>
-      <c r="F363" s="56" t="n"/>
+      <c r="E363" s="61" t="n"/>
+      <c r="F363" s="61" t="n"/>
       <c r="G363" s="57">
         <f>IF(AND(D363&lt;&gt;"已完成",D363&lt;&gt;"",E363&lt;&gt;"",E363&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7784,8 +7795,8 @@
       <c r="B364" s="55" t="n"/>
       <c r="C364" s="54" t="n"/>
       <c r="D364" s="54" t="n"/>
-      <c r="E364" s="56" t="n"/>
-      <c r="F364" s="56" t="n"/>
+      <c r="E364" s="61" t="n"/>
+      <c r="F364" s="61" t="n"/>
       <c r="G364" s="57">
         <f>IF(AND(D364&lt;&gt;"已完成",D364&lt;&gt;"",E364&lt;&gt;"",E364&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7798,8 +7809,8 @@
       <c r="B365" s="55" t="n"/>
       <c r="C365" s="54" t="n"/>
       <c r="D365" s="54" t="n"/>
-      <c r="E365" s="56" t="n"/>
-      <c r="F365" s="56" t="n"/>
+      <c r="E365" s="61" t="n"/>
+      <c r="F365" s="61" t="n"/>
       <c r="G365" s="57">
         <f>IF(AND(D365&lt;&gt;"已完成",D365&lt;&gt;"",E365&lt;&gt;"",E365&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7812,8 +7823,8 @@
       <c r="B366" s="55" t="n"/>
       <c r="C366" s="54" t="n"/>
       <c r="D366" s="54" t="n"/>
-      <c r="E366" s="56" t="n"/>
-      <c r="F366" s="56" t="n"/>
+      <c r="E366" s="61" t="n"/>
+      <c r="F366" s="61" t="n"/>
       <c r="G366" s="57">
         <f>IF(AND(D366&lt;&gt;"已完成",D366&lt;&gt;"",E366&lt;&gt;"",E366&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7826,8 +7837,8 @@
       <c r="B367" s="55" t="n"/>
       <c r="C367" s="54" t="n"/>
       <c r="D367" s="54" t="n"/>
-      <c r="E367" s="56" t="n"/>
-      <c r="F367" s="56" t="n"/>
+      <c r="E367" s="61" t="n"/>
+      <c r="F367" s="61" t="n"/>
       <c r="G367" s="57">
         <f>IF(AND(D367&lt;&gt;"已完成",D367&lt;&gt;"",E367&lt;&gt;"",E367&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7840,8 +7851,8 @@
       <c r="B368" s="55" t="n"/>
       <c r="C368" s="54" t="n"/>
       <c r="D368" s="54" t="n"/>
-      <c r="E368" s="56" t="n"/>
-      <c r="F368" s="56" t="n"/>
+      <c r="E368" s="61" t="n"/>
+      <c r="F368" s="61" t="n"/>
       <c r="G368" s="57">
         <f>IF(AND(D368&lt;&gt;"已完成",D368&lt;&gt;"",E368&lt;&gt;"",E368&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7854,8 +7865,8 @@
       <c r="B369" s="55" t="n"/>
       <c r="C369" s="54" t="n"/>
       <c r="D369" s="54" t="n"/>
-      <c r="E369" s="56" t="n"/>
-      <c r="F369" s="56" t="n"/>
+      <c r="E369" s="61" t="n"/>
+      <c r="F369" s="61" t="n"/>
       <c r="G369" s="57">
         <f>IF(AND(D369&lt;&gt;"已完成",D369&lt;&gt;"",E369&lt;&gt;"",E369&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7868,8 +7879,8 @@
       <c r="B370" s="55" t="n"/>
       <c r="C370" s="54" t="n"/>
       <c r="D370" s="54" t="n"/>
-      <c r="E370" s="56" t="n"/>
-      <c r="F370" s="56" t="n"/>
+      <c r="E370" s="61" t="n"/>
+      <c r="F370" s="61" t="n"/>
       <c r="G370" s="57">
         <f>IF(AND(D370&lt;&gt;"已完成",D370&lt;&gt;"",E370&lt;&gt;"",E370&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7882,8 +7893,8 @@
       <c r="B371" s="55" t="n"/>
       <c r="C371" s="54" t="n"/>
       <c r="D371" s="54" t="n"/>
-      <c r="E371" s="56" t="n"/>
-      <c r="F371" s="56" t="n"/>
+      <c r="E371" s="61" t="n"/>
+      <c r="F371" s="61" t="n"/>
       <c r="G371" s="57">
         <f>IF(AND(D371&lt;&gt;"已完成",D371&lt;&gt;"",E371&lt;&gt;"",E371&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7896,8 +7907,8 @@
       <c r="B372" s="55" t="n"/>
       <c r="C372" s="54" t="n"/>
       <c r="D372" s="54" t="n"/>
-      <c r="E372" s="56" t="n"/>
-      <c r="F372" s="56" t="n"/>
+      <c r="E372" s="61" t="n"/>
+      <c r="F372" s="61" t="n"/>
       <c r="G372" s="57">
         <f>IF(AND(D372&lt;&gt;"已完成",D372&lt;&gt;"",E372&lt;&gt;"",E372&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7910,8 +7921,8 @@
       <c r="B373" s="55" t="n"/>
       <c r="C373" s="54" t="n"/>
       <c r="D373" s="54" t="n"/>
-      <c r="E373" s="56" t="n"/>
-      <c r="F373" s="56" t="n"/>
+      <c r="E373" s="61" t="n"/>
+      <c r="F373" s="61" t="n"/>
       <c r="G373" s="57">
         <f>IF(AND(D373&lt;&gt;"已完成",D373&lt;&gt;"",E373&lt;&gt;"",E373&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7924,8 +7935,8 @@
       <c r="B374" s="55" t="n"/>
       <c r="C374" s="54" t="n"/>
       <c r="D374" s="54" t="n"/>
-      <c r="E374" s="56" t="n"/>
-      <c r="F374" s="56" t="n"/>
+      <c r="E374" s="61" t="n"/>
+      <c r="F374" s="61" t="n"/>
       <c r="G374" s="57">
         <f>IF(AND(D374&lt;&gt;"已完成",D374&lt;&gt;"",E374&lt;&gt;"",E374&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7938,8 +7949,8 @@
       <c r="B375" s="55" t="n"/>
       <c r="C375" s="54" t="n"/>
       <c r="D375" s="54" t="n"/>
-      <c r="E375" s="56" t="n"/>
-      <c r="F375" s="56" t="n"/>
+      <c r="E375" s="61" t="n"/>
+      <c r="F375" s="61" t="n"/>
       <c r="G375" s="57">
         <f>IF(AND(D375&lt;&gt;"已完成",D375&lt;&gt;"",E375&lt;&gt;"",E375&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7952,8 +7963,8 @@
       <c r="B376" s="55" t="n"/>
       <c r="C376" s="54" t="n"/>
       <c r="D376" s="54" t="n"/>
-      <c r="E376" s="56" t="n"/>
-      <c r="F376" s="56" t="n"/>
+      <c r="E376" s="61" t="n"/>
+      <c r="F376" s="61" t="n"/>
       <c r="G376" s="57">
         <f>IF(AND(D376&lt;&gt;"已完成",D376&lt;&gt;"",E376&lt;&gt;"",E376&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7966,8 +7977,8 @@
       <c r="B377" s="55" t="n"/>
       <c r="C377" s="54" t="n"/>
       <c r="D377" s="54" t="n"/>
-      <c r="E377" s="56" t="n"/>
-      <c r="F377" s="56" t="n"/>
+      <c r="E377" s="61" t="n"/>
+      <c r="F377" s="61" t="n"/>
       <c r="G377" s="57">
         <f>IF(AND(D377&lt;&gt;"已完成",D377&lt;&gt;"",E377&lt;&gt;"",E377&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7980,8 +7991,8 @@
       <c r="B378" s="55" t="n"/>
       <c r="C378" s="54" t="n"/>
       <c r="D378" s="54" t="n"/>
-      <c r="E378" s="56" t="n"/>
-      <c r="F378" s="56" t="n"/>
+      <c r="E378" s="61" t="n"/>
+      <c r="F378" s="61" t="n"/>
       <c r="G378" s="57">
         <f>IF(AND(D378&lt;&gt;"已完成",D378&lt;&gt;"",E378&lt;&gt;"",E378&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -7994,8 +8005,8 @@
       <c r="B379" s="55" t="n"/>
       <c r="C379" s="54" t="n"/>
       <c r="D379" s="54" t="n"/>
-      <c r="E379" s="56" t="n"/>
-      <c r="F379" s="56" t="n"/>
+      <c r="E379" s="61" t="n"/>
+      <c r="F379" s="61" t="n"/>
       <c r="G379" s="57">
         <f>IF(AND(D379&lt;&gt;"已完成",D379&lt;&gt;"",E379&lt;&gt;"",E379&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8008,8 +8019,8 @@
       <c r="B380" s="55" t="n"/>
       <c r="C380" s="54" t="n"/>
       <c r="D380" s="54" t="n"/>
-      <c r="E380" s="56" t="n"/>
-      <c r="F380" s="56" t="n"/>
+      <c r="E380" s="61" t="n"/>
+      <c r="F380" s="61" t="n"/>
       <c r="G380" s="57">
         <f>IF(AND(D380&lt;&gt;"已完成",D380&lt;&gt;"",E380&lt;&gt;"",E380&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8022,8 +8033,8 @@
       <c r="B381" s="55" t="n"/>
       <c r="C381" s="54" t="n"/>
       <c r="D381" s="54" t="n"/>
-      <c r="E381" s="56" t="n"/>
-      <c r="F381" s="56" t="n"/>
+      <c r="E381" s="61" t="n"/>
+      <c r="F381" s="61" t="n"/>
       <c r="G381" s="57">
         <f>IF(AND(D381&lt;&gt;"已完成",D381&lt;&gt;"",E381&lt;&gt;"",E381&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8036,8 +8047,8 @@
       <c r="B382" s="55" t="n"/>
       <c r="C382" s="54" t="n"/>
       <c r="D382" s="54" t="n"/>
-      <c r="E382" s="56" t="n"/>
-      <c r="F382" s="56" t="n"/>
+      <c r="E382" s="61" t="n"/>
+      <c r="F382" s="61" t="n"/>
       <c r="G382" s="57">
         <f>IF(AND(D382&lt;&gt;"已完成",D382&lt;&gt;"",E382&lt;&gt;"",E382&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8050,8 +8061,8 @@
       <c r="B383" s="55" t="n"/>
       <c r="C383" s="54" t="n"/>
       <c r="D383" s="54" t="n"/>
-      <c r="E383" s="56" t="n"/>
-      <c r="F383" s="56" t="n"/>
+      <c r="E383" s="61" t="n"/>
+      <c r="F383" s="61" t="n"/>
       <c r="G383" s="57">
         <f>IF(AND(D383&lt;&gt;"已完成",D383&lt;&gt;"",E383&lt;&gt;"",E383&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8064,8 +8075,8 @@
       <c r="B384" s="55" t="n"/>
       <c r="C384" s="54" t="n"/>
       <c r="D384" s="54" t="n"/>
-      <c r="E384" s="56" t="n"/>
-      <c r="F384" s="56" t="n"/>
+      <c r="E384" s="61" t="n"/>
+      <c r="F384" s="61" t="n"/>
       <c r="G384" s="57">
         <f>IF(AND(D384&lt;&gt;"已完成",D384&lt;&gt;"",E384&lt;&gt;"",E384&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8078,8 +8089,8 @@
       <c r="B385" s="55" t="n"/>
       <c r="C385" s="54" t="n"/>
       <c r="D385" s="54" t="n"/>
-      <c r="E385" s="56" t="n"/>
-      <c r="F385" s="56" t="n"/>
+      <c r="E385" s="61" t="n"/>
+      <c r="F385" s="61" t="n"/>
       <c r="G385" s="57">
         <f>IF(AND(D385&lt;&gt;"已完成",D385&lt;&gt;"",E385&lt;&gt;"",E385&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8092,8 +8103,8 @@
       <c r="B386" s="55" t="n"/>
       <c r="C386" s="54" t="n"/>
       <c r="D386" s="54" t="n"/>
-      <c r="E386" s="56" t="n"/>
-      <c r="F386" s="56" t="n"/>
+      <c r="E386" s="61" t="n"/>
+      <c r="F386" s="61" t="n"/>
       <c r="G386" s="57">
         <f>IF(AND(D386&lt;&gt;"已完成",D386&lt;&gt;"",E386&lt;&gt;"",E386&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8106,8 +8117,8 @@
       <c r="B387" s="55" t="n"/>
       <c r="C387" s="54" t="n"/>
       <c r="D387" s="54" t="n"/>
-      <c r="E387" s="56" t="n"/>
-      <c r="F387" s="56" t="n"/>
+      <c r="E387" s="61" t="n"/>
+      <c r="F387" s="61" t="n"/>
       <c r="G387" s="57">
         <f>IF(AND(D387&lt;&gt;"已完成",D387&lt;&gt;"",E387&lt;&gt;"",E387&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8120,8 +8131,8 @@
       <c r="B388" s="55" t="n"/>
       <c r="C388" s="54" t="n"/>
       <c r="D388" s="54" t="n"/>
-      <c r="E388" s="56" t="n"/>
-      <c r="F388" s="56" t="n"/>
+      <c r="E388" s="61" t="n"/>
+      <c r="F388" s="61" t="n"/>
       <c r="G388" s="57">
         <f>IF(AND(D388&lt;&gt;"已完成",D388&lt;&gt;"",E388&lt;&gt;"",E388&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8134,8 +8145,8 @@
       <c r="B389" s="55" t="n"/>
       <c r="C389" s="54" t="n"/>
       <c r="D389" s="54" t="n"/>
-      <c r="E389" s="56" t="n"/>
-      <c r="F389" s="56" t="n"/>
+      <c r="E389" s="61" t="n"/>
+      <c r="F389" s="61" t="n"/>
       <c r="G389" s="57">
         <f>IF(AND(D389&lt;&gt;"已完成",D389&lt;&gt;"",E389&lt;&gt;"",E389&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8148,8 +8159,8 @@
       <c r="B390" s="55" t="n"/>
       <c r="C390" s="54" t="n"/>
       <c r="D390" s="54" t="n"/>
-      <c r="E390" s="56" t="n"/>
-      <c r="F390" s="56" t="n"/>
+      <c r="E390" s="61" t="n"/>
+      <c r="F390" s="61" t="n"/>
       <c r="G390" s="57">
         <f>IF(AND(D390&lt;&gt;"已完成",D390&lt;&gt;"",E390&lt;&gt;"",E390&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8162,8 +8173,8 @@
       <c r="B391" s="55" t="n"/>
       <c r="C391" s="54" t="n"/>
       <c r="D391" s="54" t="n"/>
-      <c r="E391" s="56" t="n"/>
-      <c r="F391" s="56" t="n"/>
+      <c r="E391" s="61" t="n"/>
+      <c r="F391" s="61" t="n"/>
       <c r="G391" s="57">
         <f>IF(AND(D391&lt;&gt;"已完成",D391&lt;&gt;"",E391&lt;&gt;"",E391&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8176,8 +8187,8 @@
       <c r="B392" s="55" t="n"/>
       <c r="C392" s="54" t="n"/>
       <c r="D392" s="54" t="n"/>
-      <c r="E392" s="56" t="n"/>
-      <c r="F392" s="56" t="n"/>
+      <c r="E392" s="61" t="n"/>
+      <c r="F392" s="61" t="n"/>
       <c r="G392" s="57">
         <f>IF(AND(D392&lt;&gt;"已完成",D392&lt;&gt;"",E392&lt;&gt;"",E392&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8190,8 +8201,8 @@
       <c r="B393" s="55" t="n"/>
       <c r="C393" s="54" t="n"/>
       <c r="D393" s="54" t="n"/>
-      <c r="E393" s="56" t="n"/>
-      <c r="F393" s="56" t="n"/>
+      <c r="E393" s="61" t="n"/>
+      <c r="F393" s="61" t="n"/>
       <c r="G393" s="57">
         <f>IF(AND(D393&lt;&gt;"已完成",D393&lt;&gt;"",E393&lt;&gt;"",E393&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8204,8 +8215,8 @@
       <c r="B394" s="55" t="n"/>
       <c r="C394" s="54" t="n"/>
       <c r="D394" s="54" t="n"/>
-      <c r="E394" s="56" t="n"/>
-      <c r="F394" s="56" t="n"/>
+      <c r="E394" s="61" t="n"/>
+      <c r="F394" s="61" t="n"/>
       <c r="G394" s="57">
         <f>IF(AND(D394&lt;&gt;"已完成",D394&lt;&gt;"",E394&lt;&gt;"",E394&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8218,8 +8229,8 @@
       <c r="B395" s="55" t="n"/>
       <c r="C395" s="54" t="n"/>
       <c r="D395" s="54" t="n"/>
-      <c r="E395" s="56" t="n"/>
-      <c r="F395" s="56" t="n"/>
+      <c r="E395" s="61" t="n"/>
+      <c r="F395" s="61" t="n"/>
       <c r="G395" s="57">
         <f>IF(AND(D395&lt;&gt;"已完成",D395&lt;&gt;"",E395&lt;&gt;"",E395&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8232,8 +8243,8 @@
       <c r="B396" s="55" t="n"/>
       <c r="C396" s="54" t="n"/>
       <c r="D396" s="54" t="n"/>
-      <c r="E396" s="56" t="n"/>
-      <c r="F396" s="56" t="n"/>
+      <c r="E396" s="61" t="n"/>
+      <c r="F396" s="61" t="n"/>
       <c r="G396" s="57">
         <f>IF(AND(D396&lt;&gt;"已完成",D396&lt;&gt;"",E396&lt;&gt;"",E396&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8246,8 +8257,8 @@
       <c r="B397" s="55" t="n"/>
       <c r="C397" s="54" t="n"/>
       <c r="D397" s="54" t="n"/>
-      <c r="E397" s="56" t="n"/>
-      <c r="F397" s="56" t="n"/>
+      <c r="E397" s="61" t="n"/>
+      <c r="F397" s="61" t="n"/>
       <c r="G397" s="57">
         <f>IF(AND(D397&lt;&gt;"已完成",D397&lt;&gt;"",E397&lt;&gt;"",E397&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8260,8 +8271,8 @@
       <c r="B398" s="55" t="n"/>
       <c r="C398" s="54" t="n"/>
       <c r="D398" s="54" t="n"/>
-      <c r="E398" s="56" t="n"/>
-      <c r="F398" s="56" t="n"/>
+      <c r="E398" s="61" t="n"/>
+      <c r="F398" s="61" t="n"/>
       <c r="G398" s="57">
         <f>IF(AND(D398&lt;&gt;"已完成",D398&lt;&gt;"",E398&lt;&gt;"",E398&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8274,8 +8285,8 @@
       <c r="B399" s="55" t="n"/>
       <c r="C399" s="54" t="n"/>
       <c r="D399" s="54" t="n"/>
-      <c r="E399" s="56" t="n"/>
-      <c r="F399" s="56" t="n"/>
+      <c r="E399" s="61" t="n"/>
+      <c r="F399" s="61" t="n"/>
       <c r="G399" s="57">
         <f>IF(AND(D399&lt;&gt;"已完成",D399&lt;&gt;"",E399&lt;&gt;"",E399&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8288,8 +8299,8 @@
       <c r="B400" s="55" t="n"/>
       <c r="C400" s="54" t="n"/>
       <c r="D400" s="54" t="n"/>
-      <c r="E400" s="56" t="n"/>
-      <c r="F400" s="56" t="n"/>
+      <c r="E400" s="61" t="n"/>
+      <c r="F400" s="61" t="n"/>
       <c r="G400" s="57">
         <f>IF(AND(D400&lt;&gt;"已完成",D400&lt;&gt;"",E400&lt;&gt;"",E400&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8302,8 +8313,8 @@
       <c r="B401" s="55" t="n"/>
       <c r="C401" s="54" t="n"/>
       <c r="D401" s="54" t="n"/>
-      <c r="E401" s="56" t="n"/>
-      <c r="F401" s="56" t="n"/>
+      <c r="E401" s="61" t="n"/>
+      <c r="F401" s="61" t="n"/>
       <c r="G401" s="57">
         <f>IF(AND(D401&lt;&gt;"已完成",D401&lt;&gt;"",E401&lt;&gt;"",E401&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8316,8 +8327,8 @@
       <c r="B402" s="55" t="n"/>
       <c r="C402" s="54" t="n"/>
       <c r="D402" s="54" t="n"/>
-      <c r="E402" s="56" t="n"/>
-      <c r="F402" s="56" t="n"/>
+      <c r="E402" s="61" t="n"/>
+      <c r="F402" s="61" t="n"/>
       <c r="G402" s="57">
         <f>IF(AND(D402&lt;&gt;"已完成",D402&lt;&gt;"",E402&lt;&gt;"",E402&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8330,8 +8341,8 @@
       <c r="B403" s="55" t="n"/>
       <c r="C403" s="54" t="n"/>
       <c r="D403" s="54" t="n"/>
-      <c r="E403" s="56" t="n"/>
-      <c r="F403" s="56" t="n"/>
+      <c r="E403" s="61" t="n"/>
+      <c r="F403" s="61" t="n"/>
       <c r="G403" s="57">
         <f>IF(AND(D403&lt;&gt;"已完成",D403&lt;&gt;"",E403&lt;&gt;"",E403&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8344,8 +8355,8 @@
       <c r="B404" s="55" t="n"/>
       <c r="C404" s="54" t="n"/>
       <c r="D404" s="54" t="n"/>
-      <c r="E404" s="56" t="n"/>
-      <c r="F404" s="56" t="n"/>
+      <c r="E404" s="61" t="n"/>
+      <c r="F404" s="61" t="n"/>
       <c r="G404" s="57">
         <f>IF(AND(D404&lt;&gt;"已完成",D404&lt;&gt;"",E404&lt;&gt;"",E404&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8358,8 +8369,8 @@
       <c r="B405" s="55" t="n"/>
       <c r="C405" s="54" t="n"/>
       <c r="D405" s="54" t="n"/>
-      <c r="E405" s="56" t="n"/>
-      <c r="F405" s="56" t="n"/>
+      <c r="E405" s="61" t="n"/>
+      <c r="F405" s="61" t="n"/>
       <c r="G405" s="57">
         <f>IF(AND(D405&lt;&gt;"已完成",D405&lt;&gt;"",E405&lt;&gt;"",E405&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8372,8 +8383,8 @@
       <c r="B406" s="55" t="n"/>
       <c r="C406" s="54" t="n"/>
       <c r="D406" s="54" t="n"/>
-      <c r="E406" s="56" t="n"/>
-      <c r="F406" s="56" t="n"/>
+      <c r="E406" s="61" t="n"/>
+      <c r="F406" s="61" t="n"/>
       <c r="G406" s="57">
         <f>IF(AND(D406&lt;&gt;"已完成",D406&lt;&gt;"",E406&lt;&gt;"",E406&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8386,8 +8397,8 @@
       <c r="B407" s="55" t="n"/>
       <c r="C407" s="54" t="n"/>
       <c r="D407" s="54" t="n"/>
-      <c r="E407" s="56" t="n"/>
-      <c r="F407" s="56" t="n"/>
+      <c r="E407" s="61" t="n"/>
+      <c r="F407" s="61" t="n"/>
       <c r="G407" s="57">
         <f>IF(AND(D407&lt;&gt;"已完成",D407&lt;&gt;"",E407&lt;&gt;"",E407&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8400,8 +8411,8 @@
       <c r="B408" s="55" t="n"/>
       <c r="C408" s="54" t="n"/>
       <c r="D408" s="54" t="n"/>
-      <c r="E408" s="56" t="n"/>
-      <c r="F408" s="56" t="n"/>
+      <c r="E408" s="61" t="n"/>
+      <c r="F408" s="61" t="n"/>
       <c r="G408" s="57">
         <f>IF(AND(D408&lt;&gt;"已完成",D408&lt;&gt;"",E408&lt;&gt;"",E408&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8414,8 +8425,8 @@
       <c r="B409" s="55" t="n"/>
       <c r="C409" s="54" t="n"/>
       <c r="D409" s="54" t="n"/>
-      <c r="E409" s="56" t="n"/>
-      <c r="F409" s="56" t="n"/>
+      <c r="E409" s="61" t="n"/>
+      <c r="F409" s="61" t="n"/>
       <c r="G409" s="57">
         <f>IF(AND(D409&lt;&gt;"已完成",D409&lt;&gt;"",E409&lt;&gt;"",E409&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8428,8 +8439,8 @@
       <c r="B410" s="55" t="n"/>
       <c r="C410" s="54" t="n"/>
       <c r="D410" s="54" t="n"/>
-      <c r="E410" s="56" t="n"/>
-      <c r="F410" s="56" t="n"/>
+      <c r="E410" s="61" t="n"/>
+      <c r="F410" s="61" t="n"/>
       <c r="G410" s="57">
         <f>IF(AND(D410&lt;&gt;"已完成",D410&lt;&gt;"",E410&lt;&gt;"",E410&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8442,8 +8453,8 @@
       <c r="B411" s="55" t="n"/>
       <c r="C411" s="54" t="n"/>
       <c r="D411" s="54" t="n"/>
-      <c r="E411" s="56" t="n"/>
-      <c r="F411" s="56" t="n"/>
+      <c r="E411" s="61" t="n"/>
+      <c r="F411" s="61" t="n"/>
       <c r="G411" s="57">
         <f>IF(AND(D411&lt;&gt;"已完成",D411&lt;&gt;"",E411&lt;&gt;"",E411&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8456,8 +8467,8 @@
       <c r="B412" s="55" t="n"/>
       <c r="C412" s="54" t="n"/>
       <c r="D412" s="54" t="n"/>
-      <c r="E412" s="56" t="n"/>
-      <c r="F412" s="56" t="n"/>
+      <c r="E412" s="61" t="n"/>
+      <c r="F412" s="61" t="n"/>
       <c r="G412" s="57">
         <f>IF(AND(D412&lt;&gt;"已完成",D412&lt;&gt;"",E412&lt;&gt;"",E412&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8470,8 +8481,8 @@
       <c r="B413" s="55" t="n"/>
       <c r="C413" s="54" t="n"/>
       <c r="D413" s="54" t="n"/>
-      <c r="E413" s="56" t="n"/>
-      <c r="F413" s="56" t="n"/>
+      <c r="E413" s="61" t="n"/>
+      <c r="F413" s="61" t="n"/>
       <c r="G413" s="57">
         <f>IF(AND(D413&lt;&gt;"已完成",D413&lt;&gt;"",E413&lt;&gt;"",E413&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8484,8 +8495,8 @@
       <c r="B414" s="55" t="n"/>
       <c r="C414" s="54" t="n"/>
       <c r="D414" s="54" t="n"/>
-      <c r="E414" s="56" t="n"/>
-      <c r="F414" s="56" t="n"/>
+      <c r="E414" s="61" t="n"/>
+      <c r="F414" s="61" t="n"/>
       <c r="G414" s="57">
         <f>IF(AND(D414&lt;&gt;"已完成",D414&lt;&gt;"",E414&lt;&gt;"",E414&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8498,8 +8509,8 @@
       <c r="B415" s="55" t="n"/>
       <c r="C415" s="54" t="n"/>
       <c r="D415" s="54" t="n"/>
-      <c r="E415" s="56" t="n"/>
-      <c r="F415" s="56" t="n"/>
+      <c r="E415" s="61" t="n"/>
+      <c r="F415" s="61" t="n"/>
       <c r="G415" s="57">
         <f>IF(AND(D415&lt;&gt;"已完成",D415&lt;&gt;"",E415&lt;&gt;"",E415&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8512,8 +8523,8 @@
       <c r="B416" s="55" t="n"/>
       <c r="C416" s="54" t="n"/>
       <c r="D416" s="54" t="n"/>
-      <c r="E416" s="56" t="n"/>
-      <c r="F416" s="56" t="n"/>
+      <c r="E416" s="61" t="n"/>
+      <c r="F416" s="61" t="n"/>
       <c r="G416" s="57">
         <f>IF(AND(D416&lt;&gt;"已完成",D416&lt;&gt;"",E416&lt;&gt;"",E416&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8526,8 +8537,8 @@
       <c r="B417" s="55" t="n"/>
       <c r="C417" s="54" t="n"/>
       <c r="D417" s="54" t="n"/>
-      <c r="E417" s="56" t="n"/>
-      <c r="F417" s="56" t="n"/>
+      <c r="E417" s="61" t="n"/>
+      <c r="F417" s="61" t="n"/>
       <c r="G417" s="57">
         <f>IF(AND(D417&lt;&gt;"已完成",D417&lt;&gt;"",E417&lt;&gt;"",E417&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8540,8 +8551,8 @@
       <c r="B418" s="55" t="n"/>
       <c r="C418" s="54" t="n"/>
       <c r="D418" s="54" t="n"/>
-      <c r="E418" s="56" t="n"/>
-      <c r="F418" s="56" t="n"/>
+      <c r="E418" s="61" t="n"/>
+      <c r="F418" s="61" t="n"/>
       <c r="G418" s="57">
         <f>IF(AND(D418&lt;&gt;"已完成",D418&lt;&gt;"",E418&lt;&gt;"",E418&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8554,8 +8565,8 @@
       <c r="B419" s="55" t="n"/>
       <c r="C419" s="54" t="n"/>
       <c r="D419" s="54" t="n"/>
-      <c r="E419" s="56" t="n"/>
-      <c r="F419" s="56" t="n"/>
+      <c r="E419" s="61" t="n"/>
+      <c r="F419" s="61" t="n"/>
       <c r="G419" s="57">
         <f>IF(AND(D419&lt;&gt;"已完成",D419&lt;&gt;"",E419&lt;&gt;"",E419&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8568,8 +8579,8 @@
       <c r="B420" s="55" t="n"/>
       <c r="C420" s="54" t="n"/>
       <c r="D420" s="54" t="n"/>
-      <c r="E420" s="56" t="n"/>
-      <c r="F420" s="56" t="n"/>
+      <c r="E420" s="61" t="n"/>
+      <c r="F420" s="61" t="n"/>
       <c r="G420" s="57">
         <f>IF(AND(D420&lt;&gt;"已完成",D420&lt;&gt;"",E420&lt;&gt;"",E420&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8582,8 +8593,8 @@
       <c r="B421" s="55" t="n"/>
       <c r="C421" s="54" t="n"/>
       <c r="D421" s="54" t="n"/>
-      <c r="E421" s="56" t="n"/>
-      <c r="F421" s="56" t="n"/>
+      <c r="E421" s="61" t="n"/>
+      <c r="F421" s="61" t="n"/>
       <c r="G421" s="57">
         <f>IF(AND(D421&lt;&gt;"已完成",D421&lt;&gt;"",E421&lt;&gt;"",E421&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8596,8 +8607,8 @@
       <c r="B422" s="55" t="n"/>
       <c r="C422" s="54" t="n"/>
       <c r="D422" s="54" t="n"/>
-      <c r="E422" s="56" t="n"/>
-      <c r="F422" s="56" t="n"/>
+      <c r="E422" s="61" t="n"/>
+      <c r="F422" s="61" t="n"/>
       <c r="G422" s="57">
         <f>IF(AND(D422&lt;&gt;"已完成",D422&lt;&gt;"",E422&lt;&gt;"",E422&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8610,8 +8621,8 @@
       <c r="B423" s="55" t="n"/>
       <c r="C423" s="54" t="n"/>
       <c r="D423" s="54" t="n"/>
-      <c r="E423" s="56" t="n"/>
-      <c r="F423" s="56" t="n"/>
+      <c r="E423" s="61" t="n"/>
+      <c r="F423" s="61" t="n"/>
       <c r="G423" s="57">
         <f>IF(AND(D423&lt;&gt;"已完成",D423&lt;&gt;"",E423&lt;&gt;"",E423&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8624,8 +8635,8 @@
       <c r="B424" s="55" t="n"/>
       <c r="C424" s="54" t="n"/>
       <c r="D424" s="54" t="n"/>
-      <c r="E424" s="56" t="n"/>
-      <c r="F424" s="56" t="n"/>
+      <c r="E424" s="61" t="n"/>
+      <c r="F424" s="61" t="n"/>
       <c r="G424" s="57">
         <f>IF(AND(D424&lt;&gt;"已完成",D424&lt;&gt;"",E424&lt;&gt;"",E424&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8638,8 +8649,8 @@
       <c r="B425" s="55" t="n"/>
       <c r="C425" s="54" t="n"/>
       <c r="D425" s="54" t="n"/>
-      <c r="E425" s="56" t="n"/>
-      <c r="F425" s="56" t="n"/>
+      <c r="E425" s="61" t="n"/>
+      <c r="F425" s="61" t="n"/>
       <c r="G425" s="57">
         <f>IF(AND(D425&lt;&gt;"已完成",D425&lt;&gt;"",E425&lt;&gt;"",E425&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8652,8 +8663,8 @@
       <c r="B426" s="55" t="n"/>
       <c r="C426" s="54" t="n"/>
       <c r="D426" s="54" t="n"/>
-      <c r="E426" s="56" t="n"/>
-      <c r="F426" s="56" t="n"/>
+      <c r="E426" s="61" t="n"/>
+      <c r="F426" s="61" t="n"/>
       <c r="G426" s="57">
         <f>IF(AND(D426&lt;&gt;"已完成",D426&lt;&gt;"",E426&lt;&gt;"",E426&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8666,8 +8677,8 @@
       <c r="B427" s="55" t="n"/>
       <c r="C427" s="54" t="n"/>
       <c r="D427" s="54" t="n"/>
-      <c r="E427" s="56" t="n"/>
-      <c r="F427" s="56" t="n"/>
+      <c r="E427" s="61" t="n"/>
+      <c r="F427" s="61" t="n"/>
       <c r="G427" s="57">
         <f>IF(AND(D427&lt;&gt;"已完成",D427&lt;&gt;"",E427&lt;&gt;"",E427&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8680,8 +8691,8 @@
       <c r="B428" s="55" t="n"/>
       <c r="C428" s="54" t="n"/>
       <c r="D428" s="54" t="n"/>
-      <c r="E428" s="56" t="n"/>
-      <c r="F428" s="56" t="n"/>
+      <c r="E428" s="61" t="n"/>
+      <c r="F428" s="61" t="n"/>
       <c r="G428" s="57">
         <f>IF(AND(D428&lt;&gt;"已完成",D428&lt;&gt;"",E428&lt;&gt;"",E428&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8694,8 +8705,8 @@
       <c r="B429" s="55" t="n"/>
       <c r="C429" s="54" t="n"/>
       <c r="D429" s="54" t="n"/>
-      <c r="E429" s="56" t="n"/>
-      <c r="F429" s="56" t="n"/>
+      <c r="E429" s="61" t="n"/>
+      <c r="F429" s="61" t="n"/>
       <c r="G429" s="57">
         <f>IF(AND(D429&lt;&gt;"已完成",D429&lt;&gt;"",E429&lt;&gt;"",E429&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8708,8 +8719,8 @@
       <c r="B430" s="55" t="n"/>
       <c r="C430" s="54" t="n"/>
       <c r="D430" s="54" t="n"/>
-      <c r="E430" s="56" t="n"/>
-      <c r="F430" s="56" t="n"/>
+      <c r="E430" s="61" t="n"/>
+      <c r="F430" s="61" t="n"/>
       <c r="G430" s="57">
         <f>IF(AND(D430&lt;&gt;"已完成",D430&lt;&gt;"",E430&lt;&gt;"",E430&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8722,8 +8733,8 @@
       <c r="B431" s="55" t="n"/>
       <c r="C431" s="54" t="n"/>
       <c r="D431" s="54" t="n"/>
-      <c r="E431" s="56" t="n"/>
-      <c r="F431" s="56" t="n"/>
+      <c r="E431" s="61" t="n"/>
+      <c r="F431" s="61" t="n"/>
       <c r="G431" s="57">
         <f>IF(AND(D431&lt;&gt;"已完成",D431&lt;&gt;"",E431&lt;&gt;"",E431&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8736,8 +8747,8 @@
       <c r="B432" s="55" t="n"/>
       <c r="C432" s="54" t="n"/>
       <c r="D432" s="54" t="n"/>
-      <c r="E432" s="56" t="n"/>
-      <c r="F432" s="56" t="n"/>
+      <c r="E432" s="61" t="n"/>
+      <c r="F432" s="61" t="n"/>
       <c r="G432" s="57">
         <f>IF(AND(D432&lt;&gt;"已完成",D432&lt;&gt;"",E432&lt;&gt;"",E432&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8750,8 +8761,8 @@
       <c r="B433" s="55" t="n"/>
       <c r="C433" s="54" t="n"/>
       <c r="D433" s="54" t="n"/>
-      <c r="E433" s="56" t="n"/>
-      <c r="F433" s="56" t="n"/>
+      <c r="E433" s="61" t="n"/>
+      <c r="F433" s="61" t="n"/>
       <c r="G433" s="57">
         <f>IF(AND(D433&lt;&gt;"已完成",D433&lt;&gt;"",E433&lt;&gt;"",E433&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8764,8 +8775,8 @@
       <c r="B434" s="55" t="n"/>
       <c r="C434" s="54" t="n"/>
       <c r="D434" s="54" t="n"/>
-      <c r="E434" s="56" t="n"/>
-      <c r="F434" s="56" t="n"/>
+      <c r="E434" s="61" t="n"/>
+      <c r="F434" s="61" t="n"/>
       <c r="G434" s="57">
         <f>IF(AND(D434&lt;&gt;"已完成",D434&lt;&gt;"",E434&lt;&gt;"",E434&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8778,8 +8789,8 @@
       <c r="B435" s="55" t="n"/>
       <c r="C435" s="54" t="n"/>
       <c r="D435" s="54" t="n"/>
-      <c r="E435" s="56" t="n"/>
-      <c r="F435" s="56" t="n"/>
+      <c r="E435" s="61" t="n"/>
+      <c r="F435" s="61" t="n"/>
       <c r="G435" s="57">
         <f>IF(AND(D435&lt;&gt;"已完成",D435&lt;&gt;"",E435&lt;&gt;"",E435&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8792,8 +8803,8 @@
       <c r="B436" s="55" t="n"/>
       <c r="C436" s="54" t="n"/>
       <c r="D436" s="54" t="n"/>
-      <c r="E436" s="56" t="n"/>
-      <c r="F436" s="56" t="n"/>
+      <c r="E436" s="61" t="n"/>
+      <c r="F436" s="61" t="n"/>
       <c r="G436" s="57">
         <f>IF(AND(D436&lt;&gt;"已完成",D436&lt;&gt;"",E436&lt;&gt;"",E436&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8806,8 +8817,8 @@
       <c r="B437" s="55" t="n"/>
       <c r="C437" s="54" t="n"/>
       <c r="D437" s="54" t="n"/>
-      <c r="E437" s="56" t="n"/>
-      <c r="F437" s="56" t="n"/>
+      <c r="E437" s="61" t="n"/>
+      <c r="F437" s="61" t="n"/>
       <c r="G437" s="57">
         <f>IF(AND(D437&lt;&gt;"已完成",D437&lt;&gt;"",E437&lt;&gt;"",E437&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8820,8 +8831,8 @@
       <c r="B438" s="55" t="n"/>
       <c r="C438" s="54" t="n"/>
       <c r="D438" s="54" t="n"/>
-      <c r="E438" s="56" t="n"/>
-      <c r="F438" s="56" t="n"/>
+      <c r="E438" s="61" t="n"/>
+      <c r="F438" s="61" t="n"/>
       <c r="G438" s="57">
         <f>IF(AND(D438&lt;&gt;"已完成",D438&lt;&gt;"",E438&lt;&gt;"",E438&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8834,8 +8845,8 @@
       <c r="B439" s="55" t="n"/>
       <c r="C439" s="54" t="n"/>
       <c r="D439" s="54" t="n"/>
-      <c r="E439" s="56" t="n"/>
-      <c r="F439" s="56" t="n"/>
+      <c r="E439" s="61" t="n"/>
+      <c r="F439" s="61" t="n"/>
       <c r="G439" s="57">
         <f>IF(AND(D439&lt;&gt;"已完成",D439&lt;&gt;"",E439&lt;&gt;"",E439&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8848,8 +8859,8 @@
       <c r="B440" s="55" t="n"/>
       <c r="C440" s="54" t="n"/>
       <c r="D440" s="54" t="n"/>
-      <c r="E440" s="56" t="n"/>
-      <c r="F440" s="56" t="n"/>
+      <c r="E440" s="61" t="n"/>
+      <c r="F440" s="61" t="n"/>
       <c r="G440" s="57">
         <f>IF(AND(D440&lt;&gt;"已完成",D440&lt;&gt;"",E440&lt;&gt;"",E440&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8862,8 +8873,8 @@
       <c r="B441" s="55" t="n"/>
       <c r="C441" s="54" t="n"/>
       <c r="D441" s="54" t="n"/>
-      <c r="E441" s="56" t="n"/>
-      <c r="F441" s="56" t="n"/>
+      <c r="E441" s="61" t="n"/>
+      <c r="F441" s="61" t="n"/>
       <c r="G441" s="57">
         <f>IF(AND(D441&lt;&gt;"已完成",D441&lt;&gt;"",E441&lt;&gt;"",E441&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8876,8 +8887,8 @@
       <c r="B442" s="55" t="n"/>
       <c r="C442" s="54" t="n"/>
       <c r="D442" s="54" t="n"/>
-      <c r="E442" s="56" t="n"/>
-      <c r="F442" s="56" t="n"/>
+      <c r="E442" s="61" t="n"/>
+      <c r="F442" s="61" t="n"/>
       <c r="G442" s="57">
         <f>IF(AND(D442&lt;&gt;"已完成",D442&lt;&gt;"",E442&lt;&gt;"",E442&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8890,8 +8901,8 @@
       <c r="B443" s="55" t="n"/>
       <c r="C443" s="54" t="n"/>
       <c r="D443" s="54" t="n"/>
-      <c r="E443" s="56" t="n"/>
-      <c r="F443" s="56" t="n"/>
+      <c r="E443" s="61" t="n"/>
+      <c r="F443" s="61" t="n"/>
       <c r="G443" s="57">
         <f>IF(AND(D443&lt;&gt;"已完成",D443&lt;&gt;"",E443&lt;&gt;"",E443&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8904,8 +8915,8 @@
       <c r="B444" s="55" t="n"/>
       <c r="C444" s="54" t="n"/>
       <c r="D444" s="54" t="n"/>
-      <c r="E444" s="56" t="n"/>
-      <c r="F444" s="56" t="n"/>
+      <c r="E444" s="61" t="n"/>
+      <c r="F444" s="61" t="n"/>
       <c r="G444" s="57">
         <f>IF(AND(D444&lt;&gt;"已完成",D444&lt;&gt;"",E444&lt;&gt;"",E444&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8918,8 +8929,8 @@
       <c r="B445" s="55" t="n"/>
       <c r="C445" s="54" t="n"/>
       <c r="D445" s="54" t="n"/>
-      <c r="E445" s="56" t="n"/>
-      <c r="F445" s="56" t="n"/>
+      <c r="E445" s="61" t="n"/>
+      <c r="F445" s="61" t="n"/>
       <c r="G445" s="57">
         <f>IF(AND(D445&lt;&gt;"已完成",D445&lt;&gt;"",E445&lt;&gt;"",E445&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8932,8 +8943,8 @@
       <c r="B446" s="55" t="n"/>
       <c r="C446" s="54" t="n"/>
       <c r="D446" s="54" t="n"/>
-      <c r="E446" s="56" t="n"/>
-      <c r="F446" s="56" t="n"/>
+      <c r="E446" s="61" t="n"/>
+      <c r="F446" s="61" t="n"/>
       <c r="G446" s="57">
         <f>IF(AND(D446&lt;&gt;"已完成",D446&lt;&gt;"",E446&lt;&gt;"",E446&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8946,8 +8957,8 @@
       <c r="B447" s="55" t="n"/>
       <c r="C447" s="54" t="n"/>
       <c r="D447" s="54" t="n"/>
-      <c r="E447" s="56" t="n"/>
-      <c r="F447" s="56" t="n"/>
+      <c r="E447" s="61" t="n"/>
+      <c r="F447" s="61" t="n"/>
       <c r="G447" s="57">
         <f>IF(AND(D447&lt;&gt;"已完成",D447&lt;&gt;"",E447&lt;&gt;"",E447&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8960,8 +8971,8 @@
       <c r="B448" s="55" t="n"/>
       <c r="C448" s="54" t="n"/>
       <c r="D448" s="54" t="n"/>
-      <c r="E448" s="56" t="n"/>
-      <c r="F448" s="56" t="n"/>
+      <c r="E448" s="61" t="n"/>
+      <c r="F448" s="61" t="n"/>
       <c r="G448" s="57">
         <f>IF(AND(D448&lt;&gt;"已完成",D448&lt;&gt;"",E448&lt;&gt;"",E448&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8974,8 +8985,8 @@
       <c r="B449" s="55" t="n"/>
       <c r="C449" s="54" t="n"/>
       <c r="D449" s="54" t="n"/>
-      <c r="E449" s="56" t="n"/>
-      <c r="F449" s="56" t="n"/>
+      <c r="E449" s="61" t="n"/>
+      <c r="F449" s="61" t="n"/>
       <c r="G449" s="57">
         <f>IF(AND(D449&lt;&gt;"已完成",D449&lt;&gt;"",E449&lt;&gt;"",E449&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -8988,8 +8999,8 @@
       <c r="B450" s="55" t="n"/>
       <c r="C450" s="54" t="n"/>
       <c r="D450" s="54" t="n"/>
-      <c r="E450" s="56" t="n"/>
-      <c r="F450" s="56" t="n"/>
+      <c r="E450" s="61" t="n"/>
+      <c r="F450" s="61" t="n"/>
       <c r="G450" s="57">
         <f>IF(AND(D450&lt;&gt;"已完成",D450&lt;&gt;"",E450&lt;&gt;"",E450&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9002,8 +9013,8 @@
       <c r="B451" s="55" t="n"/>
       <c r="C451" s="54" t="n"/>
       <c r="D451" s="54" t="n"/>
-      <c r="E451" s="56" t="n"/>
-      <c r="F451" s="56" t="n"/>
+      <c r="E451" s="61" t="n"/>
+      <c r="F451" s="61" t="n"/>
       <c r="G451" s="57">
         <f>IF(AND(D451&lt;&gt;"已完成",D451&lt;&gt;"",E451&lt;&gt;"",E451&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9016,8 +9027,8 @@
       <c r="B452" s="55" t="n"/>
       <c r="C452" s="54" t="n"/>
       <c r="D452" s="54" t="n"/>
-      <c r="E452" s="56" t="n"/>
-      <c r="F452" s="56" t="n"/>
+      <c r="E452" s="61" t="n"/>
+      <c r="F452" s="61" t="n"/>
       <c r="G452" s="57">
         <f>IF(AND(D452&lt;&gt;"已完成",D452&lt;&gt;"",E452&lt;&gt;"",E452&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9030,8 +9041,8 @@
       <c r="B453" s="55" t="n"/>
       <c r="C453" s="54" t="n"/>
       <c r="D453" s="54" t="n"/>
-      <c r="E453" s="56" t="n"/>
-      <c r="F453" s="56" t="n"/>
+      <c r="E453" s="61" t="n"/>
+      <c r="F453" s="61" t="n"/>
       <c r="G453" s="57">
         <f>IF(AND(D453&lt;&gt;"已完成",D453&lt;&gt;"",E453&lt;&gt;"",E453&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9044,8 +9055,8 @@
       <c r="B454" s="55" t="n"/>
       <c r="C454" s="54" t="n"/>
       <c r="D454" s="54" t="n"/>
-      <c r="E454" s="56" t="n"/>
-      <c r="F454" s="56" t="n"/>
+      <c r="E454" s="61" t="n"/>
+      <c r="F454" s="61" t="n"/>
       <c r="G454" s="57">
         <f>IF(AND(D454&lt;&gt;"已完成",D454&lt;&gt;"",E454&lt;&gt;"",E454&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9058,8 +9069,8 @@
       <c r="B455" s="55" t="n"/>
       <c r="C455" s="54" t="n"/>
       <c r="D455" s="54" t="n"/>
-      <c r="E455" s="56" t="n"/>
-      <c r="F455" s="56" t="n"/>
+      <c r="E455" s="61" t="n"/>
+      <c r="F455" s="61" t="n"/>
       <c r="G455" s="57">
         <f>IF(AND(D455&lt;&gt;"已完成",D455&lt;&gt;"",E455&lt;&gt;"",E455&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9072,8 +9083,8 @@
       <c r="B456" s="55" t="n"/>
       <c r="C456" s="54" t="n"/>
       <c r="D456" s="54" t="n"/>
-      <c r="E456" s="56" t="n"/>
-      <c r="F456" s="56" t="n"/>
+      <c r="E456" s="61" t="n"/>
+      <c r="F456" s="61" t="n"/>
       <c r="G456" s="57">
         <f>IF(AND(D456&lt;&gt;"已完成",D456&lt;&gt;"",E456&lt;&gt;"",E456&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9086,8 +9097,8 @@
       <c r="B457" s="55" t="n"/>
       <c r="C457" s="54" t="n"/>
       <c r="D457" s="54" t="n"/>
-      <c r="E457" s="56" t="n"/>
-      <c r="F457" s="56" t="n"/>
+      <c r="E457" s="61" t="n"/>
+      <c r="F457" s="61" t="n"/>
       <c r="G457" s="57">
         <f>IF(AND(D457&lt;&gt;"已完成",D457&lt;&gt;"",E457&lt;&gt;"",E457&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9100,8 +9111,8 @@
       <c r="B458" s="55" t="n"/>
       <c r="C458" s="54" t="n"/>
       <c r="D458" s="54" t="n"/>
-      <c r="E458" s="56" t="n"/>
-      <c r="F458" s="56" t="n"/>
+      <c r="E458" s="61" t="n"/>
+      <c r="F458" s="61" t="n"/>
       <c r="G458" s="57">
         <f>IF(AND(D458&lt;&gt;"已完成",D458&lt;&gt;"",E458&lt;&gt;"",E458&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9114,8 +9125,8 @@
       <c r="B459" s="55" t="n"/>
       <c r="C459" s="54" t="n"/>
       <c r="D459" s="54" t="n"/>
-      <c r="E459" s="56" t="n"/>
-      <c r="F459" s="56" t="n"/>
+      <c r="E459" s="61" t="n"/>
+      <c r="F459" s="61" t="n"/>
       <c r="G459" s="57">
         <f>IF(AND(D459&lt;&gt;"已完成",D459&lt;&gt;"",E459&lt;&gt;"",E459&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9128,8 +9139,8 @@
       <c r="B460" s="55" t="n"/>
       <c r="C460" s="54" t="n"/>
       <c r="D460" s="54" t="n"/>
-      <c r="E460" s="56" t="n"/>
-      <c r="F460" s="56" t="n"/>
+      <c r="E460" s="61" t="n"/>
+      <c r="F460" s="61" t="n"/>
       <c r="G460" s="57">
         <f>IF(AND(D460&lt;&gt;"已完成",D460&lt;&gt;"",E460&lt;&gt;"",E460&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9142,8 +9153,8 @@
       <c r="B461" s="55" t="n"/>
       <c r="C461" s="54" t="n"/>
       <c r="D461" s="54" t="n"/>
-      <c r="E461" s="56" t="n"/>
-      <c r="F461" s="56" t="n"/>
+      <c r="E461" s="61" t="n"/>
+      <c r="F461" s="61" t="n"/>
       <c r="G461" s="57">
         <f>IF(AND(D461&lt;&gt;"已完成",D461&lt;&gt;"",E461&lt;&gt;"",E461&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9156,8 +9167,8 @@
       <c r="B462" s="55" t="n"/>
       <c r="C462" s="54" t="n"/>
       <c r="D462" s="54" t="n"/>
-      <c r="E462" s="56" t="n"/>
-      <c r="F462" s="56" t="n"/>
+      <c r="E462" s="61" t="n"/>
+      <c r="F462" s="61" t="n"/>
       <c r="G462" s="57">
         <f>IF(AND(D462&lt;&gt;"已完成",D462&lt;&gt;"",E462&lt;&gt;"",E462&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9170,8 +9181,8 @@
       <c r="B463" s="55" t="n"/>
       <c r="C463" s="54" t="n"/>
       <c r="D463" s="54" t="n"/>
-      <c r="E463" s="56" t="n"/>
-      <c r="F463" s="56" t="n"/>
+      <c r="E463" s="61" t="n"/>
+      <c r="F463" s="61" t="n"/>
       <c r="G463" s="57">
         <f>IF(AND(D463&lt;&gt;"已完成",D463&lt;&gt;"",E463&lt;&gt;"",E463&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9184,8 +9195,8 @@
       <c r="B464" s="55" t="n"/>
       <c r="C464" s="54" t="n"/>
       <c r="D464" s="54" t="n"/>
-      <c r="E464" s="56" t="n"/>
-      <c r="F464" s="56" t="n"/>
+      <c r="E464" s="61" t="n"/>
+      <c r="F464" s="61" t="n"/>
       <c r="G464" s="57">
         <f>IF(AND(D464&lt;&gt;"已完成",D464&lt;&gt;"",E464&lt;&gt;"",E464&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9198,8 +9209,8 @@
       <c r="B465" s="55" t="n"/>
       <c r="C465" s="54" t="n"/>
       <c r="D465" s="54" t="n"/>
-      <c r="E465" s="56" t="n"/>
-      <c r="F465" s="56" t="n"/>
+      <c r="E465" s="61" t="n"/>
+      <c r="F465" s="61" t="n"/>
       <c r="G465" s="57">
         <f>IF(AND(D465&lt;&gt;"已完成",D465&lt;&gt;"",E465&lt;&gt;"",E465&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9212,8 +9223,8 @@
       <c r="B466" s="55" t="n"/>
       <c r="C466" s="54" t="n"/>
       <c r="D466" s="54" t="n"/>
-      <c r="E466" s="56" t="n"/>
-      <c r="F466" s="56" t="n"/>
+      <c r="E466" s="61" t="n"/>
+      <c r="F466" s="61" t="n"/>
       <c r="G466" s="57">
         <f>IF(AND(D466&lt;&gt;"已完成",D466&lt;&gt;"",E466&lt;&gt;"",E466&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9226,8 +9237,8 @@
       <c r="B467" s="55" t="n"/>
       <c r="C467" s="54" t="n"/>
       <c r="D467" s="54" t="n"/>
-      <c r="E467" s="56" t="n"/>
-      <c r="F467" s="56" t="n"/>
+      <c r="E467" s="61" t="n"/>
+      <c r="F467" s="61" t="n"/>
       <c r="G467" s="57">
         <f>IF(AND(D467&lt;&gt;"已完成",D467&lt;&gt;"",E467&lt;&gt;"",E467&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9240,8 +9251,8 @@
       <c r="B468" s="55" t="n"/>
       <c r="C468" s="54" t="n"/>
       <c r="D468" s="54" t="n"/>
-      <c r="E468" s="56" t="n"/>
-      <c r="F468" s="56" t="n"/>
+      <c r="E468" s="61" t="n"/>
+      <c r="F468" s="61" t="n"/>
       <c r="G468" s="57">
         <f>IF(AND(D468&lt;&gt;"已完成",D468&lt;&gt;"",E468&lt;&gt;"",E468&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9254,8 +9265,8 @@
       <c r="B469" s="55" t="n"/>
       <c r="C469" s="54" t="n"/>
       <c r="D469" s="54" t="n"/>
-      <c r="E469" s="56" t="n"/>
-      <c r="F469" s="56" t="n"/>
+      <c r="E469" s="61" t="n"/>
+      <c r="F469" s="61" t="n"/>
       <c r="G469" s="57">
         <f>IF(AND(D469&lt;&gt;"已完成",D469&lt;&gt;"",E469&lt;&gt;"",E469&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9268,8 +9279,8 @@
       <c r="B470" s="55" t="n"/>
       <c r="C470" s="54" t="n"/>
       <c r="D470" s="54" t="n"/>
-      <c r="E470" s="56" t="n"/>
-      <c r="F470" s="56" t="n"/>
+      <c r="E470" s="61" t="n"/>
+      <c r="F470" s="61" t="n"/>
       <c r="G470" s="57">
         <f>IF(AND(D470&lt;&gt;"已完成",D470&lt;&gt;"",E470&lt;&gt;"",E470&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9282,8 +9293,8 @@
       <c r="B471" s="55" t="n"/>
       <c r="C471" s="54" t="n"/>
       <c r="D471" s="54" t="n"/>
-      <c r="E471" s="56" t="n"/>
-      <c r="F471" s="56" t="n"/>
+      <c r="E471" s="61" t="n"/>
+      <c r="F471" s="61" t="n"/>
       <c r="G471" s="57">
         <f>IF(AND(D471&lt;&gt;"已完成",D471&lt;&gt;"",E471&lt;&gt;"",E471&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9296,8 +9307,8 @@
       <c r="B472" s="55" t="n"/>
       <c r="C472" s="54" t="n"/>
       <c r="D472" s="54" t="n"/>
-      <c r="E472" s="56" t="n"/>
-      <c r="F472" s="56" t="n"/>
+      <c r="E472" s="61" t="n"/>
+      <c r="F472" s="61" t="n"/>
       <c r="G472" s="57">
         <f>IF(AND(D472&lt;&gt;"已完成",D472&lt;&gt;"",E472&lt;&gt;"",E472&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9310,8 +9321,8 @@
       <c r="B473" s="55" t="n"/>
       <c r="C473" s="54" t="n"/>
       <c r="D473" s="54" t="n"/>
-      <c r="E473" s="56" t="n"/>
-      <c r="F473" s="56" t="n"/>
+      <c r="E473" s="61" t="n"/>
+      <c r="F473" s="61" t="n"/>
       <c r="G473" s="57">
         <f>IF(AND(D473&lt;&gt;"已完成",D473&lt;&gt;"",E473&lt;&gt;"",E473&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9324,8 +9335,8 @@
       <c r="B474" s="55" t="n"/>
       <c r="C474" s="54" t="n"/>
       <c r="D474" s="54" t="n"/>
-      <c r="E474" s="56" t="n"/>
-      <c r="F474" s="56" t="n"/>
+      <c r="E474" s="61" t="n"/>
+      <c r="F474" s="61" t="n"/>
       <c r="G474" s="57">
         <f>IF(AND(D474&lt;&gt;"已完成",D474&lt;&gt;"",E474&lt;&gt;"",E474&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9338,8 +9349,8 @@
       <c r="B475" s="55" t="n"/>
       <c r="C475" s="54" t="n"/>
       <c r="D475" s="54" t="n"/>
-      <c r="E475" s="56" t="n"/>
-      <c r="F475" s="56" t="n"/>
+      <c r="E475" s="61" t="n"/>
+      <c r="F475" s="61" t="n"/>
       <c r="G475" s="57">
         <f>IF(AND(D475&lt;&gt;"已完成",D475&lt;&gt;"",E475&lt;&gt;"",E475&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9352,8 +9363,8 @@
       <c r="B476" s="55" t="n"/>
       <c r="C476" s="54" t="n"/>
       <c r="D476" s="54" t="n"/>
-      <c r="E476" s="56" t="n"/>
-      <c r="F476" s="56" t="n"/>
+      <c r="E476" s="61" t="n"/>
+      <c r="F476" s="61" t="n"/>
       <c r="G476" s="57">
         <f>IF(AND(D476&lt;&gt;"已完成",D476&lt;&gt;"",E476&lt;&gt;"",E476&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9366,8 +9377,8 @@
       <c r="B477" s="55" t="n"/>
       <c r="C477" s="54" t="n"/>
       <c r="D477" s="54" t="n"/>
-      <c r="E477" s="56" t="n"/>
-      <c r="F477" s="56" t="n"/>
+      <c r="E477" s="61" t="n"/>
+      <c r="F477" s="61" t="n"/>
       <c r="G477" s="57">
         <f>IF(AND(D477&lt;&gt;"已完成",D477&lt;&gt;"",E477&lt;&gt;"",E477&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9380,8 +9391,8 @@
       <c r="B478" s="55" t="n"/>
       <c r="C478" s="54" t="n"/>
       <c r="D478" s="54" t="n"/>
-      <c r="E478" s="56" t="n"/>
-      <c r="F478" s="56" t="n"/>
+      <c r="E478" s="61" t="n"/>
+      <c r="F478" s="61" t="n"/>
       <c r="G478" s="57">
         <f>IF(AND(D478&lt;&gt;"已完成",D478&lt;&gt;"",E478&lt;&gt;"",E478&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9394,8 +9405,8 @@
       <c r="B479" s="55" t="n"/>
       <c r="C479" s="54" t="n"/>
       <c r="D479" s="54" t="n"/>
-      <c r="E479" s="56" t="n"/>
-      <c r="F479" s="56" t="n"/>
+      <c r="E479" s="61" t="n"/>
+      <c r="F479" s="61" t="n"/>
       <c r="G479" s="57">
         <f>IF(AND(D479&lt;&gt;"已完成",D479&lt;&gt;"",E479&lt;&gt;"",E479&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9408,8 +9419,8 @@
       <c r="B480" s="55" t="n"/>
       <c r="C480" s="54" t="n"/>
       <c r="D480" s="54" t="n"/>
-      <c r="E480" s="56" t="n"/>
-      <c r="F480" s="56" t="n"/>
+      <c r="E480" s="61" t="n"/>
+      <c r="F480" s="61" t="n"/>
       <c r="G480" s="57">
         <f>IF(AND(D480&lt;&gt;"已完成",D480&lt;&gt;"",E480&lt;&gt;"",E480&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9422,8 +9433,8 @@
       <c r="B481" s="55" t="n"/>
       <c r="C481" s="54" t="n"/>
       <c r="D481" s="54" t="n"/>
-      <c r="E481" s="56" t="n"/>
-      <c r="F481" s="56" t="n"/>
+      <c r="E481" s="61" t="n"/>
+      <c r="F481" s="61" t="n"/>
       <c r="G481" s="57">
         <f>IF(AND(D481&lt;&gt;"已完成",D481&lt;&gt;"",E481&lt;&gt;"",E481&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9436,8 +9447,8 @@
       <c r="B482" s="55" t="n"/>
       <c r="C482" s="54" t="n"/>
       <c r="D482" s="54" t="n"/>
-      <c r="E482" s="56" t="n"/>
-      <c r="F482" s="56" t="n"/>
+      <c r="E482" s="61" t="n"/>
+      <c r="F482" s="61" t="n"/>
       <c r="G482" s="57">
         <f>IF(AND(D482&lt;&gt;"已完成",D482&lt;&gt;"",E482&lt;&gt;"",E482&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9450,8 +9461,8 @@
       <c r="B483" s="55" t="n"/>
       <c r="C483" s="54" t="n"/>
       <c r="D483" s="54" t="n"/>
-      <c r="E483" s="56" t="n"/>
-      <c r="F483" s="56" t="n"/>
+      <c r="E483" s="61" t="n"/>
+      <c r="F483" s="61" t="n"/>
       <c r="G483" s="57">
         <f>IF(AND(D483&lt;&gt;"已完成",D483&lt;&gt;"",E483&lt;&gt;"",E483&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9464,8 +9475,8 @@
       <c r="B484" s="55" t="n"/>
       <c r="C484" s="54" t="n"/>
       <c r="D484" s="54" t="n"/>
-      <c r="E484" s="56" t="n"/>
-      <c r="F484" s="56" t="n"/>
+      <c r="E484" s="61" t="n"/>
+      <c r="F484" s="61" t="n"/>
       <c r="G484" s="57">
         <f>IF(AND(D484&lt;&gt;"已完成",D484&lt;&gt;"",E484&lt;&gt;"",E484&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9478,8 +9489,8 @@
       <c r="B485" s="55" t="n"/>
       <c r="C485" s="54" t="n"/>
       <c r="D485" s="54" t="n"/>
-      <c r="E485" s="56" t="n"/>
-      <c r="F485" s="56" t="n"/>
+      <c r="E485" s="61" t="n"/>
+      <c r="F485" s="61" t="n"/>
       <c r="G485" s="57">
         <f>IF(AND(D485&lt;&gt;"已完成",D485&lt;&gt;"",E485&lt;&gt;"",E485&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9492,8 +9503,8 @@
       <c r="B486" s="55" t="n"/>
       <c r="C486" s="54" t="n"/>
       <c r="D486" s="54" t="n"/>
-      <c r="E486" s="56" t="n"/>
-      <c r="F486" s="56" t="n"/>
+      <c r="E486" s="61" t="n"/>
+      <c r="F486" s="61" t="n"/>
       <c r="G486" s="57">
         <f>IF(AND(D486&lt;&gt;"已完成",D486&lt;&gt;"",E486&lt;&gt;"",E486&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9506,8 +9517,8 @@
       <c r="B487" s="55" t="n"/>
       <c r="C487" s="54" t="n"/>
       <c r="D487" s="54" t="n"/>
-      <c r="E487" s="56" t="n"/>
-      <c r="F487" s="56" t="n"/>
+      <c r="E487" s="61" t="n"/>
+      <c r="F487" s="61" t="n"/>
       <c r="G487" s="57">
         <f>IF(AND(D487&lt;&gt;"已完成",D487&lt;&gt;"",E487&lt;&gt;"",E487&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9520,8 +9531,8 @@
       <c r="B488" s="55" t="n"/>
       <c r="C488" s="54" t="n"/>
       <c r="D488" s="54" t="n"/>
-      <c r="E488" s="56" t="n"/>
-      <c r="F488" s="56" t="n"/>
+      <c r="E488" s="61" t="n"/>
+      <c r="F488" s="61" t="n"/>
       <c r="G488" s="57">
         <f>IF(AND(D488&lt;&gt;"已完成",D488&lt;&gt;"",E488&lt;&gt;"",E488&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9534,8 +9545,8 @@
       <c r="B489" s="55" t="n"/>
       <c r="C489" s="54" t="n"/>
       <c r="D489" s="54" t="n"/>
-      <c r="E489" s="56" t="n"/>
-      <c r="F489" s="56" t="n"/>
+      <c r="E489" s="61" t="n"/>
+      <c r="F489" s="61" t="n"/>
       <c r="G489" s="57">
         <f>IF(AND(D489&lt;&gt;"已完成",D489&lt;&gt;"",E489&lt;&gt;"",E489&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9548,8 +9559,8 @@
       <c r="B490" s="55" t="n"/>
       <c r="C490" s="54" t="n"/>
       <c r="D490" s="54" t="n"/>
-      <c r="E490" s="56" t="n"/>
-      <c r="F490" s="56" t="n"/>
+      <c r="E490" s="61" t="n"/>
+      <c r="F490" s="61" t="n"/>
       <c r="G490" s="57">
         <f>IF(AND(D490&lt;&gt;"已完成",D490&lt;&gt;"",E490&lt;&gt;"",E490&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9562,8 +9573,8 @@
       <c r="B491" s="55" t="n"/>
       <c r="C491" s="54" t="n"/>
       <c r="D491" s="54" t="n"/>
-      <c r="E491" s="56" t="n"/>
-      <c r="F491" s="56" t="n"/>
+      <c r="E491" s="61" t="n"/>
+      <c r="F491" s="61" t="n"/>
       <c r="G491" s="57">
         <f>IF(AND(D491&lt;&gt;"已完成",D491&lt;&gt;"",E491&lt;&gt;"",E491&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9576,8 +9587,8 @@
       <c r="B492" s="55" t="n"/>
       <c r="C492" s="54" t="n"/>
       <c r="D492" s="54" t="n"/>
-      <c r="E492" s="56" t="n"/>
-      <c r="F492" s="56" t="n"/>
+      <c r="E492" s="61" t="n"/>
+      <c r="F492" s="61" t="n"/>
       <c r="G492" s="57">
         <f>IF(AND(D492&lt;&gt;"已完成",D492&lt;&gt;"",E492&lt;&gt;"",E492&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9590,8 +9601,8 @@
       <c r="B493" s="55" t="n"/>
       <c r="C493" s="54" t="n"/>
       <c r="D493" s="54" t="n"/>
-      <c r="E493" s="56" t="n"/>
-      <c r="F493" s="56" t="n"/>
+      <c r="E493" s="61" t="n"/>
+      <c r="F493" s="61" t="n"/>
       <c r="G493" s="57">
         <f>IF(AND(D493&lt;&gt;"已完成",D493&lt;&gt;"",E493&lt;&gt;"",E493&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9604,8 +9615,8 @@
       <c r="B494" s="55" t="n"/>
       <c r="C494" s="54" t="n"/>
       <c r="D494" s="54" t="n"/>
-      <c r="E494" s="56" t="n"/>
-      <c r="F494" s="56" t="n"/>
+      <c r="E494" s="61" t="n"/>
+      <c r="F494" s="61" t="n"/>
       <c r="G494" s="57">
         <f>IF(AND(D494&lt;&gt;"已完成",D494&lt;&gt;"",E494&lt;&gt;"",E494&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9618,8 +9629,8 @@
       <c r="B495" s="55" t="n"/>
       <c r="C495" s="54" t="n"/>
       <c r="D495" s="54" t="n"/>
-      <c r="E495" s="56" t="n"/>
-      <c r="F495" s="56" t="n"/>
+      <c r="E495" s="61" t="n"/>
+      <c r="F495" s="61" t="n"/>
       <c r="G495" s="57">
         <f>IF(AND(D495&lt;&gt;"已完成",D495&lt;&gt;"",E495&lt;&gt;"",E495&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9632,8 +9643,8 @@
       <c r="B496" s="55" t="n"/>
       <c r="C496" s="54" t="n"/>
       <c r="D496" s="54" t="n"/>
-      <c r="E496" s="56" t="n"/>
-      <c r="F496" s="56" t="n"/>
+      <c r="E496" s="61" t="n"/>
+      <c r="F496" s="61" t="n"/>
       <c r="G496" s="57">
         <f>IF(AND(D496&lt;&gt;"已完成",D496&lt;&gt;"",E496&lt;&gt;"",E496&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9646,8 +9657,8 @@
       <c r="B497" s="55" t="n"/>
       <c r="C497" s="54" t="n"/>
       <c r="D497" s="54" t="n"/>
-      <c r="E497" s="56" t="n"/>
-      <c r="F497" s="56" t="n"/>
+      <c r="E497" s="61" t="n"/>
+      <c r="F497" s="61" t="n"/>
       <c r="G497" s="57">
         <f>IF(AND(D497&lt;&gt;"已完成",D497&lt;&gt;"",E497&lt;&gt;"",E497&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9660,8 +9671,8 @@
       <c r="B498" s="55" t="n"/>
       <c r="C498" s="54" t="n"/>
       <c r="D498" s="54" t="n"/>
-      <c r="E498" s="56" t="n"/>
-      <c r="F498" s="56" t="n"/>
+      <c r="E498" s="61" t="n"/>
+      <c r="F498" s="61" t="n"/>
       <c r="G498" s="57">
         <f>IF(AND(D498&lt;&gt;"已完成",D498&lt;&gt;"",E498&lt;&gt;"",E498&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9674,8 +9685,8 @@
       <c r="B499" s="55" t="n"/>
       <c r="C499" s="54" t="n"/>
       <c r="D499" s="54" t="n"/>
-      <c r="E499" s="56" t="n"/>
-      <c r="F499" s="56" t="n"/>
+      <c r="E499" s="61" t="n"/>
+      <c r="F499" s="61" t="n"/>
       <c r="G499" s="57">
         <f>IF(AND(D499&lt;&gt;"已完成",D499&lt;&gt;"",E499&lt;&gt;"",E499&lt;TODAY()),"⚠️延期","")</f>
         <v/>
@@ -9688,8 +9699,8 @@
       <c r="B500" s="55" t="n"/>
       <c r="C500" s="54" t="n"/>
       <c r="D500" s="54" t="n"/>
-      <c r="E500" s="56" t="n"/>
-      <c r="F500" s="56" t="n"/>
+      <c r="E500" s="61" t="n"/>
+      <c r="F500" s="61" t="n"/>
       <c r="G500" s="57">
         <f>IF(AND(D500&lt;&gt;"已完成",D500&lt;&gt;"",E500&lt;&gt;"",E500&lt;TODAY()),"⚠️延期","")</f>
         <v/>
